--- a/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD39"/>
+  <dimension ref="A1:BG39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,6 +677,15 @@
       <c r="BA2" t="n">
         <v>6</v>
       </c>
+      <c r="BB2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -941,6 +950,21 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
           <t>[S]</t>
         </is>
       </c>
@@ -1213,15 +1237,30 @@
       </c>
       <c r="BB4" s="4" t="inlineStr">
         <is>
+          <t>Q53</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
+        <is>
+          <t>Q54</t>
+        </is>
+      </c>
+      <c r="BD4" s="4" t="inlineStr">
+        <is>
+          <t>Q55</t>
+        </is>
+      </c>
+      <c r="BE4" s="4" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="BF4" s="4" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr">
+      <c r="BG4" s="4" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
@@ -1283,16 +1322,19 @@
       <c r="AY5" s="5" t="n"/>
       <c r="AZ5" s="5" t="n"/>
       <c r="BA5" s="5" t="n"/>
-      <c r="BB5">
-        <f>IF(COUNT(B5:BA5)=0,"",SUM(B5:BA5))</f>
-        <v/>
-      </c>
-      <c r="BC5">
-        <f>COUNT(B5:BA5)</f>
-        <v/>
-      </c>
-      <c r="BD5">
-        <f>IF(OR(BB5="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB5,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB5,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB5" s="5" t="n"/>
+      <c r="BC5" s="5" t="n"/>
+      <c r="BD5" s="5" t="n"/>
+      <c r="BE5">
+        <f>IF(COUNT(B5:BD5)=0,"",SUM(B5:BD5))</f>
+        <v/>
+      </c>
+      <c r="BF5">
+        <f>COUNT(B5:BD5)</f>
+        <v/>
+      </c>
+      <c r="BG5">
+        <f>IF(OR(BE5="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE5,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE5,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1352,16 +1394,19 @@
       <c r="AY6" s="5" t="n"/>
       <c r="AZ6" s="5" t="n"/>
       <c r="BA6" s="5" t="n"/>
-      <c r="BB6">
-        <f>IF(COUNT(B6:BA6)=0,"",SUM(B6:BA6))</f>
-        <v/>
-      </c>
-      <c r="BC6">
-        <f>COUNT(B6:BA6)</f>
-        <v/>
-      </c>
-      <c r="BD6">
-        <f>IF(OR(BB6="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB6,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB6,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB6" s="5" t="n"/>
+      <c r="BC6" s="5" t="n"/>
+      <c r="BD6" s="5" t="n"/>
+      <c r="BE6">
+        <f>IF(COUNT(B6:BD6)=0,"",SUM(B6:BD6))</f>
+        <v/>
+      </c>
+      <c r="BF6">
+        <f>COUNT(B6:BD6)</f>
+        <v/>
+      </c>
+      <c r="BG6">
+        <f>IF(OR(BE6="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE6,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE6,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1421,16 +1466,19 @@
       <c r="AY7" s="5" t="n"/>
       <c r="AZ7" s="5" t="n"/>
       <c r="BA7" s="5" t="n"/>
-      <c r="BB7">
-        <f>IF(COUNT(B7:BA7)=0,"",SUM(B7:BA7))</f>
-        <v/>
-      </c>
-      <c r="BC7">
-        <f>COUNT(B7:BA7)</f>
-        <v/>
-      </c>
-      <c r="BD7">
-        <f>IF(OR(BB7="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB7,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB7,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB7" s="5" t="n"/>
+      <c r="BC7" s="5" t="n"/>
+      <c r="BD7" s="5" t="n"/>
+      <c r="BE7">
+        <f>IF(COUNT(B7:BD7)=0,"",SUM(B7:BD7))</f>
+        <v/>
+      </c>
+      <c r="BF7">
+        <f>COUNT(B7:BD7)</f>
+        <v/>
+      </c>
+      <c r="BG7">
+        <f>IF(OR(BE7="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE7,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE7,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1490,16 +1538,19 @@
       <c r="AY8" s="5" t="n"/>
       <c r="AZ8" s="5" t="n"/>
       <c r="BA8" s="5" t="n"/>
-      <c r="BB8">
-        <f>IF(COUNT(B8:BA8)=0,"",SUM(B8:BA8))</f>
-        <v/>
-      </c>
-      <c r="BC8">
-        <f>COUNT(B8:BA8)</f>
-        <v/>
-      </c>
-      <c r="BD8">
-        <f>IF(OR(BB8="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB8,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB8,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB8" s="5" t="n"/>
+      <c r="BC8" s="5" t="n"/>
+      <c r="BD8" s="5" t="n"/>
+      <c r="BE8">
+        <f>IF(COUNT(B8:BD8)=0,"",SUM(B8:BD8))</f>
+        <v/>
+      </c>
+      <c r="BF8">
+        <f>COUNT(B8:BD8)</f>
+        <v/>
+      </c>
+      <c r="BG8">
+        <f>IF(OR(BE8="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE8,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE8,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1559,16 +1610,19 @@
       <c r="AY9" s="5" t="n"/>
       <c r="AZ9" s="5" t="n"/>
       <c r="BA9" s="5" t="n"/>
-      <c r="BB9">
-        <f>IF(COUNT(B9:BA9)=0,"",SUM(B9:BA9))</f>
-        <v/>
-      </c>
-      <c r="BC9">
-        <f>COUNT(B9:BA9)</f>
-        <v/>
-      </c>
-      <c r="BD9">
-        <f>IF(OR(BB9="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB9,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB9,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB9" s="5" t="n"/>
+      <c r="BC9" s="5" t="n"/>
+      <c r="BD9" s="5" t="n"/>
+      <c r="BE9">
+        <f>IF(COUNT(B9:BD9)=0,"",SUM(B9:BD9))</f>
+        <v/>
+      </c>
+      <c r="BF9">
+        <f>COUNT(B9:BD9)</f>
+        <v/>
+      </c>
+      <c r="BG9">
+        <f>IF(OR(BE9="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE9,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE9,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1628,16 +1682,19 @@
       <c r="AY10" s="5" t="n"/>
       <c r="AZ10" s="5" t="n"/>
       <c r="BA10" s="5" t="n"/>
-      <c r="BB10">
-        <f>IF(COUNT(B10:BA10)=0,"",SUM(B10:BA10))</f>
-        <v/>
-      </c>
-      <c r="BC10">
-        <f>COUNT(B10:BA10)</f>
-        <v/>
-      </c>
-      <c r="BD10">
-        <f>IF(OR(BB10="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB10,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB10,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB10" s="5" t="n"/>
+      <c r="BC10" s="5" t="n"/>
+      <c r="BD10" s="5" t="n"/>
+      <c r="BE10">
+        <f>IF(COUNT(B10:BD10)=0,"",SUM(B10:BD10))</f>
+        <v/>
+      </c>
+      <c r="BF10">
+        <f>COUNT(B10:BD10)</f>
+        <v/>
+      </c>
+      <c r="BG10">
+        <f>IF(OR(BE10="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE10,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE10,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1697,16 +1754,19 @@
       <c r="AY11" s="5" t="n"/>
       <c r="AZ11" s="5" t="n"/>
       <c r="BA11" s="5" t="n"/>
-      <c r="BB11">
-        <f>IF(COUNT(B11:BA11)=0,"",SUM(B11:BA11))</f>
-        <v/>
-      </c>
-      <c r="BC11">
-        <f>COUNT(B11:BA11)</f>
-        <v/>
-      </c>
-      <c r="BD11">
-        <f>IF(OR(BB11="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB11,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB11,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB11" s="5" t="n"/>
+      <c r="BC11" s="5" t="n"/>
+      <c r="BD11" s="5" t="n"/>
+      <c r="BE11">
+        <f>IF(COUNT(B11:BD11)=0,"",SUM(B11:BD11))</f>
+        <v/>
+      </c>
+      <c r="BF11">
+        <f>COUNT(B11:BD11)</f>
+        <v/>
+      </c>
+      <c r="BG11">
+        <f>IF(OR(BE11="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE11,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE11,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1766,16 +1826,19 @@
       <c r="AY12" s="5" t="n"/>
       <c r="AZ12" s="5" t="n"/>
       <c r="BA12" s="5" t="n"/>
-      <c r="BB12">
-        <f>IF(COUNT(B12:BA12)=0,"",SUM(B12:BA12))</f>
-        <v/>
-      </c>
-      <c r="BC12">
-        <f>COUNT(B12:BA12)</f>
-        <v/>
-      </c>
-      <c r="BD12">
-        <f>IF(OR(BB12="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB12,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB12,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB12" s="5" t="n"/>
+      <c r="BC12" s="5" t="n"/>
+      <c r="BD12" s="5" t="n"/>
+      <c r="BE12">
+        <f>IF(COUNT(B12:BD12)=0,"",SUM(B12:BD12))</f>
+        <v/>
+      </c>
+      <c r="BF12">
+        <f>COUNT(B12:BD12)</f>
+        <v/>
+      </c>
+      <c r="BG12">
+        <f>IF(OR(BE12="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE12,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE12,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1835,16 +1898,19 @@
       <c r="AY13" s="5" t="n"/>
       <c r="AZ13" s="5" t="n"/>
       <c r="BA13" s="5" t="n"/>
-      <c r="BB13">
-        <f>IF(COUNT(B13:BA13)=0,"",SUM(B13:BA13))</f>
-        <v/>
-      </c>
-      <c r="BC13">
-        <f>COUNT(B13:BA13)</f>
-        <v/>
-      </c>
-      <c r="BD13">
-        <f>IF(OR(BB13="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB13,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB13,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB13" s="5" t="n"/>
+      <c r="BC13" s="5" t="n"/>
+      <c r="BD13" s="5" t="n"/>
+      <c r="BE13">
+        <f>IF(COUNT(B13:BD13)=0,"",SUM(B13:BD13))</f>
+        <v/>
+      </c>
+      <c r="BF13">
+        <f>COUNT(B13:BD13)</f>
+        <v/>
+      </c>
+      <c r="BG13">
+        <f>IF(OR(BE13="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE13,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE13,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1904,16 +1970,19 @@
       <c r="AY14" s="5" t="n"/>
       <c r="AZ14" s="5" t="n"/>
       <c r="BA14" s="5" t="n"/>
-      <c r="BB14">
-        <f>IF(COUNT(B14:BA14)=0,"",SUM(B14:BA14))</f>
-        <v/>
-      </c>
-      <c r="BC14">
-        <f>COUNT(B14:BA14)</f>
-        <v/>
-      </c>
-      <c r="BD14">
-        <f>IF(OR(BB14="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB14,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB14,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB14" s="5" t="n"/>
+      <c r="BC14" s="5" t="n"/>
+      <c r="BD14" s="5" t="n"/>
+      <c r="BE14">
+        <f>IF(COUNT(B14:BD14)=0,"",SUM(B14:BD14))</f>
+        <v/>
+      </c>
+      <c r="BF14">
+        <f>COUNT(B14:BD14)</f>
+        <v/>
+      </c>
+      <c r="BG14">
+        <f>IF(OR(BE14="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE14,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE14,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1973,16 +2042,19 @@
       <c r="AY15" s="5" t="n"/>
       <c r="AZ15" s="5" t="n"/>
       <c r="BA15" s="5" t="n"/>
-      <c r="BB15">
-        <f>IF(COUNT(B15:BA15)=0,"",SUM(B15:BA15))</f>
-        <v/>
-      </c>
-      <c r="BC15">
-        <f>COUNT(B15:BA15)</f>
-        <v/>
-      </c>
-      <c r="BD15">
-        <f>IF(OR(BB15="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB15,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB15,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB15" s="5" t="n"/>
+      <c r="BC15" s="5" t="n"/>
+      <c r="BD15" s="5" t="n"/>
+      <c r="BE15">
+        <f>IF(COUNT(B15:BD15)=0,"",SUM(B15:BD15))</f>
+        <v/>
+      </c>
+      <c r="BF15">
+        <f>COUNT(B15:BD15)</f>
+        <v/>
+      </c>
+      <c r="BG15">
+        <f>IF(OR(BE15="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE15,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE15,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2042,16 +2114,19 @@
       <c r="AY16" s="5" t="n"/>
       <c r="AZ16" s="5" t="n"/>
       <c r="BA16" s="5" t="n"/>
-      <c r="BB16">
-        <f>IF(COUNT(B16:BA16)=0,"",SUM(B16:BA16))</f>
-        <v/>
-      </c>
-      <c r="BC16">
-        <f>COUNT(B16:BA16)</f>
-        <v/>
-      </c>
-      <c r="BD16">
-        <f>IF(OR(BB16="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB16,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB16,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB16" s="5" t="n"/>
+      <c r="BC16" s="5" t="n"/>
+      <c r="BD16" s="5" t="n"/>
+      <c r="BE16">
+        <f>IF(COUNT(B16:BD16)=0,"",SUM(B16:BD16))</f>
+        <v/>
+      </c>
+      <c r="BF16">
+        <f>COUNT(B16:BD16)</f>
+        <v/>
+      </c>
+      <c r="BG16">
+        <f>IF(OR(BE16="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE16,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE16,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2111,16 +2186,19 @@
       <c r="AY17" s="5" t="n"/>
       <c r="AZ17" s="5" t="n"/>
       <c r="BA17" s="5" t="n"/>
-      <c r="BB17">
-        <f>IF(COUNT(B17:BA17)=0,"",SUM(B17:BA17))</f>
-        <v/>
-      </c>
-      <c r="BC17">
-        <f>COUNT(B17:BA17)</f>
-        <v/>
-      </c>
-      <c r="BD17">
-        <f>IF(OR(BB17="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB17,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB17,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB17" s="5" t="n"/>
+      <c r="BC17" s="5" t="n"/>
+      <c r="BD17" s="5" t="n"/>
+      <c r="BE17">
+        <f>IF(COUNT(B17:BD17)=0,"",SUM(B17:BD17))</f>
+        <v/>
+      </c>
+      <c r="BF17">
+        <f>COUNT(B17:BD17)</f>
+        <v/>
+      </c>
+      <c r="BG17">
+        <f>IF(OR(BE17="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE17,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE17,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2180,16 +2258,19 @@
       <c r="AY18" s="5" t="n"/>
       <c r="AZ18" s="5" t="n"/>
       <c r="BA18" s="5" t="n"/>
-      <c r="BB18">
-        <f>IF(COUNT(B18:BA18)=0,"",SUM(B18:BA18))</f>
-        <v/>
-      </c>
-      <c r="BC18">
-        <f>COUNT(B18:BA18)</f>
-        <v/>
-      </c>
-      <c r="BD18">
-        <f>IF(OR(BB18="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB18,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB18,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB18" s="5" t="n"/>
+      <c r="BC18" s="5" t="n"/>
+      <c r="BD18" s="5" t="n"/>
+      <c r="BE18">
+        <f>IF(COUNT(B18:BD18)=0,"",SUM(B18:BD18))</f>
+        <v/>
+      </c>
+      <c r="BF18">
+        <f>COUNT(B18:BD18)</f>
+        <v/>
+      </c>
+      <c r="BG18">
+        <f>IF(OR(BE18="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE18,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE18,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2249,16 +2330,19 @@
       <c r="AY19" s="5" t="n"/>
       <c r="AZ19" s="5" t="n"/>
       <c r="BA19" s="5" t="n"/>
-      <c r="BB19">
-        <f>IF(COUNT(B19:BA19)=0,"",SUM(B19:BA19))</f>
-        <v/>
-      </c>
-      <c r="BC19">
-        <f>COUNT(B19:BA19)</f>
-        <v/>
-      </c>
-      <c r="BD19">
-        <f>IF(OR(BB19="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB19,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB19,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB19" s="5" t="n"/>
+      <c r="BC19" s="5" t="n"/>
+      <c r="BD19" s="5" t="n"/>
+      <c r="BE19">
+        <f>IF(COUNT(B19:BD19)=0,"",SUM(B19:BD19))</f>
+        <v/>
+      </c>
+      <c r="BF19">
+        <f>COUNT(B19:BD19)</f>
+        <v/>
+      </c>
+      <c r="BG19">
+        <f>IF(OR(BE19="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE19,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE19,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2318,16 +2402,19 @@
       <c r="AY20" s="5" t="n"/>
       <c r="AZ20" s="5" t="n"/>
       <c r="BA20" s="5" t="n"/>
-      <c r="BB20">
-        <f>IF(COUNT(B20:BA20)=0,"",SUM(B20:BA20))</f>
-        <v/>
-      </c>
-      <c r="BC20">
-        <f>COUNT(B20:BA20)</f>
-        <v/>
-      </c>
-      <c r="BD20">
-        <f>IF(OR(BB20="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB20,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB20,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB20" s="5" t="n"/>
+      <c r="BC20" s="5" t="n"/>
+      <c r="BD20" s="5" t="n"/>
+      <c r="BE20">
+        <f>IF(COUNT(B20:BD20)=0,"",SUM(B20:BD20))</f>
+        <v/>
+      </c>
+      <c r="BF20">
+        <f>COUNT(B20:BD20)</f>
+        <v/>
+      </c>
+      <c r="BG20">
+        <f>IF(OR(BE20="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE20,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE20,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2387,16 +2474,19 @@
       <c r="AY21" s="5" t="n"/>
       <c r="AZ21" s="5" t="n"/>
       <c r="BA21" s="5" t="n"/>
-      <c r="BB21">
-        <f>IF(COUNT(B21:BA21)=0,"",SUM(B21:BA21))</f>
-        <v/>
-      </c>
-      <c r="BC21">
-        <f>COUNT(B21:BA21)</f>
-        <v/>
-      </c>
-      <c r="BD21">
-        <f>IF(OR(BB21="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB21,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB21,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB21" s="5" t="n"/>
+      <c r="BC21" s="5" t="n"/>
+      <c r="BD21" s="5" t="n"/>
+      <c r="BE21">
+        <f>IF(COUNT(B21:BD21)=0,"",SUM(B21:BD21))</f>
+        <v/>
+      </c>
+      <c r="BF21">
+        <f>COUNT(B21:BD21)</f>
+        <v/>
+      </c>
+      <c r="BG21">
+        <f>IF(OR(BE21="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE21,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE21,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2456,16 +2546,19 @@
       <c r="AY22" s="5" t="n"/>
       <c r="AZ22" s="5" t="n"/>
       <c r="BA22" s="5" t="n"/>
-      <c r="BB22">
-        <f>IF(COUNT(B22:BA22)=0,"",SUM(B22:BA22))</f>
-        <v/>
-      </c>
-      <c r="BC22">
-        <f>COUNT(B22:BA22)</f>
-        <v/>
-      </c>
-      <c r="BD22">
-        <f>IF(OR(BB22="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB22,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB22,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB22" s="5" t="n"/>
+      <c r="BC22" s="5" t="n"/>
+      <c r="BD22" s="5" t="n"/>
+      <c r="BE22">
+        <f>IF(COUNT(B22:BD22)=0,"",SUM(B22:BD22))</f>
+        <v/>
+      </c>
+      <c r="BF22">
+        <f>COUNT(B22:BD22)</f>
+        <v/>
+      </c>
+      <c r="BG22">
+        <f>IF(OR(BE22="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE22,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE22,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2525,16 +2618,19 @@
       <c r="AY23" s="5" t="n"/>
       <c r="AZ23" s="5" t="n"/>
       <c r="BA23" s="5" t="n"/>
-      <c r="BB23">
-        <f>IF(COUNT(B23:BA23)=0,"",SUM(B23:BA23))</f>
-        <v/>
-      </c>
-      <c r="BC23">
-        <f>COUNT(B23:BA23)</f>
-        <v/>
-      </c>
-      <c r="BD23">
-        <f>IF(OR(BB23="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB23,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB23,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB23" s="5" t="n"/>
+      <c r="BC23" s="5" t="n"/>
+      <c r="BD23" s="5" t="n"/>
+      <c r="BE23">
+        <f>IF(COUNT(B23:BD23)=0,"",SUM(B23:BD23))</f>
+        <v/>
+      </c>
+      <c r="BF23">
+        <f>COUNT(B23:BD23)</f>
+        <v/>
+      </c>
+      <c r="BG23">
+        <f>IF(OR(BE23="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE23,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE23,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2594,16 +2690,19 @@
       <c r="AY24" s="5" t="n"/>
       <c r="AZ24" s="5" t="n"/>
       <c r="BA24" s="5" t="n"/>
-      <c r="BB24">
-        <f>IF(COUNT(B24:BA24)=0,"",SUM(B24:BA24))</f>
-        <v/>
-      </c>
-      <c r="BC24">
-        <f>COUNT(B24:BA24)</f>
-        <v/>
-      </c>
-      <c r="BD24">
-        <f>IF(OR(BB24="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB24,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB24,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB24" s="5" t="n"/>
+      <c r="BC24" s="5" t="n"/>
+      <c r="BD24" s="5" t="n"/>
+      <c r="BE24">
+        <f>IF(COUNT(B24:BD24)=0,"",SUM(B24:BD24))</f>
+        <v/>
+      </c>
+      <c r="BF24">
+        <f>COUNT(B24:BD24)</f>
+        <v/>
+      </c>
+      <c r="BG24">
+        <f>IF(OR(BE24="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE24,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE24,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2663,16 +2762,19 @@
       <c r="AY25" s="5" t="n"/>
       <c r="AZ25" s="5" t="n"/>
       <c r="BA25" s="5" t="n"/>
-      <c r="BB25">
-        <f>IF(COUNT(B25:BA25)=0,"",SUM(B25:BA25))</f>
-        <v/>
-      </c>
-      <c r="BC25">
-        <f>COUNT(B25:BA25)</f>
-        <v/>
-      </c>
-      <c r="BD25">
-        <f>IF(OR(BB25="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB25,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB25,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB25" s="5" t="n"/>
+      <c r="BC25" s="5" t="n"/>
+      <c r="BD25" s="5" t="n"/>
+      <c r="BE25">
+        <f>IF(COUNT(B25:BD25)=0,"",SUM(B25:BD25))</f>
+        <v/>
+      </c>
+      <c r="BF25">
+        <f>COUNT(B25:BD25)</f>
+        <v/>
+      </c>
+      <c r="BG25">
+        <f>IF(OR(BE25="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE25,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE25,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2732,16 +2834,19 @@
       <c r="AY26" s="5" t="n"/>
       <c r="AZ26" s="5" t="n"/>
       <c r="BA26" s="5" t="n"/>
-      <c r="BB26">
-        <f>IF(COUNT(B26:BA26)=0,"",SUM(B26:BA26))</f>
-        <v/>
-      </c>
-      <c r="BC26">
-        <f>COUNT(B26:BA26)</f>
-        <v/>
-      </c>
-      <c r="BD26">
-        <f>IF(OR(BB26="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB26,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB26,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB26" s="5" t="n"/>
+      <c r="BC26" s="5" t="n"/>
+      <c r="BD26" s="5" t="n"/>
+      <c r="BE26">
+        <f>IF(COUNT(B26:BD26)=0,"",SUM(B26:BD26))</f>
+        <v/>
+      </c>
+      <c r="BF26">
+        <f>COUNT(B26:BD26)</f>
+        <v/>
+      </c>
+      <c r="BG26">
+        <f>IF(OR(BE26="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE26,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE26,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2801,16 +2906,19 @@
       <c r="AY27" s="5" t="n"/>
       <c r="AZ27" s="5" t="n"/>
       <c r="BA27" s="5" t="n"/>
-      <c r="BB27">
-        <f>IF(COUNT(B27:BA27)=0,"",SUM(B27:BA27))</f>
-        <v/>
-      </c>
-      <c r="BC27">
-        <f>COUNT(B27:BA27)</f>
-        <v/>
-      </c>
-      <c r="BD27">
-        <f>IF(OR(BB27="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB27,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB27,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB27" s="5" t="n"/>
+      <c r="BC27" s="5" t="n"/>
+      <c r="BD27" s="5" t="n"/>
+      <c r="BE27">
+        <f>IF(COUNT(B27:BD27)=0,"",SUM(B27:BD27))</f>
+        <v/>
+      </c>
+      <c r="BF27">
+        <f>COUNT(B27:BD27)</f>
+        <v/>
+      </c>
+      <c r="BG27">
+        <f>IF(OR(BE27="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE27,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE27,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2870,16 +2978,19 @@
       <c r="AY28" s="5" t="n"/>
       <c r="AZ28" s="5" t="n"/>
       <c r="BA28" s="5" t="n"/>
-      <c r="BB28">
-        <f>IF(COUNT(B28:BA28)=0,"",SUM(B28:BA28))</f>
-        <v/>
-      </c>
-      <c r="BC28">
-        <f>COUNT(B28:BA28)</f>
-        <v/>
-      </c>
-      <c r="BD28">
-        <f>IF(OR(BB28="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB28,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB28,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB28" s="5" t="n"/>
+      <c r="BC28" s="5" t="n"/>
+      <c r="BD28" s="5" t="n"/>
+      <c r="BE28">
+        <f>IF(COUNT(B28:BD28)=0,"",SUM(B28:BD28))</f>
+        <v/>
+      </c>
+      <c r="BF28">
+        <f>COUNT(B28:BD28)</f>
+        <v/>
+      </c>
+      <c r="BG28">
+        <f>IF(OR(BE28="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE28,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE28,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2939,16 +3050,19 @@
       <c r="AY29" s="5" t="n"/>
       <c r="AZ29" s="5" t="n"/>
       <c r="BA29" s="5" t="n"/>
-      <c r="BB29">
-        <f>IF(COUNT(B29:BA29)=0,"",SUM(B29:BA29))</f>
-        <v/>
-      </c>
-      <c r="BC29">
-        <f>COUNT(B29:BA29)</f>
-        <v/>
-      </c>
-      <c r="BD29">
-        <f>IF(OR(BB29="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB29,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB29,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB29" s="5" t="n"/>
+      <c r="BC29" s="5" t="n"/>
+      <c r="BD29" s="5" t="n"/>
+      <c r="BE29">
+        <f>IF(COUNT(B29:BD29)=0,"",SUM(B29:BD29))</f>
+        <v/>
+      </c>
+      <c r="BF29">
+        <f>COUNT(B29:BD29)</f>
+        <v/>
+      </c>
+      <c r="BG29">
+        <f>IF(OR(BE29="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE29,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE29,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3008,16 +3122,19 @@
       <c r="AY30" s="5" t="n"/>
       <c r="AZ30" s="5" t="n"/>
       <c r="BA30" s="5" t="n"/>
-      <c r="BB30">
-        <f>IF(COUNT(B30:BA30)=0,"",SUM(B30:BA30))</f>
-        <v/>
-      </c>
-      <c r="BC30">
-        <f>COUNT(B30:BA30)</f>
-        <v/>
-      </c>
-      <c r="BD30">
-        <f>IF(OR(BB30="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB30,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB30,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB30" s="5" t="n"/>
+      <c r="BC30" s="5" t="n"/>
+      <c r="BD30" s="5" t="n"/>
+      <c r="BE30">
+        <f>IF(COUNT(B30:BD30)=0,"",SUM(B30:BD30))</f>
+        <v/>
+      </c>
+      <c r="BF30">
+        <f>COUNT(B30:BD30)</f>
+        <v/>
+      </c>
+      <c r="BG30">
+        <f>IF(OR(BE30="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE30,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE30,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3077,16 +3194,19 @@
       <c r="AY31" s="5" t="n"/>
       <c r="AZ31" s="5" t="n"/>
       <c r="BA31" s="5" t="n"/>
-      <c r="BB31">
-        <f>IF(COUNT(B31:BA31)=0,"",SUM(B31:BA31))</f>
-        <v/>
-      </c>
-      <c r="BC31">
-        <f>COUNT(B31:BA31)</f>
-        <v/>
-      </c>
-      <c r="BD31">
-        <f>IF(OR(BB31="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB31,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB31,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB31" s="5" t="n"/>
+      <c r="BC31" s="5" t="n"/>
+      <c r="BD31" s="5" t="n"/>
+      <c r="BE31">
+        <f>IF(COUNT(B31:BD31)=0,"",SUM(B31:BD31))</f>
+        <v/>
+      </c>
+      <c r="BF31">
+        <f>COUNT(B31:BD31)</f>
+        <v/>
+      </c>
+      <c r="BG31">
+        <f>IF(OR(BE31="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE31,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE31,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3146,16 +3266,19 @@
       <c r="AY32" s="5" t="n"/>
       <c r="AZ32" s="5" t="n"/>
       <c r="BA32" s="5" t="n"/>
-      <c r="BB32">
-        <f>IF(COUNT(B32:BA32)=0,"",SUM(B32:BA32))</f>
-        <v/>
-      </c>
-      <c r="BC32">
-        <f>COUNT(B32:BA32)</f>
-        <v/>
-      </c>
-      <c r="BD32">
-        <f>IF(OR(BB32="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB32,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB32,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB32" s="5" t="n"/>
+      <c r="BC32" s="5" t="n"/>
+      <c r="BD32" s="5" t="n"/>
+      <c r="BE32">
+        <f>IF(COUNT(B32:BD32)=0,"",SUM(B32:BD32))</f>
+        <v/>
+      </c>
+      <c r="BF32">
+        <f>COUNT(B32:BD32)</f>
+        <v/>
+      </c>
+      <c r="BG32">
+        <f>IF(OR(BE32="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE32,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE32,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3215,16 +3338,19 @@
       <c r="AY33" s="5" t="n"/>
       <c r="AZ33" s="5" t="n"/>
       <c r="BA33" s="5" t="n"/>
-      <c r="BB33">
-        <f>IF(COUNT(B33:BA33)=0,"",SUM(B33:BA33))</f>
-        <v/>
-      </c>
-      <c r="BC33">
-        <f>COUNT(B33:BA33)</f>
-        <v/>
-      </c>
-      <c r="BD33">
-        <f>IF(OR(BB33="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB33,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB33,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB33" s="5" t="n"/>
+      <c r="BC33" s="5" t="n"/>
+      <c r="BD33" s="5" t="n"/>
+      <c r="BE33">
+        <f>IF(COUNT(B33:BD33)=0,"",SUM(B33:BD33))</f>
+        <v/>
+      </c>
+      <c r="BF33">
+        <f>COUNT(B33:BD33)</f>
+        <v/>
+      </c>
+      <c r="BG33">
+        <f>IF(OR(BE33="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE33,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE33,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3284,16 +3410,19 @@
       <c r="AY34" s="5" t="n"/>
       <c r="AZ34" s="5" t="n"/>
       <c r="BA34" s="5" t="n"/>
-      <c r="BB34">
-        <f>IF(COUNT(B34:BA34)=0,"",SUM(B34:BA34))</f>
-        <v/>
-      </c>
-      <c r="BC34">
-        <f>COUNT(B34:BA34)</f>
-        <v/>
-      </c>
-      <c r="BD34">
-        <f>IF(OR(BB34="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB34,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB34,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB34" s="5" t="n"/>
+      <c r="BC34" s="5" t="n"/>
+      <c r="BD34" s="5" t="n"/>
+      <c r="BE34">
+        <f>IF(COUNT(B34:BD34)=0,"",SUM(B34:BD34))</f>
+        <v/>
+      </c>
+      <c r="BF34">
+        <f>COUNT(B34:BD34)</f>
+        <v/>
+      </c>
+      <c r="BG34">
+        <f>IF(OR(BE34="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE34,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE34,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3353,16 +3482,19 @@
       <c r="AY35" s="5" t="n"/>
       <c r="AZ35" s="5" t="n"/>
       <c r="BA35" s="5" t="n"/>
-      <c r="BB35">
-        <f>IF(COUNT(B35:BA35)=0,"",SUM(B35:BA35))</f>
-        <v/>
-      </c>
-      <c r="BC35">
-        <f>COUNT(B35:BA35)</f>
-        <v/>
-      </c>
-      <c r="BD35">
-        <f>IF(OR(BB35="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB35,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB35,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB35" s="5" t="n"/>
+      <c r="BC35" s="5" t="n"/>
+      <c r="BD35" s="5" t="n"/>
+      <c r="BE35">
+        <f>IF(COUNT(B35:BD35)=0,"",SUM(B35:BD35))</f>
+        <v/>
+      </c>
+      <c r="BF35">
+        <f>COUNT(B35:BD35)</f>
+        <v/>
+      </c>
+      <c r="BG35">
+        <f>IF(OR(BE35="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE35,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE35,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3422,16 +3554,19 @@
       <c r="AY36" s="5" t="n"/>
       <c r="AZ36" s="5" t="n"/>
       <c r="BA36" s="5" t="n"/>
-      <c r="BB36">
-        <f>IF(COUNT(B36:BA36)=0,"",SUM(B36:BA36))</f>
-        <v/>
-      </c>
-      <c r="BC36">
-        <f>COUNT(B36:BA36)</f>
-        <v/>
-      </c>
-      <c r="BD36">
-        <f>IF(OR(BB36="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB36,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB36,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB36" s="5" t="n"/>
+      <c r="BC36" s="5" t="n"/>
+      <c r="BD36" s="5" t="n"/>
+      <c r="BE36">
+        <f>IF(COUNT(B36:BD36)=0,"",SUM(B36:BD36))</f>
+        <v/>
+      </c>
+      <c r="BF36">
+        <f>COUNT(B36:BD36)</f>
+        <v/>
+      </c>
+      <c r="BG36">
+        <f>IF(OR(BE36="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE36,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE36,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3491,16 +3626,19 @@
       <c r="AY37" s="5" t="n"/>
       <c r="AZ37" s="5" t="n"/>
       <c r="BA37" s="5" t="n"/>
-      <c r="BB37">
-        <f>IF(COUNT(B37:BA37)=0,"",SUM(B37:BA37))</f>
-        <v/>
-      </c>
-      <c r="BC37">
-        <f>COUNT(B37:BA37)</f>
-        <v/>
-      </c>
-      <c r="BD37">
-        <f>IF(OR(BB37="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB37,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB37,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB37" s="5" t="n"/>
+      <c r="BC37" s="5" t="n"/>
+      <c r="BD37" s="5" t="n"/>
+      <c r="BE37">
+        <f>IF(COUNT(B37:BD37)=0,"",SUM(B37:BD37))</f>
+        <v/>
+      </c>
+      <c r="BF37">
+        <f>COUNT(B37:BD37)</f>
+        <v/>
+      </c>
+      <c r="BG37">
+        <f>IF(OR(BE37="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE37,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE37,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3560,16 +3698,19 @@
       <c r="AY38" s="5" t="n"/>
       <c r="AZ38" s="5" t="n"/>
       <c r="BA38" s="5" t="n"/>
-      <c r="BB38">
-        <f>IF(COUNT(B38:BA38)=0,"",SUM(B38:BA38))</f>
-        <v/>
-      </c>
-      <c r="BC38">
-        <f>COUNT(B38:BA38)</f>
-        <v/>
-      </c>
-      <c r="BD38">
-        <f>IF(OR(BB38="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB38,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB38,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB38" s="5" t="n"/>
+      <c r="BC38" s="5" t="n"/>
+      <c r="BD38" s="5" t="n"/>
+      <c r="BE38">
+        <f>IF(COUNT(B38:BD38)=0,"",SUM(B38:BD38))</f>
+        <v/>
+      </c>
+      <c r="BF38">
+        <f>COUNT(B38:BD38)</f>
+        <v/>
+      </c>
+      <c r="BG38">
+        <f>IF(OR(BE38="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE38,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE38,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3629,16 +3770,19 @@
       <c r="AY39" s="5" t="n"/>
       <c r="AZ39" s="5" t="n"/>
       <c r="BA39" s="5" t="n"/>
-      <c r="BB39">
-        <f>IF(COUNT(B39:BA39)=0,"",SUM(B39:BA39))</f>
-        <v/>
-      </c>
-      <c r="BC39">
-        <f>COUNT(B39:BA39)</f>
-        <v/>
-      </c>
-      <c r="BD39">
-        <f>IF(OR(BB39="",COUNT($BB$5:$BB$39)&lt;3),"",IF(RANK(BB39,$BB$5:$BB$39,0)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"top",IF(RANK(BB39,$BB$5:$BB$39,1)&lt;=ROUND(COUNT($BB$5:$BB$39)/3,0),"bottom","middle")))</f>
+      <c r="BB39" s="5" t="n"/>
+      <c r="BC39" s="5" t="n"/>
+      <c r="BD39" s="5" t="n"/>
+      <c r="BE39">
+        <f>IF(COUNT(B39:BD39)=0,"",SUM(B39:BD39))</f>
+        <v/>
+      </c>
+      <c r="BF39">
+        <f>COUNT(B39:BD39)</f>
+        <v/>
+      </c>
+      <c r="BG39">
+        <f>IF(OR(BE39="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE39,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE39,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3653,7 +3797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="13" max="13"/>
@@ -3778,11 +3922,11 @@
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="L5" s="6">
@@ -3838,11 +3982,11 @@
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="L6" s="6">
@@ -3898,11 +4042,11 @@
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="L7" s="6">
@@ -3958,11 +4102,11 @@
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="L8" s="6">
@@ -4018,11 +4162,11 @@
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="L9" s="6">
@@ -4078,11 +4222,11 @@
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="L10" s="6">
@@ -4138,11 +4282,11 @@
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="L11" s="6">
@@ -4198,11 +4342,11 @@
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="L12" s="6">
@@ -4258,11 +4402,11 @@
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="L13" s="6">
@@ -4318,11 +4462,11 @@
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="L14" s="6">
@@ -4378,11 +4522,11 @@
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="L15" s="6">
@@ -4438,11 +4582,11 @@
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="L16" s="6">
@@ -4498,11 +4642,11 @@
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="L17" s="6">
@@ -4558,11 +4702,11 @@
         <v/>
       </c>
       <c r="J18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="L18" s="6">
@@ -4618,11 +4762,11 @@
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="L19" s="6">
@@ -4678,11 +4822,11 @@
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="L20" s="6">
@@ -4738,11 +4882,11 @@
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="L21" s="6">
@@ -4798,11 +4942,11 @@
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="L22" s="6">
@@ -4858,11 +5002,11 @@
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="L23" s="6">
@@ -4918,11 +5062,11 @@
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="L24" s="6">
@@ -4978,11 +5122,11 @@
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="L25" s="6">
@@ -5038,11 +5182,11 @@
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="L26" s="6">
@@ -5098,11 +5242,11 @@
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="L27" s="6">
@@ -5158,11 +5302,11 @@
         <v/>
       </c>
       <c r="J28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="L28" s="6">
@@ -5218,11 +5362,11 @@
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="L29" s="6">
@@ -5278,11 +5422,11 @@
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="L30" s="6">
@@ -5338,11 +5482,11 @@
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="L31" s="6">
@@ -5398,11 +5542,11 @@
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="L32" s="6">
@@ -5458,11 +5602,11 @@
         <v/>
       </c>
       <c r="J33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="L33" s="6">
@@ -5518,11 +5662,11 @@
         <v/>
       </c>
       <c r="J34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="L34" s="6">
@@ -5578,11 +5722,11 @@
         <v/>
       </c>
       <c r="J35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="L35" s="6">
@@ -5638,11 +5782,11 @@
         <v/>
       </c>
       <c r="J36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="L36" s="6">
@@ -5698,11 +5842,11 @@
         <v/>
       </c>
       <c r="J37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="K37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="L37" s="6">
@@ -5758,11 +5902,11 @@
         <v/>
       </c>
       <c r="J38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
         <v/>
       </c>
       <c r="K38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
         <v/>
       </c>
       <c r="L38" s="6">
@@ -5818,11 +5962,11 @@
         <v/>
       </c>
       <c r="J39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
         <v/>
       </c>
       <c r="K39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
         <v/>
       </c>
       <c r="L39" s="6">
@@ -5878,11 +6022,11 @@
         <v/>
       </c>
       <c r="J40" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AK$5:AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AK$5:AK$39)))</f>
         <v/>
       </c>
       <c r="K40" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AK$5:AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AK$5:AK$39)))</f>
         <v/>
       </c>
       <c r="L40" s="6">
@@ -5938,11 +6082,11 @@
         <v/>
       </c>
       <c r="J41" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AL$5:AL$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AL$5:AL$39)))</f>
         <v/>
       </c>
       <c r="K41" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AL$5:AL$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AL$5:AL$39)))</f>
         <v/>
       </c>
       <c r="L41" s="6">
@@ -5998,11 +6142,11 @@
         <v/>
       </c>
       <c r="J42" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AM$5:AM$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AM$5:AM$39)))</f>
         <v/>
       </c>
       <c r="K42" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AM$5:AM$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AM$5:AM$39)))</f>
         <v/>
       </c>
       <c r="L42" s="6">
@@ -6058,11 +6202,11 @@
         <v/>
       </c>
       <c r="J43" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AN$5:AN$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AN$5:AN$39)))</f>
         <v/>
       </c>
       <c r="K43" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AN$5:AN$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AN$5:AN$39)))</f>
         <v/>
       </c>
       <c r="L43" s="6">
@@ -6118,11 +6262,11 @@
         <v/>
       </c>
       <c r="J44" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AO$5:AO$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AO$5:AO$39)))</f>
         <v/>
       </c>
       <c r="K44" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AO$5:AO$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AO$5:AO$39)))</f>
         <v/>
       </c>
       <c r="L44" s="6">
@@ -6178,11 +6322,11 @@
         <v/>
       </c>
       <c r="J45" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AP$5:AP$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AP$5:AP$39)))</f>
         <v/>
       </c>
       <c r="K45" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AP$5:AP$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AP$5:AP$39)))</f>
         <v/>
       </c>
       <c r="L45" s="6">
@@ -6238,11 +6382,11 @@
         <v/>
       </c>
       <c r="J46" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
         <v/>
       </c>
       <c r="K46" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
         <v/>
       </c>
       <c r="L46" s="6">
@@ -6298,11 +6442,11 @@
         <v/>
       </c>
       <c r="J47" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AR$5:AR$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AR$5:AR$39)))</f>
         <v/>
       </c>
       <c r="K47" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AR$5:AR$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AR$5:AR$39)))</f>
         <v/>
       </c>
       <c r="L47" s="6">
@@ -6358,11 +6502,11 @@
         <v/>
       </c>
       <c r="J48" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AS$5:AS$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AS$5:AS$39)))</f>
         <v/>
       </c>
       <c r="K48" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AS$5:AS$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AS$5:AS$39)))</f>
         <v/>
       </c>
       <c r="L48" s="6">
@@ -6418,11 +6562,11 @@
         <v/>
       </c>
       <c r="J49" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AT$5:AT$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AT$5:AT$39)))</f>
         <v/>
       </c>
       <c r="K49" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AT$5:AT$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AT$5:AT$39)))</f>
         <v/>
       </c>
       <c r="L49" s="6">
@@ -6478,11 +6622,11 @@
         <v/>
       </c>
       <c r="J50" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AU$5:AU$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AU$5:AU$39)))</f>
         <v/>
       </c>
       <c r="K50" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AU$5:AU$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AU$5:AU$39)))</f>
         <v/>
       </c>
       <c r="L50" s="6">
@@ -6538,11 +6682,11 @@
         <v/>
       </c>
       <c r="J51" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AV$5:AV$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AV$5:AV$39)))</f>
         <v/>
       </c>
       <c r="K51" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AV$5:AV$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AV$5:AV$39)))</f>
         <v/>
       </c>
       <c r="L51" s="6">
@@ -6598,11 +6742,11 @@
         <v/>
       </c>
       <c r="J52" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AW$5:AW$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AW$5:AW$39)))</f>
         <v/>
       </c>
       <c r="K52" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AW$5:AW$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AW$5:AW$39)))</f>
         <v/>
       </c>
       <c r="L52" s="6">
@@ -6658,11 +6802,11 @@
         <v/>
       </c>
       <c r="J53" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AX$5:AX$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AX$5:AX$39)))</f>
         <v/>
       </c>
       <c r="K53" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AX$5:AX$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AX$5:AX$39)))</f>
         <v/>
       </c>
       <c r="L53" s="6">
@@ -6718,11 +6862,11 @@
         <v/>
       </c>
       <c r="J54" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AY$5:AY$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AY$5:AY$39)))</f>
         <v/>
       </c>
       <c r="K54" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AY$5:AY$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AY$5:AY$39)))</f>
         <v/>
       </c>
       <c r="L54" s="6">
@@ -6778,11 +6922,11 @@
         <v/>
       </c>
       <c r="J55" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
         <v/>
       </c>
       <c r="K55" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
         <v/>
       </c>
       <c r="L55" s="6">
@@ -6812,17 +6956,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G56">
@@ -6838,11 +6982,11 @@
         <v/>
       </c>
       <c r="J56" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!BA$5:BA$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="top")*(Marks!BA$5:BA$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="top")*ISNUMBER(Marks!BA$5:BA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BA$5:BA$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!BA$5:BA$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BA$5:BA$39)))</f>
         <v/>
       </c>
       <c r="K56" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!BA$5:BA$39))=0,"",SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*(Marks!BA$5:BA$39=1))/SUMPRODUCT((Marks!$BD$5:$BD$39="bottom")*ISNUMBER(Marks!BA$5:BA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BA$5:BA$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!BA$5:BA$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BA$5:BA$39)))</f>
         <v/>
       </c>
       <c r="L56" s="6">
@@ -6855,6 +6999,186 @@
       </c>
       <c r="N56">
         <f>IF(H56=0,"",I56+ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Scenario set</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="G57">
+        <f>COUNTIF(Marks!BB$5:BB$39,1)</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>COUNT(Marks!BB$5:BB$39)</f>
+        <v/>
+      </c>
+      <c r="I57" s="6">
+        <f>IF(H57=0,"",G57/H57)</f>
+        <v/>
+      </c>
+      <c r="J57" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BB$5:BB$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!BB$5:BB$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BB$5:BB$39)))</f>
+        <v/>
+      </c>
+      <c r="K57" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BB$5:BB$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!BB$5:BB$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BB$5:BB$39)))</f>
+        <v/>
+      </c>
+      <c r="L57" s="6">
+        <f>IF(OR(J57="",K57=""),"",J57-K57)</f>
+        <v/>
+      </c>
+      <c r="M57">
+        <f>IF(H57=0,"",IF(I57&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L57&lt;&gt;"",N(L57)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
+        <v/>
+      </c>
+      <c r="N57">
+        <f>IF(H57=0,"",I57+ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" t="n">
+        <v>6</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>One correct option</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="G58">
+        <f>COUNTIF(Marks!BC$5:BC$39,1)</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>COUNT(Marks!BC$5:BC$39)</f>
+        <v/>
+      </c>
+      <c r="I58" s="6">
+        <f>IF(H58=0,"",G58/H58)</f>
+        <v/>
+      </c>
+      <c r="J58" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BC$5:BC$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!BC$5:BC$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BC$5:BC$39)))</f>
+        <v/>
+      </c>
+      <c r="K58" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BC$5:BC$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!BC$5:BC$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BC$5:BC$39)))</f>
+        <v/>
+      </c>
+      <c r="L58" s="6">
+        <f>IF(OR(J58="",K58=""),"",J58-K58)</f>
+        <v/>
+      </c>
+      <c r="M58">
+        <f>IF(H58=0,"",IF(I58&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L58&lt;&gt;"",N(L58)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
+        <v/>
+      </c>
+      <c r="N58">
+        <f>IF(H58=0,"",I58+ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>One correct option</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G59">
+        <f>COUNTIF(Marks!BD$5:BD$39,1)</f>
+        <v/>
+      </c>
+      <c r="H59">
+        <f>COUNT(Marks!BD$5:BD$39)</f>
+        <v/>
+      </c>
+      <c r="I59" s="6">
+        <f>IF(H59=0,"",G59/H59)</f>
+        <v/>
+      </c>
+      <c r="J59" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BD$5:BD$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!BD$5:BD$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BD$5:BD$39)))</f>
+        <v/>
+      </c>
+      <c r="K59" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BD$5:BD$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!BD$5:BD$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BD$5:BD$39)))</f>
+        <v/>
+      </c>
+      <c r="L59" s="6">
+        <f>IF(OR(J59="",K59=""),"",J59-K59)</f>
+        <v/>
+      </c>
+      <c r="M59">
+        <f>IF(H59=0,"",IF(I59&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L59&lt;&gt;"",N(L59)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
+        <v/>
+      </c>
+      <c r="N59">
+        <f>IF(H59=0,"",I59+ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -6869,7 +7193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -6884,7 +7208,7 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>IF(SUM(Items!H5:H56)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
+        <f>IF(SUM(Items!H5:H59)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
         <v/>
       </c>
     </row>
@@ -6925,23 +7249,23 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A5,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A5),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A5,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A5),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(B5="","",INDEX(Items!$I$5:$I$56,MATCH(B5,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$I$5:$I$59,MATCH(B5,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D5">
-        <f>IF(B5="","",INDEX(Items!$B$5:$B$56,MATCH(B5,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$B$5:$B$59,MATCH(B5,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E5">
-        <f>IF(B5="","",INDEX(Items!$E$5:$E$56,MATCH(B5,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$E$5:$E$59,MATCH(B5,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F5">
-        <f>IF(B5="","",INDEX(Items!$M$5:$M$56,MATCH(B5,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$M$5:$M$59,MATCH(B5,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -6950,23 +7274,23 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A6,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A6),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A6,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A6),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(B6="","",INDEX(Items!$I$5:$I$56,MATCH(B6,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$I$5:$I$59,MATCH(B6,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IF(B6="","",INDEX(Items!$B$5:$B$56,MATCH(B6,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$B$5:$B$59,MATCH(B6,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E6">
-        <f>IF(B6="","",INDEX(Items!$E$5:$E$56,MATCH(B6,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$E$5:$E$59,MATCH(B6,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IF(B6="","",INDEX(Items!$M$5:$M$56,MATCH(B6,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$M$5:$M$59,MATCH(B6,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -6975,23 +7299,23 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A7,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A7),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A7,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A7),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(B7="","",INDEX(Items!$I$5:$I$56,MATCH(B7,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$I$5:$I$59,MATCH(B7,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D7">
-        <f>IF(B7="","",INDEX(Items!$B$5:$B$56,MATCH(B7,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$B$5:$B$59,MATCH(B7,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E7">
-        <f>IF(B7="","",INDEX(Items!$E$5:$E$56,MATCH(B7,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$E$5:$E$59,MATCH(B7,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F7">
-        <f>IF(B7="","",INDEX(Items!$M$5:$M$56,MATCH(B7,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$M$5:$M$59,MATCH(B7,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7000,23 +7324,23 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A8,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A8),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A8,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A8),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(B8="","",INDEX(Items!$I$5:$I$56,MATCH(B8,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$I$5:$I$59,MATCH(B8,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D8">
-        <f>IF(B8="","",INDEX(Items!$B$5:$B$56,MATCH(B8,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$B$5:$B$59,MATCH(B8,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E8">
-        <f>IF(B8="","",INDEX(Items!$E$5:$E$56,MATCH(B8,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$E$5:$E$59,MATCH(B8,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F8">
-        <f>IF(B8="","",INDEX(Items!$M$5:$M$56,MATCH(B8,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$M$5:$M$59,MATCH(B8,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7025,23 +7349,23 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A9,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A9),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A9,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A9),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(B9="","",INDEX(Items!$I$5:$I$56,MATCH(B9,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$I$5:$I$59,MATCH(B9,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D9">
-        <f>IF(B9="","",INDEX(Items!$B$5:$B$56,MATCH(B9,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$B$5:$B$59,MATCH(B9,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E9">
-        <f>IF(B9="","",INDEX(Items!$E$5:$E$56,MATCH(B9,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$E$5:$E$59,MATCH(B9,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F9">
-        <f>IF(B9="","",INDEX(Items!$M$5:$M$56,MATCH(B9,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$M$5:$M$59,MATCH(B9,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7050,23 +7374,23 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A10,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A10),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A10,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A10),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(B10="","",INDEX(Items!$I$5:$I$56,MATCH(B10,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$I$5:$I$59,MATCH(B10,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D10">
-        <f>IF(B10="","",INDEX(Items!$B$5:$B$56,MATCH(B10,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$B$5:$B$59,MATCH(B10,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E10">
-        <f>IF(B10="","",INDEX(Items!$E$5:$E$56,MATCH(B10,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$E$5:$E$59,MATCH(B10,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F10">
-        <f>IF(B10="","",INDEX(Items!$M$5:$M$56,MATCH(B10,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$M$5:$M$59,MATCH(B10,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7075,23 +7399,23 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A11,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A11),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A11,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A11),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(B11="","",INDEX(Items!$I$5:$I$56,MATCH(B11,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$I$5:$I$59,MATCH(B11,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D11">
-        <f>IF(B11="","",INDEX(Items!$B$5:$B$56,MATCH(B11,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$B$5:$B$59,MATCH(B11,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E11">
-        <f>IF(B11="","",INDEX(Items!$E$5:$E$56,MATCH(B11,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$E$5:$E$59,MATCH(B11,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F11">
-        <f>IF(B11="","",INDEX(Items!$M$5:$M$56,MATCH(B11,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$M$5:$M$59,MATCH(B11,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7100,23 +7424,23 @@
         <v>8</v>
       </c>
       <c r="B12">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A12,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A12),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A12,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A12),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(B12="","",INDEX(Items!$I$5:$I$56,MATCH(B12,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$I$5:$I$59,MATCH(B12,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IF(B12="","",INDEX(Items!$B$5:$B$56,MATCH(B12,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$B$5:$B$59,MATCH(B12,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IF(B12="","",INDEX(Items!$E$5:$E$56,MATCH(B12,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$E$5:$E$59,MATCH(B12,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IF(B12="","",INDEX(Items!$M$5:$M$56,MATCH(B12,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$M$5:$M$59,MATCH(B12,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7125,23 +7449,23 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A13,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A13),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A13,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A13),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(B13="","",INDEX(Items!$I$5:$I$56,MATCH(B13,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$I$5:$I$59,MATCH(B13,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D13">
-        <f>IF(B13="","",INDEX(Items!$B$5:$B$56,MATCH(B13,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$B$5:$B$59,MATCH(B13,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E13">
-        <f>IF(B13="","",INDEX(Items!$E$5:$E$56,MATCH(B13,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$E$5:$E$59,MATCH(B13,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F13">
-        <f>IF(B13="","",INDEX(Items!$M$5:$M$56,MATCH(B13,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$M$5:$M$59,MATCH(B13,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7150,23 +7474,23 @@
         <v>10</v>
       </c>
       <c r="B14">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A14,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A14),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A14,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A14),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(B14="","",INDEX(Items!$I$5:$I$56,MATCH(B14,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$I$5:$I$59,MATCH(B14,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D14">
-        <f>IF(B14="","",INDEX(Items!$B$5:$B$56,MATCH(B14,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$B$5:$B$59,MATCH(B14,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E14">
-        <f>IF(B14="","",INDEX(Items!$E$5:$E$56,MATCH(B14,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$E$5:$E$59,MATCH(B14,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F14">
-        <f>IF(B14="","",INDEX(Items!$M$5:$M$56,MATCH(B14,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$M$5:$M$59,MATCH(B14,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7175,23 +7499,23 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A15,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A15),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A15,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A15),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(B15="","",INDEX(Items!$I$5:$I$56,MATCH(B15,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$I$5:$I$59,MATCH(B15,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D15">
-        <f>IF(B15="","",INDEX(Items!$B$5:$B$56,MATCH(B15,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$B$5:$B$59,MATCH(B15,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E15">
-        <f>IF(B15="","",INDEX(Items!$E$5:$E$56,MATCH(B15,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$E$5:$E$59,MATCH(B15,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F15">
-        <f>IF(B15="","",INDEX(Items!$M$5:$M$56,MATCH(B15,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$M$5:$M$59,MATCH(B15,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7200,23 +7524,23 @@
         <v>12</v>
       </c>
       <c r="B16">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A16,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A16),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A16,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A16),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(B16="","",INDEX(Items!$I$5:$I$56,MATCH(B16,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$I$5:$I$59,MATCH(B16,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D16">
-        <f>IF(B16="","",INDEX(Items!$B$5:$B$56,MATCH(B16,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$B$5:$B$59,MATCH(B16,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E16">
-        <f>IF(B16="","",INDEX(Items!$E$5:$E$56,MATCH(B16,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$E$5:$E$59,MATCH(B16,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F16">
-        <f>IF(B16="","",INDEX(Items!$M$5:$M$56,MATCH(B16,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$M$5:$M$59,MATCH(B16,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7225,23 +7549,23 @@
         <v>13</v>
       </c>
       <c r="B17">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A17,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A17),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A17,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A17),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(B17="","",INDEX(Items!$I$5:$I$56,MATCH(B17,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$I$5:$I$59,MATCH(B17,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D17">
-        <f>IF(B17="","",INDEX(Items!$B$5:$B$56,MATCH(B17,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$B$5:$B$59,MATCH(B17,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E17">
-        <f>IF(B17="","",INDEX(Items!$E$5:$E$56,MATCH(B17,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$E$5:$E$59,MATCH(B17,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F17">
-        <f>IF(B17="","",INDEX(Items!$M$5:$M$56,MATCH(B17,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$M$5:$M$59,MATCH(B17,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7250,23 +7574,23 @@
         <v>14</v>
       </c>
       <c r="B18">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A18,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A18),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A18,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A18),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(B18="","",INDEX(Items!$I$5:$I$56,MATCH(B18,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$I$5:$I$59,MATCH(B18,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D18">
-        <f>IF(B18="","",INDEX(Items!$B$5:$B$56,MATCH(B18,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$B$5:$B$59,MATCH(B18,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E18">
-        <f>IF(B18="","",INDEX(Items!$E$5:$E$56,MATCH(B18,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$E$5:$E$59,MATCH(B18,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F18">
-        <f>IF(B18="","",INDEX(Items!$M$5:$M$56,MATCH(B18,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$M$5:$M$59,MATCH(B18,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7275,23 +7599,23 @@
         <v>15</v>
       </c>
       <c r="B19">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A19,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A19),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A19,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A19),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(B19="","",INDEX(Items!$I$5:$I$56,MATCH(B19,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$I$5:$I$59,MATCH(B19,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D19">
-        <f>IF(B19="","",INDEX(Items!$B$5:$B$56,MATCH(B19,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$B$5:$B$59,MATCH(B19,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E19">
-        <f>IF(B19="","",INDEX(Items!$E$5:$E$56,MATCH(B19,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$E$5:$E$59,MATCH(B19,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F19">
-        <f>IF(B19="","",INDEX(Items!$M$5:$M$56,MATCH(B19,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$M$5:$M$59,MATCH(B19,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7300,23 +7624,23 @@
         <v>16</v>
       </c>
       <c r="B20">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A20,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A20),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A20,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A20),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(B20="","",INDEX(Items!$I$5:$I$56,MATCH(B20,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$I$5:$I$59,MATCH(B20,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D20">
-        <f>IF(B20="","",INDEX(Items!$B$5:$B$56,MATCH(B20,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$B$5:$B$59,MATCH(B20,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E20">
-        <f>IF(B20="","",INDEX(Items!$E$5:$E$56,MATCH(B20,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$E$5:$E$59,MATCH(B20,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F20">
-        <f>IF(B20="","",INDEX(Items!$M$5:$M$56,MATCH(B20,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$M$5:$M$59,MATCH(B20,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7325,23 +7649,23 @@
         <v>17</v>
       </c>
       <c r="B21">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A21,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A21),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A21,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A21),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(B21="","",INDEX(Items!$I$5:$I$56,MATCH(B21,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$I$5:$I$59,MATCH(B21,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D21">
-        <f>IF(B21="","",INDEX(Items!$B$5:$B$56,MATCH(B21,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$B$5:$B$59,MATCH(B21,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E21">
-        <f>IF(B21="","",INDEX(Items!$E$5:$E$56,MATCH(B21,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$E$5:$E$59,MATCH(B21,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F21">
-        <f>IF(B21="","",INDEX(Items!$M$5:$M$56,MATCH(B21,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$M$5:$M$59,MATCH(B21,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7350,23 +7674,23 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A22,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A22),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A22,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A22),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(B22="","",INDEX(Items!$I$5:$I$56,MATCH(B22,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$I$5:$I$59,MATCH(B22,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D22">
-        <f>IF(B22="","",INDEX(Items!$B$5:$B$56,MATCH(B22,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$B$5:$B$59,MATCH(B22,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E22">
-        <f>IF(B22="","",INDEX(Items!$E$5:$E$56,MATCH(B22,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$E$5:$E$59,MATCH(B22,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F22">
-        <f>IF(B22="","",INDEX(Items!$M$5:$M$56,MATCH(B22,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$M$5:$M$59,MATCH(B22,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7375,23 +7699,23 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A23,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A23),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A23,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A23),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(B23="","",INDEX(Items!$I$5:$I$56,MATCH(B23,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$I$5:$I$59,MATCH(B23,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D23">
-        <f>IF(B23="","",INDEX(Items!$B$5:$B$56,MATCH(B23,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$B$5:$B$59,MATCH(B23,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E23">
-        <f>IF(B23="","",INDEX(Items!$E$5:$E$56,MATCH(B23,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$E$5:$E$59,MATCH(B23,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F23">
-        <f>IF(B23="","",INDEX(Items!$M$5:$M$56,MATCH(B23,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$M$5:$M$59,MATCH(B23,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7400,23 +7724,23 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A24,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A24),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A24,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A24),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(B24="","",INDEX(Items!$I$5:$I$56,MATCH(B24,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$I$5:$I$59,MATCH(B24,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D24">
-        <f>IF(B24="","",INDEX(Items!$B$5:$B$56,MATCH(B24,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$B$5:$B$59,MATCH(B24,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E24">
-        <f>IF(B24="","",INDEX(Items!$E$5:$E$56,MATCH(B24,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$E$5:$E$59,MATCH(B24,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F24">
-        <f>IF(B24="","",INDEX(Items!$M$5:$M$56,MATCH(B24,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$M$5:$M$59,MATCH(B24,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7425,23 +7749,23 @@
         <v>21</v>
       </c>
       <c r="B25">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A25,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A25),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A25,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A25),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(B25="","",INDEX(Items!$I$5:$I$56,MATCH(B25,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$I$5:$I$59,MATCH(B25,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D25">
-        <f>IF(B25="","",INDEX(Items!$B$5:$B$56,MATCH(B25,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$B$5:$B$59,MATCH(B25,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E25">
-        <f>IF(B25="","",INDEX(Items!$E$5:$E$56,MATCH(B25,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$E$5:$E$59,MATCH(B25,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F25">
-        <f>IF(B25="","",INDEX(Items!$M$5:$M$56,MATCH(B25,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$M$5:$M$59,MATCH(B25,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7450,23 +7774,23 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A26,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A26),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A26,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A26),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(B26="","",INDEX(Items!$I$5:$I$56,MATCH(B26,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$I$5:$I$59,MATCH(B26,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D26">
-        <f>IF(B26="","",INDEX(Items!$B$5:$B$56,MATCH(B26,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$B$5:$B$59,MATCH(B26,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E26">
-        <f>IF(B26="","",INDEX(Items!$E$5:$E$56,MATCH(B26,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$E$5:$E$59,MATCH(B26,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F26">
-        <f>IF(B26="","",INDEX(Items!$M$5:$M$56,MATCH(B26,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$M$5:$M$59,MATCH(B26,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7475,23 +7799,23 @@
         <v>23</v>
       </c>
       <c r="B27">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A27,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A27),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A27,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A27),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(B27="","",INDEX(Items!$I$5:$I$56,MATCH(B27,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$I$5:$I$59,MATCH(B27,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D27">
-        <f>IF(B27="","",INDEX(Items!$B$5:$B$56,MATCH(B27,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$B$5:$B$59,MATCH(B27,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E27">
-        <f>IF(B27="","",INDEX(Items!$E$5:$E$56,MATCH(B27,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$E$5:$E$59,MATCH(B27,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F27">
-        <f>IF(B27="","",INDEX(Items!$M$5:$M$56,MATCH(B27,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$M$5:$M$59,MATCH(B27,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7500,23 +7824,23 @@
         <v>24</v>
       </c>
       <c r="B28">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A28,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A28),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A28,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A28),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(B28="","",INDEX(Items!$I$5:$I$56,MATCH(B28,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$I$5:$I$59,MATCH(B28,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D28">
-        <f>IF(B28="","",INDEX(Items!$B$5:$B$56,MATCH(B28,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$B$5:$B$59,MATCH(B28,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E28">
-        <f>IF(B28="","",INDEX(Items!$E$5:$E$56,MATCH(B28,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$E$5:$E$59,MATCH(B28,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F28">
-        <f>IF(B28="","",INDEX(Items!$M$5:$M$56,MATCH(B28,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$M$5:$M$59,MATCH(B28,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7525,23 +7849,23 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A29,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A29),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A29,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A29),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(B29="","",INDEX(Items!$I$5:$I$56,MATCH(B29,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$I$5:$I$59,MATCH(B29,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D29">
-        <f>IF(B29="","",INDEX(Items!$B$5:$B$56,MATCH(B29,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$B$5:$B$59,MATCH(B29,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E29">
-        <f>IF(B29="","",INDEX(Items!$E$5:$E$56,MATCH(B29,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$E$5:$E$59,MATCH(B29,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F29">
-        <f>IF(B29="","",INDEX(Items!$M$5:$M$56,MATCH(B29,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$M$5:$M$59,MATCH(B29,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7550,23 +7874,23 @@
         <v>26</v>
       </c>
       <c r="B30">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A30,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A30),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A30,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A30),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(B30="","",INDEX(Items!$I$5:$I$56,MATCH(B30,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$I$5:$I$59,MATCH(B30,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D30">
-        <f>IF(B30="","",INDEX(Items!$B$5:$B$56,MATCH(B30,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$B$5:$B$59,MATCH(B30,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E30">
-        <f>IF(B30="","",INDEX(Items!$E$5:$E$56,MATCH(B30,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$E$5:$E$59,MATCH(B30,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F30">
-        <f>IF(B30="","",INDEX(Items!$M$5:$M$56,MATCH(B30,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$M$5:$M$59,MATCH(B30,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7575,23 +7899,23 @@
         <v>27</v>
       </c>
       <c r="B31">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A31,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A31),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A31,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A31),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(B31="","",INDEX(Items!$I$5:$I$56,MATCH(B31,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$I$5:$I$59,MATCH(B31,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D31">
-        <f>IF(B31="","",INDEX(Items!$B$5:$B$56,MATCH(B31,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$B$5:$B$59,MATCH(B31,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E31">
-        <f>IF(B31="","",INDEX(Items!$E$5:$E$56,MATCH(B31,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$E$5:$E$59,MATCH(B31,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F31">
-        <f>IF(B31="","",INDEX(Items!$M$5:$M$56,MATCH(B31,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$M$5:$M$59,MATCH(B31,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7600,23 +7924,23 @@
         <v>28</v>
       </c>
       <c r="B32">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A32,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A32),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A32,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A32),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(B32="","",INDEX(Items!$I$5:$I$56,MATCH(B32,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$I$5:$I$59,MATCH(B32,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D32">
-        <f>IF(B32="","",INDEX(Items!$B$5:$B$56,MATCH(B32,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$B$5:$B$59,MATCH(B32,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E32">
-        <f>IF(B32="","",INDEX(Items!$E$5:$E$56,MATCH(B32,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$E$5:$E$59,MATCH(B32,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F32">
-        <f>IF(B32="","",INDEX(Items!$M$5:$M$56,MATCH(B32,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$M$5:$M$59,MATCH(B32,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7625,23 +7949,23 @@
         <v>29</v>
       </c>
       <c r="B33">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A33,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A33),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A33,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A33),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(B33="","",INDEX(Items!$I$5:$I$56,MATCH(B33,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$I$5:$I$59,MATCH(B33,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D33">
-        <f>IF(B33="","",INDEX(Items!$B$5:$B$56,MATCH(B33,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$B$5:$B$59,MATCH(B33,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E33">
-        <f>IF(B33="","",INDEX(Items!$E$5:$E$56,MATCH(B33,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$E$5:$E$59,MATCH(B33,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F33">
-        <f>IF(B33="","",INDEX(Items!$M$5:$M$56,MATCH(B33,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$M$5:$M$59,MATCH(B33,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7650,23 +7974,23 @@
         <v>30</v>
       </c>
       <c r="B34">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A34,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A34),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A34,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A34),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(B34="","",INDEX(Items!$I$5:$I$56,MATCH(B34,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$I$5:$I$59,MATCH(B34,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D34">
-        <f>IF(B34="","",INDEX(Items!$B$5:$B$56,MATCH(B34,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$B$5:$B$59,MATCH(B34,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E34">
-        <f>IF(B34="","",INDEX(Items!$E$5:$E$56,MATCH(B34,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$E$5:$E$59,MATCH(B34,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F34">
-        <f>IF(B34="","",INDEX(Items!$M$5:$M$56,MATCH(B34,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$M$5:$M$59,MATCH(B34,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7675,23 +7999,23 @@
         <v>31</v>
       </c>
       <c r="B35">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A35,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A35),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A35,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A35),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(B35="","",INDEX(Items!$I$5:$I$56,MATCH(B35,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$I$5:$I$59,MATCH(B35,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D35">
-        <f>IF(B35="","",INDEX(Items!$B$5:$B$56,MATCH(B35,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$B$5:$B$59,MATCH(B35,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E35">
-        <f>IF(B35="","",INDEX(Items!$E$5:$E$56,MATCH(B35,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$E$5:$E$59,MATCH(B35,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F35">
-        <f>IF(B35="","",INDEX(Items!$M$5:$M$56,MATCH(B35,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$M$5:$M$59,MATCH(B35,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7700,23 +8024,23 @@
         <v>32</v>
       </c>
       <c r="B36">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A36,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A36),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A36,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A36),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(B36="","",INDEX(Items!$I$5:$I$56,MATCH(B36,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$I$5:$I$59,MATCH(B36,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D36">
-        <f>IF(B36="","",INDEX(Items!$B$5:$B$56,MATCH(B36,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$B$5:$B$59,MATCH(B36,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E36">
-        <f>IF(B36="","",INDEX(Items!$E$5:$E$56,MATCH(B36,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$E$5:$E$59,MATCH(B36,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F36">
-        <f>IF(B36="","",INDEX(Items!$M$5:$M$56,MATCH(B36,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$M$5:$M$59,MATCH(B36,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7725,23 +8049,23 @@
         <v>33</v>
       </c>
       <c r="B37">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A37,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A37),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A37,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A37),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(B37="","",INDEX(Items!$I$5:$I$56,MATCH(B37,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$I$5:$I$59,MATCH(B37,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D37">
-        <f>IF(B37="","",INDEX(Items!$B$5:$B$56,MATCH(B37,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$B$5:$B$59,MATCH(B37,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E37">
-        <f>IF(B37="","",INDEX(Items!$E$5:$E$56,MATCH(B37,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$E$5:$E$59,MATCH(B37,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F37">
-        <f>IF(B37="","",INDEX(Items!$M$5:$M$56,MATCH(B37,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$M$5:$M$59,MATCH(B37,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7750,23 +8074,23 @@
         <v>34</v>
       </c>
       <c r="B38">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A38,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A38),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A38,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A38),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(B38="","",INDEX(Items!$I$5:$I$56,MATCH(B38,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$I$5:$I$59,MATCH(B38,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D38">
-        <f>IF(B38="","",INDEX(Items!$B$5:$B$56,MATCH(B38,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$B$5:$B$59,MATCH(B38,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E38">
-        <f>IF(B38="","",INDEX(Items!$E$5:$E$56,MATCH(B38,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$E$5:$E$59,MATCH(B38,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F38">
-        <f>IF(B38="","",INDEX(Items!$M$5:$M$56,MATCH(B38,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$M$5:$M$59,MATCH(B38,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7775,23 +8099,23 @@
         <v>35</v>
       </c>
       <c r="B39">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A39,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A39),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A39,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A39),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(B39="","",INDEX(Items!$I$5:$I$56,MATCH(B39,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$I$5:$I$59,MATCH(B39,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D39">
-        <f>IF(B39="","",INDEX(Items!$B$5:$B$56,MATCH(B39,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$B$5:$B$59,MATCH(B39,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E39">
-        <f>IF(B39="","",INDEX(Items!$E$5:$E$56,MATCH(B39,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$E$5:$E$59,MATCH(B39,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F39">
-        <f>IF(B39="","",INDEX(Items!$M$5:$M$56,MATCH(B39,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$M$5:$M$59,MATCH(B39,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7800,23 +8124,23 @@
         <v>36</v>
       </c>
       <c r="B40">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A40,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A40),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A40,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A40),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C40" s="6">
-        <f>IF(B40="","",INDEX(Items!$I$5:$I$56,MATCH(B40,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$I$5:$I$59,MATCH(B40,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D40">
-        <f>IF(B40="","",INDEX(Items!$B$5:$B$56,MATCH(B40,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$B$5:$B$59,MATCH(B40,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E40">
-        <f>IF(B40="","",INDEX(Items!$E$5:$E$56,MATCH(B40,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$E$5:$E$59,MATCH(B40,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F40">
-        <f>IF(B40="","",INDEX(Items!$M$5:$M$56,MATCH(B40,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$M$5:$M$59,MATCH(B40,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7825,23 +8149,23 @@
         <v>37</v>
       </c>
       <c r="B41">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A41,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A41),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A41,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A41),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C41" s="6">
-        <f>IF(B41="","",INDEX(Items!$I$5:$I$56,MATCH(B41,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B41="","",INDEX(Items!$I$5:$I$59,MATCH(B41,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D41">
-        <f>IF(B41="","",INDEX(Items!$B$5:$B$56,MATCH(B41,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B41="","",INDEX(Items!$B$5:$B$59,MATCH(B41,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E41">
-        <f>IF(B41="","",INDEX(Items!$E$5:$E$56,MATCH(B41,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B41="","",INDEX(Items!$E$5:$E$59,MATCH(B41,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F41">
-        <f>IF(B41="","",INDEX(Items!$M$5:$M$56,MATCH(B41,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B41="","",INDEX(Items!$M$5:$M$59,MATCH(B41,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7850,23 +8174,23 @@
         <v>38</v>
       </c>
       <c r="B42">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A42,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A42),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A42,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A42),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C42" s="6">
-        <f>IF(B42="","",INDEX(Items!$I$5:$I$56,MATCH(B42,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B42="","",INDEX(Items!$I$5:$I$59,MATCH(B42,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D42">
-        <f>IF(B42="","",INDEX(Items!$B$5:$B$56,MATCH(B42,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B42="","",INDEX(Items!$B$5:$B$59,MATCH(B42,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E42">
-        <f>IF(B42="","",INDEX(Items!$E$5:$E$56,MATCH(B42,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B42="","",INDEX(Items!$E$5:$E$59,MATCH(B42,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F42">
-        <f>IF(B42="","",INDEX(Items!$M$5:$M$56,MATCH(B42,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B42="","",INDEX(Items!$M$5:$M$59,MATCH(B42,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7875,23 +8199,23 @@
         <v>39</v>
       </c>
       <c r="B43">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A43,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A43),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A43,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A43),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C43" s="6">
-        <f>IF(B43="","",INDEX(Items!$I$5:$I$56,MATCH(B43,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B43="","",INDEX(Items!$I$5:$I$59,MATCH(B43,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D43">
-        <f>IF(B43="","",INDEX(Items!$B$5:$B$56,MATCH(B43,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B43="","",INDEX(Items!$B$5:$B$59,MATCH(B43,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E43">
-        <f>IF(B43="","",INDEX(Items!$E$5:$E$56,MATCH(B43,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B43="","",INDEX(Items!$E$5:$E$59,MATCH(B43,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F43">
-        <f>IF(B43="","",INDEX(Items!$M$5:$M$56,MATCH(B43,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B43="","",INDEX(Items!$M$5:$M$59,MATCH(B43,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7900,23 +8224,23 @@
         <v>40</v>
       </c>
       <c r="B44">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A44,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A44),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A44,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A44),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C44" s="6">
-        <f>IF(B44="","",INDEX(Items!$I$5:$I$56,MATCH(B44,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B44="","",INDEX(Items!$I$5:$I$59,MATCH(B44,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D44">
-        <f>IF(B44="","",INDEX(Items!$B$5:$B$56,MATCH(B44,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B44="","",INDEX(Items!$B$5:$B$59,MATCH(B44,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E44">
-        <f>IF(B44="","",INDEX(Items!$E$5:$E$56,MATCH(B44,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B44="","",INDEX(Items!$E$5:$E$59,MATCH(B44,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F44">
-        <f>IF(B44="","",INDEX(Items!$M$5:$M$56,MATCH(B44,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B44="","",INDEX(Items!$M$5:$M$59,MATCH(B44,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7925,23 +8249,23 @@
         <v>41</v>
       </c>
       <c r="B45">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A45,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A45),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A45,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A45),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C45" s="6">
-        <f>IF(B45="","",INDEX(Items!$I$5:$I$56,MATCH(B45,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B45="","",INDEX(Items!$I$5:$I$59,MATCH(B45,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D45">
-        <f>IF(B45="","",INDEX(Items!$B$5:$B$56,MATCH(B45,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B45="","",INDEX(Items!$B$5:$B$59,MATCH(B45,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E45">
-        <f>IF(B45="","",INDEX(Items!$E$5:$E$56,MATCH(B45,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B45="","",INDEX(Items!$E$5:$E$59,MATCH(B45,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F45">
-        <f>IF(B45="","",INDEX(Items!$M$5:$M$56,MATCH(B45,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B45="","",INDEX(Items!$M$5:$M$59,MATCH(B45,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7950,23 +8274,23 @@
         <v>42</v>
       </c>
       <c r="B46">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A46,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A46),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A46,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A46),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C46" s="6">
-        <f>IF(B46="","",INDEX(Items!$I$5:$I$56,MATCH(B46,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B46="","",INDEX(Items!$I$5:$I$59,MATCH(B46,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D46">
-        <f>IF(B46="","",INDEX(Items!$B$5:$B$56,MATCH(B46,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B46="","",INDEX(Items!$B$5:$B$59,MATCH(B46,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E46">
-        <f>IF(B46="","",INDEX(Items!$E$5:$E$56,MATCH(B46,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B46="","",INDEX(Items!$E$5:$E$59,MATCH(B46,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F46">
-        <f>IF(B46="","",INDEX(Items!$M$5:$M$56,MATCH(B46,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B46="","",INDEX(Items!$M$5:$M$59,MATCH(B46,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -7975,23 +8299,23 @@
         <v>43</v>
       </c>
       <c r="B47">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A47,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A47),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A47,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A47),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C47" s="6">
-        <f>IF(B47="","",INDEX(Items!$I$5:$I$56,MATCH(B47,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B47="","",INDEX(Items!$I$5:$I$59,MATCH(B47,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D47">
-        <f>IF(B47="","",INDEX(Items!$B$5:$B$56,MATCH(B47,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B47="","",INDEX(Items!$B$5:$B$59,MATCH(B47,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E47">
-        <f>IF(B47="","",INDEX(Items!$E$5:$E$56,MATCH(B47,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B47="","",INDEX(Items!$E$5:$E$59,MATCH(B47,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F47">
-        <f>IF(B47="","",INDEX(Items!$M$5:$M$56,MATCH(B47,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B47="","",INDEX(Items!$M$5:$M$59,MATCH(B47,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -8000,23 +8324,23 @@
         <v>44</v>
       </c>
       <c r="B48">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A48,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A48),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A48,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A48),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C48" s="6">
-        <f>IF(B48="","",INDEX(Items!$I$5:$I$56,MATCH(B48,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B48="","",INDEX(Items!$I$5:$I$59,MATCH(B48,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D48">
-        <f>IF(B48="","",INDEX(Items!$B$5:$B$56,MATCH(B48,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B48="","",INDEX(Items!$B$5:$B$59,MATCH(B48,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E48">
-        <f>IF(B48="","",INDEX(Items!$E$5:$E$56,MATCH(B48,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B48="","",INDEX(Items!$E$5:$E$59,MATCH(B48,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F48">
-        <f>IF(B48="","",INDEX(Items!$M$5:$M$56,MATCH(B48,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B48="","",INDEX(Items!$M$5:$M$59,MATCH(B48,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -8025,23 +8349,23 @@
         <v>45</v>
       </c>
       <c r="B49">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A49,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A49),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A49,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A49),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C49" s="6">
-        <f>IF(B49="","",INDEX(Items!$I$5:$I$56,MATCH(B49,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B49="","",INDEX(Items!$I$5:$I$59,MATCH(B49,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D49">
-        <f>IF(B49="","",INDEX(Items!$B$5:$B$56,MATCH(B49,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B49="","",INDEX(Items!$B$5:$B$59,MATCH(B49,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E49">
-        <f>IF(B49="","",INDEX(Items!$E$5:$E$56,MATCH(B49,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B49="","",INDEX(Items!$E$5:$E$59,MATCH(B49,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F49">
-        <f>IF(B49="","",INDEX(Items!$M$5:$M$56,MATCH(B49,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B49="","",INDEX(Items!$M$5:$M$59,MATCH(B49,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -8050,23 +8374,23 @@
         <v>46</v>
       </c>
       <c r="B50">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A50,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A50),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A50,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A50),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C50" s="6">
-        <f>IF(B50="","",INDEX(Items!$I$5:$I$56,MATCH(B50,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B50="","",INDEX(Items!$I$5:$I$59,MATCH(B50,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D50">
-        <f>IF(B50="","",INDEX(Items!$B$5:$B$56,MATCH(B50,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B50="","",INDEX(Items!$B$5:$B$59,MATCH(B50,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E50">
-        <f>IF(B50="","",INDEX(Items!$E$5:$E$56,MATCH(B50,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B50="","",INDEX(Items!$E$5:$E$59,MATCH(B50,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F50">
-        <f>IF(B50="","",INDEX(Items!$M$5:$M$56,MATCH(B50,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B50="","",INDEX(Items!$M$5:$M$59,MATCH(B50,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -8075,23 +8399,23 @@
         <v>47</v>
       </c>
       <c r="B51">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A51,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A51),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A51,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A51),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C51" s="6">
-        <f>IF(B51="","",INDEX(Items!$I$5:$I$56,MATCH(B51,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B51="","",INDEX(Items!$I$5:$I$59,MATCH(B51,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D51">
-        <f>IF(B51="","",INDEX(Items!$B$5:$B$56,MATCH(B51,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B51="","",INDEX(Items!$B$5:$B$59,MATCH(B51,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E51">
-        <f>IF(B51="","",INDEX(Items!$E$5:$E$56,MATCH(B51,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B51="","",INDEX(Items!$E$5:$E$59,MATCH(B51,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F51">
-        <f>IF(B51="","",INDEX(Items!$M$5:$M$56,MATCH(B51,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B51="","",INDEX(Items!$M$5:$M$59,MATCH(B51,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -8100,23 +8424,23 @@
         <v>48</v>
       </c>
       <c r="B52">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A52,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A52),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A52,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A52),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C52" s="6">
-        <f>IF(B52="","",INDEX(Items!$I$5:$I$56,MATCH(B52,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B52="","",INDEX(Items!$I$5:$I$59,MATCH(B52,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D52">
-        <f>IF(B52="","",INDEX(Items!$B$5:$B$56,MATCH(B52,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B52="","",INDEX(Items!$B$5:$B$59,MATCH(B52,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E52">
-        <f>IF(B52="","",INDEX(Items!$E$5:$E$56,MATCH(B52,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B52="","",INDEX(Items!$E$5:$E$59,MATCH(B52,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F52">
-        <f>IF(B52="","",INDEX(Items!$M$5:$M$56,MATCH(B52,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B52="","",INDEX(Items!$M$5:$M$59,MATCH(B52,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -8125,23 +8449,23 @@
         <v>49</v>
       </c>
       <c r="B53">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A53,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A53),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A53,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A53),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C53" s="6">
-        <f>IF(B53="","",INDEX(Items!$I$5:$I$56,MATCH(B53,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B53="","",INDEX(Items!$I$5:$I$59,MATCH(B53,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D53">
-        <f>IF(B53="","",INDEX(Items!$B$5:$B$56,MATCH(B53,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B53="","",INDEX(Items!$B$5:$B$59,MATCH(B53,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E53">
-        <f>IF(B53="","",INDEX(Items!$E$5:$E$56,MATCH(B53,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B53="","",INDEX(Items!$E$5:$E$59,MATCH(B53,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F53">
-        <f>IF(B53="","",INDEX(Items!$M$5:$M$56,MATCH(B53,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B53="","",INDEX(Items!$M$5:$M$59,MATCH(B53,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -8150,23 +8474,23 @@
         <v>50</v>
       </c>
       <c r="B54">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A54,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A54),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A54,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A54),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C54" s="6">
-        <f>IF(B54="","",INDEX(Items!$I$5:$I$56,MATCH(B54,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B54="","",INDEX(Items!$I$5:$I$59,MATCH(B54,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D54">
-        <f>IF(B54="","",INDEX(Items!$B$5:$B$56,MATCH(B54,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B54="","",INDEX(Items!$B$5:$B$59,MATCH(B54,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E54">
-        <f>IF(B54="","",INDEX(Items!$E$5:$E$56,MATCH(B54,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B54="","",INDEX(Items!$E$5:$E$59,MATCH(B54,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F54">
-        <f>IF(B54="","",INDEX(Items!$M$5:$M$56,MATCH(B54,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B54="","",INDEX(Items!$M$5:$M$59,MATCH(B54,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -8175,23 +8499,23 @@
         <v>51</v>
       </c>
       <c r="B55">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A55,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A55),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A55,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A55),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C55" s="6">
-        <f>IF(B55="","",INDEX(Items!$I$5:$I$56,MATCH(B55,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B55="","",INDEX(Items!$I$5:$I$59,MATCH(B55,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D55">
-        <f>IF(B55="","",INDEX(Items!$B$5:$B$56,MATCH(B55,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B55="","",INDEX(Items!$B$5:$B$59,MATCH(B55,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E55">
-        <f>IF(B55="","",INDEX(Items!$E$5:$E$56,MATCH(B55,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B55="","",INDEX(Items!$E$5:$E$59,MATCH(B55,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F55">
-        <f>IF(B55="","",INDEX(Items!$M$5:$M$56,MATCH(B55,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B55="","",INDEX(Items!$M$5:$M$59,MATCH(B55,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -8200,23 +8524,98 @@
         <v>52</v>
       </c>
       <c r="B56">
-        <f>IF(COUNT(Items!$N$5:$N$56)&lt;A56,"",INDEX(Items!$A$5:$A$56,MATCH(SMALL(Items!$N$5:$N$56,A56),Items!$N$5:$N$56,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A56,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A56),Items!$N$5:$N$59,0)))</f>
         <v/>
       </c>
       <c r="C56" s="6">
-        <f>IF(B56="","",INDEX(Items!$I$5:$I$56,MATCH(B56,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B56="","",INDEX(Items!$I$5:$I$59,MATCH(B56,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="D56">
-        <f>IF(B56="","",INDEX(Items!$B$5:$B$56,MATCH(B56,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B56="","",INDEX(Items!$B$5:$B$59,MATCH(B56,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="E56">
-        <f>IF(B56="","",INDEX(Items!$E$5:$E$56,MATCH(B56,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B56="","",INDEX(Items!$E$5:$E$59,MATCH(B56,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
       <c r="F56">
-        <f>IF(B56="","",INDEX(Items!$M$5:$M$56,MATCH(B56,Items!$A$5:$A$56,0)))</f>
+        <f>IF(B56="","",INDEX(Items!$M$5:$M$59,MATCH(B56,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57">
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A57,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A57),Items!$N$5:$N$59,0)))</f>
+        <v/>
+      </c>
+      <c r="C57" s="6">
+        <f>IF(B57="","",INDEX(Items!$I$5:$I$59,MATCH(B57,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>IF(B57="","",INDEX(Items!$B$5:$B$59,MATCH(B57,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>IF(B57="","",INDEX(Items!$E$5:$E$59,MATCH(B57,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>IF(B57="","",INDEX(Items!$M$5:$M$59,MATCH(B57,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58">
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A58,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A58),Items!$N$5:$N$59,0)))</f>
+        <v/>
+      </c>
+      <c r="C58" s="6">
+        <f>IF(B58="","",INDEX(Items!$I$5:$I$59,MATCH(B58,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>IF(B58="","",INDEX(Items!$B$5:$B$59,MATCH(B58,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>IF(B58="","",INDEX(Items!$E$5:$E$59,MATCH(B58,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>IF(B58="","",INDEX(Items!$M$5:$M$59,MATCH(B58,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59">
+        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A59,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A59),Items!$N$5:$N$59,0)))</f>
+        <v/>
+      </c>
+      <c r="C59" s="6">
+        <f>IF(B59="","",INDEX(Items!$I$5:$I$59,MATCH(B59,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>IF(B59="","",INDEX(Items!$B$5:$B$59,MATCH(B59,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>IF(B59="","",INDEX(Items!$E$5:$E$59,MATCH(B59,Items!$A$5:$A$59,0)))</f>
+        <v/>
+      </c>
+      <c r="F59">
+        <f>IF(B59="","",INDEX(Items!$M$5:$M$59,MATCH(B59,Items!$A$5:$A$59,0)))</f>
         <v/>
       </c>
     </row>
@@ -8278,11 +8677,11 @@
         </is>
       </c>
       <c r="C5">
-        <f>COUNTIF(Items!$E$5:$E$56,A5)</f>
+        <f>COUNTIF(Items!$E$5:$E$59,A5)</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$56=A5)*Items!$H$5:$H$56)=0,"",SUMPRODUCT((Items!$E$5:$E$56=A5)*Items!$G$5:$G$56)/SUMPRODUCT((Items!$E$5:$E$56=A5)*Items!$H$5:$H$56))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$59=A5)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$E$5:$E$59=A5)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$E$5:$E$59=A5)*Items!$H$5:$H$59))</f>
         <v/>
       </c>
     </row>
@@ -8298,11 +8697,11 @@
         </is>
       </c>
       <c r="C6">
-        <f>COUNTIF(Items!$E$5:$E$56,A6)</f>
+        <f>COUNTIF(Items!$E$5:$E$59,A6)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$56=A6)*Items!$H$5:$H$56)=0,"",SUMPRODUCT((Items!$E$5:$E$56=A6)*Items!$G$5:$G$56)/SUMPRODUCT((Items!$E$5:$E$56=A6)*Items!$H$5:$H$56))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$59=A6)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$E$5:$E$59=A6)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$E$5:$E$59=A6)*Items!$H$5:$H$59))</f>
         <v/>
       </c>
     </row>
@@ -8318,11 +8717,11 @@
         </is>
       </c>
       <c r="C7">
-        <f>COUNTIF(Items!$E$5:$E$56,A7)</f>
+        <f>COUNTIF(Items!$E$5:$E$59,A7)</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$56=A7)*Items!$H$5:$H$56)=0,"",SUMPRODUCT((Items!$E$5:$E$56=A7)*Items!$G$5:$G$56)/SUMPRODUCT((Items!$E$5:$E$56=A7)*Items!$H$5:$H$56))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$59=A7)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$E$5:$E$59=A7)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$E$5:$E$59=A7)*Items!$H$5:$H$59))</f>
         <v/>
       </c>
     </row>
@@ -8336,11 +8735,11 @@
         </is>
       </c>
       <c r="C8">
-        <f>COUNTIF(Items!$B$5:$B$56,A8)</f>
+        <f>COUNTIF(Items!$B$5:$B$59,A8)</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$56=A8)*Items!$H$5:$H$56)=0,"",SUMPRODUCT((Items!$B$5:$B$56=A8)*Items!$G$5:$G$56)/SUMPRODUCT((Items!$B$5:$B$56=A8)*Items!$H$5:$H$56))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A8)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A8)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A8)*Items!$H$5:$H$59))</f>
         <v/>
       </c>
     </row>
@@ -8354,11 +8753,11 @@
         </is>
       </c>
       <c r="C9">
-        <f>COUNTIF(Items!$B$5:$B$56,A9)</f>
+        <f>COUNTIF(Items!$B$5:$B$59,A9)</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$56=A9)*Items!$H$5:$H$56)=0,"",SUMPRODUCT((Items!$B$5:$B$56=A9)*Items!$G$5:$G$56)/SUMPRODUCT((Items!$B$5:$B$56=A9)*Items!$H$5:$H$56))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A9)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A9)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A9)*Items!$H$5:$H$59))</f>
         <v/>
       </c>
     </row>
@@ -8372,11 +8771,11 @@
         </is>
       </c>
       <c r="C10">
-        <f>COUNTIF(Items!$B$5:$B$56,A10)</f>
+        <f>COUNTIF(Items!$B$5:$B$59,A10)</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$56=A10)*Items!$H$5:$H$56)=0,"",SUMPRODUCT((Items!$B$5:$B$56=A10)*Items!$G$5:$G$56)/SUMPRODUCT((Items!$B$5:$B$56=A10)*Items!$H$5:$H$56))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A10)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A10)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A10)*Items!$H$5:$H$59))</f>
         <v/>
       </c>
     </row>
@@ -8390,11 +8789,11 @@
         </is>
       </c>
       <c r="C11">
-        <f>COUNTIF(Items!$B$5:$B$56,A11)</f>
+        <f>COUNTIF(Items!$B$5:$B$59,A11)</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$56=A11)*Items!$H$5:$H$56)=0,"",SUMPRODUCT((Items!$B$5:$B$56=A11)*Items!$G$5:$G$56)/SUMPRODUCT((Items!$B$5:$B$56=A11)*Items!$H$5:$H$56))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A11)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A11)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A11)*Items!$H$5:$H$59))</f>
         <v/>
       </c>
     </row>
@@ -8408,11 +8807,11 @@
         </is>
       </c>
       <c r="C12">
-        <f>COUNTIF(Items!$B$5:$B$56,A12)</f>
+        <f>COUNTIF(Items!$B$5:$B$59,A12)</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$56=A12)*Items!$H$5:$H$56)=0,"",SUMPRODUCT((Items!$B$5:$B$56=A12)*Items!$G$5:$G$56)/SUMPRODUCT((Items!$B$5:$B$56=A12)*Items!$H$5:$H$56))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A12)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A12)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A12)*Items!$H$5:$H$59))</f>
         <v/>
       </c>
     </row>
@@ -8426,11 +8825,11 @@
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(Items!$B$5:$B$56,A13)</f>
+        <f>COUNTIF(Items!$B$5:$B$59,A13)</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$56=A13)*Items!$H$5:$H$56)=0,"",SUMPRODUCT((Items!$B$5:$B$56=A13)*Items!$G$5:$G$56)/SUMPRODUCT((Items!$B$5:$B$56=A13)*Items!$H$5:$H$56))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A13)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A13)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A13)*Items!$H$5:$H$59))</f>
         <v/>
       </c>
     </row>
@@ -8482,15 +8881,15 @@
         <v>1</v>
       </c>
       <c r="B5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$5:$BA$5))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$5:$BA$5=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$5:$BA$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$5:$BA$5))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$5:$BA$5=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$5:$BA$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$5:$BA$5))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$5:$BA$5=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$5:$BA$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
         <v/>
       </c>
     </row>
@@ -8499,15 +8898,15 @@
         <v>2</v>
       </c>
       <c r="B6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$6:$BA$6))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$6:$BA$6=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$6:$BA$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$6:$BA$6))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$6:$BA$6=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$6:$BA$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$6:$BA$6))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$6:$BA$6=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$6:$BA$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
         <v/>
       </c>
     </row>
@@ -8516,15 +8915,15 @@
         <v>3</v>
       </c>
       <c r="B7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$7:$BA$7))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$7:$BA$7=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$7:$BA$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$7:$BA$7))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$7:$BA$7=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$7:$BA$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$7:$BA$7))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$7:$BA$7=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$7:$BA$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
         <v/>
       </c>
     </row>
@@ -8533,15 +8932,15 @@
         <v>4</v>
       </c>
       <c r="B8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$8:$BA$8))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$8:$BA$8=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$8:$BA$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$8:$BA$8))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$8:$BA$8=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$8:$BA$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$8:$BA$8))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$8:$BA$8=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$8:$BA$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
         <v/>
       </c>
     </row>
@@ -8550,15 +8949,15 @@
         <v>5</v>
       </c>
       <c r="B9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$9:$BA$9))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$9:$BA$9=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$9:$BA$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$9:$BA$9))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$9:$BA$9=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$9:$BA$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$9:$BA$9))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$9:$BA$9=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$9:$BA$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
         <v/>
       </c>
     </row>
@@ -8567,15 +8966,15 @@
         <v>6</v>
       </c>
       <c r="B10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$10:$BA$10))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$10:$BA$10=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$10:$BA$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$10:$BA$10))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$10:$BA$10=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$10:$BA$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$10:$BA$10))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$10:$BA$10=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$10:$BA$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
         <v/>
       </c>
     </row>
@@ -8584,15 +8983,15 @@
         <v>7</v>
       </c>
       <c r="B11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$11:$BA$11))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$11:$BA$11=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$11:$BA$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$11:$BA$11))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$11:$BA$11=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$11:$BA$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$11:$BA$11))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$11:$BA$11=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$11:$BA$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
         <v/>
       </c>
     </row>
@@ -8601,15 +9000,15 @@
         <v>8</v>
       </c>
       <c r="B12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$12:$BA$12))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$12:$BA$12=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$12:$BA$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$12:$BA$12))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$12:$BA$12=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$12:$BA$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$12:$BA$12))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$12:$BA$12=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$12:$BA$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
         <v/>
       </c>
     </row>
@@ -8618,15 +9017,15 @@
         <v>9</v>
       </c>
       <c r="B13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$13:$BA$13))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$13:$BA$13=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$13:$BA$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$13:$BA$13))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$13:$BA$13=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$13:$BA$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$13:$BA$13))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$13:$BA$13=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$13:$BA$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
         <v/>
       </c>
     </row>
@@ -8635,15 +9034,15 @@
         <v>10</v>
       </c>
       <c r="B14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$14:$BA$14))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$14:$BA$14=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$14:$BA$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$14:$BA$14))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$14:$BA$14=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$14:$BA$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$14:$BA$14))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$14:$BA$14=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$14:$BA$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
         <v/>
       </c>
     </row>
@@ -8652,15 +9051,15 @@
         <v>11</v>
       </c>
       <c r="B15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$15:$BA$15))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$15:$BA$15=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$15:$BA$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$15:$BA$15))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$15:$BA$15=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$15:$BA$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
         <v/>
       </c>
       <c r="D15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$15:$BA$15))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$15:$BA$15=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$15:$BA$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
         <v/>
       </c>
     </row>
@@ -8669,15 +9068,15 @@
         <v>12</v>
       </c>
       <c r="B16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$16:$BA$16))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$16:$BA$16=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$16:$BA$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$16:$BA$16))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$16:$BA$16=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$16:$BA$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
         <v/>
       </c>
       <c r="D16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$16:$BA$16))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$16:$BA$16=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$16:$BA$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
         <v/>
       </c>
     </row>
@@ -8686,15 +9085,15 @@
         <v>13</v>
       </c>
       <c r="B17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$17:$BA$17))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$17:$BA$17=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$17:$BA$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$17:$BA$17))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$17:$BA$17=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$17:$BA$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
         <v/>
       </c>
       <c r="D17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$17:$BA$17))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$17:$BA$17=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$17:$BA$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
         <v/>
       </c>
     </row>
@@ -8703,15 +9102,15 @@
         <v>14</v>
       </c>
       <c r="B18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$18:$BA$18))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$18:$BA$18=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$18:$BA$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$18:$BA$18))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$18:$BA$18=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$18:$BA$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
         <v/>
       </c>
       <c r="D18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$18:$BA$18))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$18:$BA$18=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$18:$BA$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
         <v/>
       </c>
     </row>
@@ -8720,15 +9119,15 @@
         <v>15</v>
       </c>
       <c r="B19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$19:$BA$19))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$19:$BA$19=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$19:$BA$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$19:$BA$19))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$19:$BA$19=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$19:$BA$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$19:$BA$19))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$19:$BA$19=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$19:$BA$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
         <v/>
       </c>
     </row>
@@ -8737,15 +9136,15 @@
         <v>16</v>
       </c>
       <c r="B20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$20:$BA$20))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$20:$BA$20=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$20:$BA$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$20:$BA$20))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$20:$BA$20=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$20:$BA$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
         <v/>
       </c>
       <c r="D20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$20:$BA$20))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$20:$BA$20=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$20:$BA$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
         <v/>
       </c>
     </row>
@@ -8754,15 +9153,15 @@
         <v>17</v>
       </c>
       <c r="B21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$21:$BA$21))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$21:$BA$21=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$21:$BA$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$21:$BA$21))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$21:$BA$21=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$21:$BA$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
         <v/>
       </c>
       <c r="D21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$21:$BA$21))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$21:$BA$21=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$21:$BA$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
         <v/>
       </c>
     </row>
@@ -8771,15 +9170,15 @@
         <v>18</v>
       </c>
       <c r="B22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$22:$BA$22))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$22:$BA$22=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$22:$BA$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$22:$BA$22))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$22:$BA$22=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$22:$BA$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
         <v/>
       </c>
       <c r="D22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$22:$BA$22))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$22:$BA$22=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$22:$BA$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
         <v/>
       </c>
     </row>
@@ -8788,15 +9187,15 @@
         <v>19</v>
       </c>
       <c r="B23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$23:$BA$23))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$23:$BA$23=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$23:$BA$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$23:$BA$23))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$23:$BA$23=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$23:$BA$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
         <v/>
       </c>
       <c r="D23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$23:$BA$23))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$23:$BA$23=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$23:$BA$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
         <v/>
       </c>
     </row>
@@ -8805,15 +9204,15 @@
         <v>20</v>
       </c>
       <c r="B24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$24:$BA$24))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$24:$BA$24=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$24:$BA$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$24:$BA$24))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$24:$BA$24=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$24:$BA$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$24:$BA$24))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$24:$BA$24=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$24:$BA$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
         <v/>
       </c>
     </row>
@@ -8822,15 +9221,15 @@
         <v>21</v>
       </c>
       <c r="B25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$25:$BA$25))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$25:$BA$25=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$25:$BA$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$25:$BA$25))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$25:$BA$25=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$25:$BA$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$25:$BA$25))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$25:$BA$25=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$25:$BA$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
         <v/>
       </c>
     </row>
@@ -8839,15 +9238,15 @@
         <v>22</v>
       </c>
       <c r="B26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$26:$BA$26))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$26:$BA$26=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$26:$BA$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$26:$BA$26))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$26:$BA$26=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$26:$BA$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$26:$BA$26))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$26:$BA$26=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$26:$BA$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
         <v/>
       </c>
     </row>
@@ -8856,15 +9255,15 @@
         <v>23</v>
       </c>
       <c r="B27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$27:$BA$27))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$27:$BA$27=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$27:$BA$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$27:$BA$27))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$27:$BA$27=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$27:$BA$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$27:$BA$27))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$27:$BA$27=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$27:$BA$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
         <v/>
       </c>
     </row>
@@ -8873,15 +9272,15 @@
         <v>24</v>
       </c>
       <c r="B28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$28:$BA$28))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$28:$BA$28=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$28:$BA$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$28:$BA$28))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$28:$BA$28=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$28:$BA$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$28:$BA$28))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$28:$BA$28=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$28:$BA$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
         <v/>
       </c>
     </row>
@@ -8890,15 +9289,15 @@
         <v>25</v>
       </c>
       <c r="B29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$29:$BA$29))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$29:$BA$29=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$29:$BA$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$29:$BA$29))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$29:$BA$29=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$29:$BA$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$29:$BA$29))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$29:$BA$29=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$29:$BA$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
         <v/>
       </c>
     </row>
@@ -8907,15 +9306,15 @@
         <v>26</v>
       </c>
       <c r="B30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$30:$BA$30))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$30:$BA$30=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$30:$BA$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$30:$BA$30))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$30:$BA$30=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$30:$BA$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$30:$BA$30))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$30:$BA$30=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$30:$BA$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
         <v/>
       </c>
     </row>
@@ -8924,15 +9323,15 @@
         <v>27</v>
       </c>
       <c r="B31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$31:$BA$31))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$31:$BA$31=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$31:$BA$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$31:$BA$31))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$31:$BA$31=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$31:$BA$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$31:$BA$31))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$31:$BA$31=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$31:$BA$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
         <v/>
       </c>
     </row>
@@ -8941,15 +9340,15 @@
         <v>28</v>
       </c>
       <c r="B32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$32:$BA$32))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$32:$BA$32=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$32:$BA$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$32:$BA$32))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$32:$BA$32=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$32:$BA$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$32:$BA$32))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$32:$BA$32=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$32:$BA$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
         <v/>
       </c>
     </row>
@@ -8958,15 +9357,15 @@
         <v>29</v>
       </c>
       <c r="B33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$33:$BA$33))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$33:$BA$33=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$33:$BA$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$33:$BA$33))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$33:$BA$33=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$33:$BA$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$33:$BA$33))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$33:$BA$33=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$33:$BA$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
         <v/>
       </c>
     </row>
@@ -8975,15 +9374,15 @@
         <v>30</v>
       </c>
       <c r="B34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$34:$BA$34))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$34:$BA$34=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$34:$BA$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$34:$BA$34))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$34:$BA$34=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$34:$BA$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$34:$BA$34))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$34:$BA$34=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$34:$BA$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
         <v/>
       </c>
     </row>
@@ -8992,15 +9391,15 @@
         <v>31</v>
       </c>
       <c r="B35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$35:$BA$35))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$35:$BA$35=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$35:$BA$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$35:$BA$35))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$35:$BA$35=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$35:$BA$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$35:$BA$35))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$35:$BA$35=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$35:$BA$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
         <v/>
       </c>
     </row>
@@ -9009,15 +9408,15 @@
         <v>32</v>
       </c>
       <c r="B36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$36:$BA$36))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$36:$BA$36=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$36:$BA$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$36:$BA$36))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$36:$BA$36=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$36:$BA$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$36:$BA$36))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$36:$BA$36=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$36:$BA$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
         <v/>
       </c>
     </row>
@@ -9026,15 +9425,15 @@
         <v>33</v>
       </c>
       <c r="B37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$37:$BA$37))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$37:$BA$37=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$37:$BA$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$37:$BA$37))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$37:$BA$37=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$37:$BA$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$37:$BA$37))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$37:$BA$37=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$37:$BA$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
         <v/>
       </c>
     </row>
@@ -9043,15 +9442,15 @@
         <v>34</v>
       </c>
       <c r="B38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$38:$BA$38))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$38:$BA$38=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$38:$BA$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$38:$BA$38))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$38:$BA$38=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$38:$BA$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$38:$BA$38))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$38:$BA$38=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$38:$BA$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
         <v/>
       </c>
     </row>
@@ -9060,15 +9459,15 @@
         <v>35</v>
       </c>
       <c r="B39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$39:$BA$39))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*(Marks!$B$39:$BA$39=1))/SUMPRODUCT((Marks!$B$3:$BA$3=B$4)*ISNUMBER(Marks!$B$39:$BA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$39:$BA$39))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*(Marks!$B$39:$BA$39=1))/SUMPRODUCT((Marks!$B$3:$BA$3=C$4)*ISNUMBER(Marks!$B$39:$BA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
         <v/>
       </c>
       <c r="D39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$39:$BA$39))=0,"",SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*(Marks!$B$39:$BA$39=1))/SUMPRODUCT((Marks!$B$3:$BA$3=D$4)*ISNUMBER(Marks!$B$39:$BA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
         <v/>
       </c>
     </row>

--- a/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discussion" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tags" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seats" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratings" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -81,6 +84,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9474,4 +9478,1508 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Step one: each part's rating beside its score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Type each seat's ratings, 1 to 4, from the answer sheet; the rates on the right are computed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 1</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 2</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 3</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 4</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 5</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 6</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 1</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 2</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 3</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 4</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 5</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="I5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <v/>
+      </c>
+      <c r="J5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <v/>
+      </c>
+      <c r="K5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <v/>
+      </c>
+      <c r="L5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <v/>
+      </c>
+      <c r="M5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <v/>
+      </c>
+      <c r="N5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="I6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <v/>
+      </c>
+      <c r="J6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <v/>
+      </c>
+      <c r="K6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <v/>
+      </c>
+      <c r="L6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <v/>
+      </c>
+      <c r="M6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <v/>
+      </c>
+      <c r="N6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="I7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <v/>
+      </c>
+      <c r="J7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <v/>
+      </c>
+      <c r="K7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <v/>
+      </c>
+      <c r="L7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <v/>
+      </c>
+      <c r="M7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <v/>
+      </c>
+      <c r="N7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="I8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <v/>
+      </c>
+      <c r="K8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <v/>
+      </c>
+      <c r="L8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <v/>
+      </c>
+      <c r="M8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <v/>
+      </c>
+      <c r="N8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="I9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <v/>
+      </c>
+      <c r="K9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <v/>
+      </c>
+      <c r="L9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <v/>
+      </c>
+      <c r="M9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <v/>
+      </c>
+      <c r="N9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="I10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <v/>
+      </c>
+      <c r="K10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <v/>
+      </c>
+      <c r="L10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <v/>
+      </c>
+      <c r="N10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="I11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <v/>
+      </c>
+      <c r="K11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <v/>
+      </c>
+      <c r="L11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <v/>
+      </c>
+      <c r="N11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="I12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <v/>
+      </c>
+      <c r="K12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <v/>
+      </c>
+      <c r="L12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <v/>
+      </c>
+      <c r="N12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="I13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <v/>
+      </c>
+      <c r="K13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <v/>
+      </c>
+      <c r="L13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <v/>
+      </c>
+      <c r="M13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <v/>
+      </c>
+      <c r="N13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="I14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <v/>
+      </c>
+      <c r="K14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <v/>
+      </c>
+      <c r="L14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <v/>
+      </c>
+      <c r="M14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <v/>
+      </c>
+      <c r="N14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="I15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <v/>
+      </c>
+      <c r="J15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <v/>
+      </c>
+      <c r="K15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <v/>
+      </c>
+      <c r="L15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <v/>
+      </c>
+      <c r="M15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <v/>
+      </c>
+      <c r="N15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="I16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <v/>
+      </c>
+      <c r="J16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <v/>
+      </c>
+      <c r="K16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <v/>
+      </c>
+      <c r="L16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <v/>
+      </c>
+      <c r="M16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <v/>
+      </c>
+      <c r="N16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="I17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <v/>
+      </c>
+      <c r="J17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <v/>
+      </c>
+      <c r="K17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <v/>
+      </c>
+      <c r="L17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <v/>
+      </c>
+      <c r="M17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <v/>
+      </c>
+      <c r="N17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="I18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <v/>
+      </c>
+      <c r="J18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <v/>
+      </c>
+      <c r="K18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <v/>
+      </c>
+      <c r="L18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <v/>
+      </c>
+      <c r="M18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <v/>
+      </c>
+      <c r="N18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="I19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <v/>
+      </c>
+      <c r="J19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <v/>
+      </c>
+      <c r="K19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <v/>
+      </c>
+      <c r="L19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <v/>
+      </c>
+      <c r="M19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <v/>
+      </c>
+      <c r="N19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="I20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <v/>
+      </c>
+      <c r="K20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <v/>
+      </c>
+      <c r="L20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <v/>
+      </c>
+      <c r="M20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <v/>
+      </c>
+      <c r="N20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="I21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <v/>
+      </c>
+      <c r="K21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <v/>
+      </c>
+      <c r="L21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <v/>
+      </c>
+      <c r="M21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <v/>
+      </c>
+      <c r="N21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="I22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <v/>
+      </c>
+      <c r="K22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <v/>
+      </c>
+      <c r="L22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <v/>
+      </c>
+      <c r="M22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <v/>
+      </c>
+      <c r="N22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="I23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <v/>
+      </c>
+      <c r="K23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <v/>
+      </c>
+      <c r="L23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <v/>
+      </c>
+      <c r="M23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <v/>
+      </c>
+      <c r="N23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="I24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <v/>
+      </c>
+      <c r="K24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <v/>
+      </c>
+      <c r="L24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <v/>
+      </c>
+      <c r="M24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <v/>
+      </c>
+      <c r="N24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="I25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <v/>
+      </c>
+      <c r="K25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <v/>
+      </c>
+      <c r="L25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <v/>
+      </c>
+      <c r="M25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <v/>
+      </c>
+      <c r="N25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="I26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <v/>
+      </c>
+      <c r="K26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <v/>
+      </c>
+      <c r="L26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <v/>
+      </c>
+      <c r="M26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <v/>
+      </c>
+      <c r="N26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="I27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <v/>
+      </c>
+      <c r="K27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <v/>
+      </c>
+      <c r="L27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <v/>
+      </c>
+      <c r="M27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <v/>
+      </c>
+      <c r="N27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="I28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <v/>
+      </c>
+      <c r="K28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <v/>
+      </c>
+      <c r="L28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <v/>
+      </c>
+      <c r="M28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <v/>
+      </c>
+      <c r="N28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="I29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <v/>
+      </c>
+      <c r="K29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <v/>
+      </c>
+      <c r="L29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <v/>
+      </c>
+      <c r="M29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <v/>
+      </c>
+      <c r="N29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="I30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <v/>
+      </c>
+      <c r="J30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <v/>
+      </c>
+      <c r="K30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <v/>
+      </c>
+      <c r="L30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <v/>
+      </c>
+      <c r="M30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <v/>
+      </c>
+      <c r="N30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="I31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <v/>
+      </c>
+      <c r="J31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <v/>
+      </c>
+      <c r="K31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <v/>
+      </c>
+      <c r="L31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <v/>
+      </c>
+      <c r="M31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <v/>
+      </c>
+      <c r="N31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="I32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <v/>
+      </c>
+      <c r="J32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <v/>
+      </c>
+      <c r="K32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <v/>
+      </c>
+      <c r="L32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <v/>
+      </c>
+      <c r="M32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <v/>
+      </c>
+      <c r="N32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="I33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <v/>
+      </c>
+      <c r="J33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <v/>
+      </c>
+      <c r="K33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <v/>
+      </c>
+      <c r="L33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <v/>
+      </c>
+      <c r="M33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <v/>
+      </c>
+      <c r="N33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="I34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <v/>
+      </c>
+      <c r="J34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <v/>
+      </c>
+      <c r="K34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <v/>
+      </c>
+      <c r="L34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <v/>
+      </c>
+      <c r="M34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <v/>
+      </c>
+      <c r="N34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="I35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <v/>
+      </c>
+      <c r="J35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <v/>
+      </c>
+      <c r="K35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <v/>
+      </c>
+      <c r="L35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <v/>
+      </c>
+      <c r="M35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <v/>
+      </c>
+      <c r="N35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="I36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <v/>
+      </c>
+      <c r="J36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <v/>
+      </c>
+      <c r="K36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <v/>
+      </c>
+      <c r="L36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <v/>
+      </c>
+      <c r="M36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <v/>
+      </c>
+      <c r="N36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="I37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <v/>
+      </c>
+      <c r="J37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <v/>
+      </c>
+      <c r="K37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <v/>
+      </c>
+      <c r="L37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <v/>
+      </c>
+      <c r="M37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <v/>
+      </c>
+      <c r="N37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="I38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <v/>
+      </c>
+      <c r="J38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <v/>
+      </c>
+      <c r="K38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <v/>
+      </c>
+      <c r="L38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <v/>
+      </c>
+      <c r="M38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <v/>
+      </c>
+      <c r="N38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="I39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <v/>
+      </c>
+      <c r="J39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <v/>
+      </c>
+      <c r="K39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <v/>
+      </c>
+      <c r="L39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <v/>
+      </c>
+      <c r="M39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <v/>
+      </c>
+      <c r="N39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>The room</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Mean rating</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Right rate</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Rated 3 or 4, under half right</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Part 1. The week's rules, cold</t>
+        </is>
+      </c>
+      <c r="B43" s="7">
+        <f>IF(COUNT(B5:B39)=0,"",AVERAGE(B5:B39))</f>
+        <v/>
+      </c>
+      <c r="C43" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(1,Tags!$A$5:$A$13,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D43">
+        <f>SUMPRODUCT((B5:B39&gt;=3)*ISNUMBER(I5:I39)*(I5:I39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Part 2. Asking the warehouse</t>
+        </is>
+      </c>
+      <c r="B44" s="7">
+        <f>IF(COUNT(C5:C39)=0,"",AVERAGE(C5:C39))</f>
+        <v/>
+      </c>
+      <c r="C44" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(2,Tags!$A$5:$A$13,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D44">
+        <f>SUMPRODUCT((C5:C39&gt;=3)*ISNUMBER(J5:J39)*(J5:J39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Part 3. Joins that keep their rows</t>
+        </is>
+      </c>
+      <c r="B45" s="7">
+        <f>IF(COUNT(D5:D39)=0,"",AVERAGE(D5:D39))</f>
+        <v/>
+      </c>
+      <c r="C45" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(3,Tags!$A$5:$A$13,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D45">
+        <f>SUMPRODUCT((D5:D39&gt;=3)*ISNUMBER(K5:K39)*(K5:K39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Part 4. Windows: rank, lag and running totals</t>
+        </is>
+      </c>
+      <c r="B46" s="7">
+        <f>IF(COUNT(E5:E39)=0,"",AVERAGE(E5:E39))</f>
+        <v/>
+      </c>
+      <c r="C46" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(4,Tags!$A$5:$A$13,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D46">
+        <f>SUMPRODUCT((E5:E39&gt;=3)*ISNUMBER(L5:L39)*(L5:L39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Part 5. pandas and the last mile to Excel</t>
+        </is>
+      </c>
+      <c r="B47" s="7">
+        <f>IF(COUNT(F5:F39)=0,"",AVERAGE(F5:F39))</f>
+        <v/>
+      </c>
+      <c r="C47" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(5,Tags!$A$5:$A$13,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D47">
+        <f>SUMPRODUCT((F5:F39&gt;=3)*ISNUMBER(M5:M39)*(M5:M39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Part 6. Read the code, read the data</t>
+        </is>
+      </c>
+      <c r="B48" s="7">
+        <f>IF(COUNT(G5:G39)=0,"",AVERAGE(G5:G39))</f>
+        <v/>
+      </c>
+      <c r="C48" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(6,Tags!$A$5:$A$13,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D48">
+        <f>SUMPRODUCT((G5:G39&gt;=3)*ISNUMBER(N5:N39)*(N5:N39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
@@ -4690,7 +4690,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>a, b, c</t>
+          <t>a, c, d</t>
         </is>
       </c>
       <c r="G18">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>a, b, c</t>
+          <t>b, c, d</t>
         </is>
       </c>
       <c r="G25">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>a, b</t>
+          <t>b, d</t>
         </is>
       </c>
       <c r="G26">

--- a/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG39"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,150 +544,90 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -719,257 +659,157 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>[F]</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>[S]</t>
         </is>
       </c>
     </row>
@@ -1156,115 +996,15 @@
       </c>
       <c r="AK4" s="4" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="AL4" s="4" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="AM4" s="4" t="inlineStr">
-        <is>
-          <t>Q38</t>
-        </is>
-      </c>
-      <c r="AN4" s="4" t="inlineStr">
-        <is>
-          <t>Q39</t>
-        </is>
-      </c>
-      <c r="AO4" s="4" t="inlineStr">
-        <is>
-          <t>Q40</t>
-        </is>
-      </c>
-      <c r="AP4" s="4" t="inlineStr">
-        <is>
-          <t>Q41</t>
-        </is>
-      </c>
-      <c r="AQ4" s="4" t="inlineStr">
-        <is>
-          <t>Q42</t>
-        </is>
-      </c>
-      <c r="AR4" s="4" t="inlineStr">
-        <is>
-          <t>Q43</t>
-        </is>
-      </c>
-      <c r="AS4" s="4" t="inlineStr">
-        <is>
-          <t>Q44</t>
-        </is>
-      </c>
-      <c r="AT4" s="4" t="inlineStr">
-        <is>
-          <t>Q45</t>
-        </is>
-      </c>
-      <c r="AU4" s="4" t="inlineStr">
-        <is>
-          <t>Q46</t>
-        </is>
-      </c>
-      <c r="AV4" s="4" t="inlineStr">
-        <is>
-          <t>Q47</t>
-        </is>
-      </c>
-      <c r="AW4" s="4" t="inlineStr">
-        <is>
-          <t>Q48</t>
-        </is>
-      </c>
-      <c r="AX4" s="4" t="inlineStr">
-        <is>
-          <t>Q49</t>
-        </is>
-      </c>
-      <c r="AY4" s="4" t="inlineStr">
-        <is>
-          <t>Q50</t>
-        </is>
-      </c>
-      <c r="AZ4" s="4" t="inlineStr">
-        <is>
-          <t>Q51</t>
-        </is>
-      </c>
-      <c r="BA4" s="4" t="inlineStr">
-        <is>
-          <t>Q52</t>
-        </is>
-      </c>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>Q53</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
-        <is>
-          <t>Q54</t>
-        </is>
-      </c>
-      <c r="BD4" s="4" t="inlineStr">
-        <is>
-          <t>Q55</t>
-        </is>
-      </c>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="BG4" s="4" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
@@ -1309,36 +1049,16 @@
       <c r="AH5" s="5" t="n"/>
       <c r="AI5" s="5" t="n"/>
       <c r="AJ5" s="5" t="n"/>
-      <c r="AK5" s="5" t="n"/>
-      <c r="AL5" s="5" t="n"/>
-      <c r="AM5" s="5" t="n"/>
-      <c r="AN5" s="5" t="n"/>
-      <c r="AO5" s="5" t="n"/>
-      <c r="AP5" s="5" t="n"/>
-      <c r="AQ5" s="5" t="n"/>
-      <c r="AR5" s="5" t="n"/>
-      <c r="AS5" s="5" t="n"/>
-      <c r="AT5" s="5" t="n"/>
-      <c r="AU5" s="5" t="n"/>
-      <c r="AV5" s="5" t="n"/>
-      <c r="AW5" s="5" t="n"/>
-      <c r="AX5" s="5" t="n"/>
-      <c r="AY5" s="5" t="n"/>
-      <c r="AZ5" s="5" t="n"/>
-      <c r="BA5" s="5" t="n"/>
-      <c r="BB5" s="5" t="n"/>
-      <c r="BC5" s="5" t="n"/>
-      <c r="BD5" s="5" t="n"/>
-      <c r="BE5">
-        <f>IF(COUNT(B5:BD5)=0,"",SUM(B5:BD5))</f>
-        <v/>
-      </c>
-      <c r="BF5">
-        <f>COUNT(B5:BD5)</f>
-        <v/>
-      </c>
-      <c r="BG5">
-        <f>IF(OR(BE5="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE5,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE5,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK5">
+        <f>IF(COUNT(B5:AJ5)=0,"",SUM(B5:AJ5))</f>
+        <v/>
+      </c>
+      <c r="AL5">
+        <f>COUNT(B5:AJ5)</f>
+        <v/>
+      </c>
+      <c r="AM5">
+        <f>IF(OR(AK5="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK5,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK5,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1381,36 +1101,16 @@
       <c r="AH6" s="5" t="n"/>
       <c r="AI6" s="5" t="n"/>
       <c r="AJ6" s="5" t="n"/>
-      <c r="AK6" s="5" t="n"/>
-      <c r="AL6" s="5" t="n"/>
-      <c r="AM6" s="5" t="n"/>
-      <c r="AN6" s="5" t="n"/>
-      <c r="AO6" s="5" t="n"/>
-      <c r="AP6" s="5" t="n"/>
-      <c r="AQ6" s="5" t="n"/>
-      <c r="AR6" s="5" t="n"/>
-      <c r="AS6" s="5" t="n"/>
-      <c r="AT6" s="5" t="n"/>
-      <c r="AU6" s="5" t="n"/>
-      <c r="AV6" s="5" t="n"/>
-      <c r="AW6" s="5" t="n"/>
-      <c r="AX6" s="5" t="n"/>
-      <c r="AY6" s="5" t="n"/>
-      <c r="AZ6" s="5" t="n"/>
-      <c r="BA6" s="5" t="n"/>
-      <c r="BB6" s="5" t="n"/>
-      <c r="BC6" s="5" t="n"/>
-      <c r="BD6" s="5" t="n"/>
-      <c r="BE6">
-        <f>IF(COUNT(B6:BD6)=0,"",SUM(B6:BD6))</f>
-        <v/>
-      </c>
-      <c r="BF6">
-        <f>COUNT(B6:BD6)</f>
-        <v/>
-      </c>
-      <c r="BG6">
-        <f>IF(OR(BE6="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE6,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE6,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK6">
+        <f>IF(COUNT(B6:AJ6)=0,"",SUM(B6:AJ6))</f>
+        <v/>
+      </c>
+      <c r="AL6">
+        <f>COUNT(B6:AJ6)</f>
+        <v/>
+      </c>
+      <c r="AM6">
+        <f>IF(OR(AK6="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK6,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK6,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1453,36 +1153,16 @@
       <c r="AH7" s="5" t="n"/>
       <c r="AI7" s="5" t="n"/>
       <c r="AJ7" s="5" t="n"/>
-      <c r="AK7" s="5" t="n"/>
-      <c r="AL7" s="5" t="n"/>
-      <c r="AM7" s="5" t="n"/>
-      <c r="AN7" s="5" t="n"/>
-      <c r="AO7" s="5" t="n"/>
-      <c r="AP7" s="5" t="n"/>
-      <c r="AQ7" s="5" t="n"/>
-      <c r="AR7" s="5" t="n"/>
-      <c r="AS7" s="5" t="n"/>
-      <c r="AT7" s="5" t="n"/>
-      <c r="AU7" s="5" t="n"/>
-      <c r="AV7" s="5" t="n"/>
-      <c r="AW7" s="5" t="n"/>
-      <c r="AX7" s="5" t="n"/>
-      <c r="AY7" s="5" t="n"/>
-      <c r="AZ7" s="5" t="n"/>
-      <c r="BA7" s="5" t="n"/>
-      <c r="BB7" s="5" t="n"/>
-      <c r="BC7" s="5" t="n"/>
-      <c r="BD7" s="5" t="n"/>
-      <c r="BE7">
-        <f>IF(COUNT(B7:BD7)=0,"",SUM(B7:BD7))</f>
-        <v/>
-      </c>
-      <c r="BF7">
-        <f>COUNT(B7:BD7)</f>
-        <v/>
-      </c>
-      <c r="BG7">
-        <f>IF(OR(BE7="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE7,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE7,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK7">
+        <f>IF(COUNT(B7:AJ7)=0,"",SUM(B7:AJ7))</f>
+        <v/>
+      </c>
+      <c r="AL7">
+        <f>COUNT(B7:AJ7)</f>
+        <v/>
+      </c>
+      <c r="AM7">
+        <f>IF(OR(AK7="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK7,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK7,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1525,36 +1205,16 @@
       <c r="AH8" s="5" t="n"/>
       <c r="AI8" s="5" t="n"/>
       <c r="AJ8" s="5" t="n"/>
-      <c r="AK8" s="5" t="n"/>
-      <c r="AL8" s="5" t="n"/>
-      <c r="AM8" s="5" t="n"/>
-      <c r="AN8" s="5" t="n"/>
-      <c r="AO8" s="5" t="n"/>
-      <c r="AP8" s="5" t="n"/>
-      <c r="AQ8" s="5" t="n"/>
-      <c r="AR8" s="5" t="n"/>
-      <c r="AS8" s="5" t="n"/>
-      <c r="AT8" s="5" t="n"/>
-      <c r="AU8" s="5" t="n"/>
-      <c r="AV8" s="5" t="n"/>
-      <c r="AW8" s="5" t="n"/>
-      <c r="AX8" s="5" t="n"/>
-      <c r="AY8" s="5" t="n"/>
-      <c r="AZ8" s="5" t="n"/>
-      <c r="BA8" s="5" t="n"/>
-      <c r="BB8" s="5" t="n"/>
-      <c r="BC8" s="5" t="n"/>
-      <c r="BD8" s="5" t="n"/>
-      <c r="BE8">
-        <f>IF(COUNT(B8:BD8)=0,"",SUM(B8:BD8))</f>
-        <v/>
-      </c>
-      <c r="BF8">
-        <f>COUNT(B8:BD8)</f>
-        <v/>
-      </c>
-      <c r="BG8">
-        <f>IF(OR(BE8="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE8,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE8,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK8">
+        <f>IF(COUNT(B8:AJ8)=0,"",SUM(B8:AJ8))</f>
+        <v/>
+      </c>
+      <c r="AL8">
+        <f>COUNT(B8:AJ8)</f>
+        <v/>
+      </c>
+      <c r="AM8">
+        <f>IF(OR(AK8="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK8,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK8,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1597,36 +1257,16 @@
       <c r="AH9" s="5" t="n"/>
       <c r="AI9" s="5" t="n"/>
       <c r="AJ9" s="5" t="n"/>
-      <c r="AK9" s="5" t="n"/>
-      <c r="AL9" s="5" t="n"/>
-      <c r="AM9" s="5" t="n"/>
-      <c r="AN9" s="5" t="n"/>
-      <c r="AO9" s="5" t="n"/>
-      <c r="AP9" s="5" t="n"/>
-      <c r="AQ9" s="5" t="n"/>
-      <c r="AR9" s="5" t="n"/>
-      <c r="AS9" s="5" t="n"/>
-      <c r="AT9" s="5" t="n"/>
-      <c r="AU9" s="5" t="n"/>
-      <c r="AV9" s="5" t="n"/>
-      <c r="AW9" s="5" t="n"/>
-      <c r="AX9" s="5" t="n"/>
-      <c r="AY9" s="5" t="n"/>
-      <c r="AZ9" s="5" t="n"/>
-      <c r="BA9" s="5" t="n"/>
-      <c r="BB9" s="5" t="n"/>
-      <c r="BC9" s="5" t="n"/>
-      <c r="BD9" s="5" t="n"/>
-      <c r="BE9">
-        <f>IF(COUNT(B9:BD9)=0,"",SUM(B9:BD9))</f>
-        <v/>
-      </c>
-      <c r="BF9">
-        <f>COUNT(B9:BD9)</f>
-        <v/>
-      </c>
-      <c r="BG9">
-        <f>IF(OR(BE9="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE9,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE9,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK9">
+        <f>IF(COUNT(B9:AJ9)=0,"",SUM(B9:AJ9))</f>
+        <v/>
+      </c>
+      <c r="AL9">
+        <f>COUNT(B9:AJ9)</f>
+        <v/>
+      </c>
+      <c r="AM9">
+        <f>IF(OR(AK9="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK9,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK9,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1669,36 +1309,16 @@
       <c r="AH10" s="5" t="n"/>
       <c r="AI10" s="5" t="n"/>
       <c r="AJ10" s="5" t="n"/>
-      <c r="AK10" s="5" t="n"/>
-      <c r="AL10" s="5" t="n"/>
-      <c r="AM10" s="5" t="n"/>
-      <c r="AN10" s="5" t="n"/>
-      <c r="AO10" s="5" t="n"/>
-      <c r="AP10" s="5" t="n"/>
-      <c r="AQ10" s="5" t="n"/>
-      <c r="AR10" s="5" t="n"/>
-      <c r="AS10" s="5" t="n"/>
-      <c r="AT10" s="5" t="n"/>
-      <c r="AU10" s="5" t="n"/>
-      <c r="AV10" s="5" t="n"/>
-      <c r="AW10" s="5" t="n"/>
-      <c r="AX10" s="5" t="n"/>
-      <c r="AY10" s="5" t="n"/>
-      <c r="AZ10" s="5" t="n"/>
-      <c r="BA10" s="5" t="n"/>
-      <c r="BB10" s="5" t="n"/>
-      <c r="BC10" s="5" t="n"/>
-      <c r="BD10" s="5" t="n"/>
-      <c r="BE10">
-        <f>IF(COUNT(B10:BD10)=0,"",SUM(B10:BD10))</f>
-        <v/>
-      </c>
-      <c r="BF10">
-        <f>COUNT(B10:BD10)</f>
-        <v/>
-      </c>
-      <c r="BG10">
-        <f>IF(OR(BE10="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE10,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE10,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK10">
+        <f>IF(COUNT(B10:AJ10)=0,"",SUM(B10:AJ10))</f>
+        <v/>
+      </c>
+      <c r="AL10">
+        <f>COUNT(B10:AJ10)</f>
+        <v/>
+      </c>
+      <c r="AM10">
+        <f>IF(OR(AK10="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK10,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK10,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1741,36 +1361,16 @@
       <c r="AH11" s="5" t="n"/>
       <c r="AI11" s="5" t="n"/>
       <c r="AJ11" s="5" t="n"/>
-      <c r="AK11" s="5" t="n"/>
-      <c r="AL11" s="5" t="n"/>
-      <c r="AM11" s="5" t="n"/>
-      <c r="AN11" s="5" t="n"/>
-      <c r="AO11" s="5" t="n"/>
-      <c r="AP11" s="5" t="n"/>
-      <c r="AQ11" s="5" t="n"/>
-      <c r="AR11" s="5" t="n"/>
-      <c r="AS11" s="5" t="n"/>
-      <c r="AT11" s="5" t="n"/>
-      <c r="AU11" s="5" t="n"/>
-      <c r="AV11" s="5" t="n"/>
-      <c r="AW11" s="5" t="n"/>
-      <c r="AX11" s="5" t="n"/>
-      <c r="AY11" s="5" t="n"/>
-      <c r="AZ11" s="5" t="n"/>
-      <c r="BA11" s="5" t="n"/>
-      <c r="BB11" s="5" t="n"/>
-      <c r="BC11" s="5" t="n"/>
-      <c r="BD11" s="5" t="n"/>
-      <c r="BE11">
-        <f>IF(COUNT(B11:BD11)=0,"",SUM(B11:BD11))</f>
-        <v/>
-      </c>
-      <c r="BF11">
-        <f>COUNT(B11:BD11)</f>
-        <v/>
-      </c>
-      <c r="BG11">
-        <f>IF(OR(BE11="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE11,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE11,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK11">
+        <f>IF(COUNT(B11:AJ11)=0,"",SUM(B11:AJ11))</f>
+        <v/>
+      </c>
+      <c r="AL11">
+        <f>COUNT(B11:AJ11)</f>
+        <v/>
+      </c>
+      <c r="AM11">
+        <f>IF(OR(AK11="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK11,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK11,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1813,36 +1413,16 @@
       <c r="AH12" s="5" t="n"/>
       <c r="AI12" s="5" t="n"/>
       <c r="AJ12" s="5" t="n"/>
-      <c r="AK12" s="5" t="n"/>
-      <c r="AL12" s="5" t="n"/>
-      <c r="AM12" s="5" t="n"/>
-      <c r="AN12" s="5" t="n"/>
-      <c r="AO12" s="5" t="n"/>
-      <c r="AP12" s="5" t="n"/>
-      <c r="AQ12" s="5" t="n"/>
-      <c r="AR12" s="5" t="n"/>
-      <c r="AS12" s="5" t="n"/>
-      <c r="AT12" s="5" t="n"/>
-      <c r="AU12" s="5" t="n"/>
-      <c r="AV12" s="5" t="n"/>
-      <c r="AW12" s="5" t="n"/>
-      <c r="AX12" s="5" t="n"/>
-      <c r="AY12" s="5" t="n"/>
-      <c r="AZ12" s="5" t="n"/>
-      <c r="BA12" s="5" t="n"/>
-      <c r="BB12" s="5" t="n"/>
-      <c r="BC12" s="5" t="n"/>
-      <c r="BD12" s="5" t="n"/>
-      <c r="BE12">
-        <f>IF(COUNT(B12:BD12)=0,"",SUM(B12:BD12))</f>
-        <v/>
-      </c>
-      <c r="BF12">
-        <f>COUNT(B12:BD12)</f>
-        <v/>
-      </c>
-      <c r="BG12">
-        <f>IF(OR(BE12="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE12,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE12,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK12">
+        <f>IF(COUNT(B12:AJ12)=0,"",SUM(B12:AJ12))</f>
+        <v/>
+      </c>
+      <c r="AL12">
+        <f>COUNT(B12:AJ12)</f>
+        <v/>
+      </c>
+      <c r="AM12">
+        <f>IF(OR(AK12="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK12,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK12,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1885,36 +1465,16 @@
       <c r="AH13" s="5" t="n"/>
       <c r="AI13" s="5" t="n"/>
       <c r="AJ13" s="5" t="n"/>
-      <c r="AK13" s="5" t="n"/>
-      <c r="AL13" s="5" t="n"/>
-      <c r="AM13" s="5" t="n"/>
-      <c r="AN13" s="5" t="n"/>
-      <c r="AO13" s="5" t="n"/>
-      <c r="AP13" s="5" t="n"/>
-      <c r="AQ13" s="5" t="n"/>
-      <c r="AR13" s="5" t="n"/>
-      <c r="AS13" s="5" t="n"/>
-      <c r="AT13" s="5" t="n"/>
-      <c r="AU13" s="5" t="n"/>
-      <c r="AV13" s="5" t="n"/>
-      <c r="AW13" s="5" t="n"/>
-      <c r="AX13" s="5" t="n"/>
-      <c r="AY13" s="5" t="n"/>
-      <c r="AZ13" s="5" t="n"/>
-      <c r="BA13" s="5" t="n"/>
-      <c r="BB13" s="5" t="n"/>
-      <c r="BC13" s="5" t="n"/>
-      <c r="BD13" s="5" t="n"/>
-      <c r="BE13">
-        <f>IF(COUNT(B13:BD13)=0,"",SUM(B13:BD13))</f>
-        <v/>
-      </c>
-      <c r="BF13">
-        <f>COUNT(B13:BD13)</f>
-        <v/>
-      </c>
-      <c r="BG13">
-        <f>IF(OR(BE13="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE13,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE13,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK13">
+        <f>IF(COUNT(B13:AJ13)=0,"",SUM(B13:AJ13))</f>
+        <v/>
+      </c>
+      <c r="AL13">
+        <f>COUNT(B13:AJ13)</f>
+        <v/>
+      </c>
+      <c r="AM13">
+        <f>IF(OR(AK13="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK13,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK13,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1957,36 +1517,16 @@
       <c r="AH14" s="5" t="n"/>
       <c r="AI14" s="5" t="n"/>
       <c r="AJ14" s="5" t="n"/>
-      <c r="AK14" s="5" t="n"/>
-      <c r="AL14" s="5" t="n"/>
-      <c r="AM14" s="5" t="n"/>
-      <c r="AN14" s="5" t="n"/>
-      <c r="AO14" s="5" t="n"/>
-      <c r="AP14" s="5" t="n"/>
-      <c r="AQ14" s="5" t="n"/>
-      <c r="AR14" s="5" t="n"/>
-      <c r="AS14" s="5" t="n"/>
-      <c r="AT14" s="5" t="n"/>
-      <c r="AU14" s="5" t="n"/>
-      <c r="AV14" s="5" t="n"/>
-      <c r="AW14" s="5" t="n"/>
-      <c r="AX14" s="5" t="n"/>
-      <c r="AY14" s="5" t="n"/>
-      <c r="AZ14" s="5" t="n"/>
-      <c r="BA14" s="5" t="n"/>
-      <c r="BB14" s="5" t="n"/>
-      <c r="BC14" s="5" t="n"/>
-      <c r="BD14" s="5" t="n"/>
-      <c r="BE14">
-        <f>IF(COUNT(B14:BD14)=0,"",SUM(B14:BD14))</f>
-        <v/>
-      </c>
-      <c r="BF14">
-        <f>COUNT(B14:BD14)</f>
-        <v/>
-      </c>
-      <c r="BG14">
-        <f>IF(OR(BE14="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE14,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE14,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK14">
+        <f>IF(COUNT(B14:AJ14)=0,"",SUM(B14:AJ14))</f>
+        <v/>
+      </c>
+      <c r="AL14">
+        <f>COUNT(B14:AJ14)</f>
+        <v/>
+      </c>
+      <c r="AM14">
+        <f>IF(OR(AK14="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK14,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK14,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2029,36 +1569,16 @@
       <c r="AH15" s="5" t="n"/>
       <c r="AI15" s="5" t="n"/>
       <c r="AJ15" s="5" t="n"/>
-      <c r="AK15" s="5" t="n"/>
-      <c r="AL15" s="5" t="n"/>
-      <c r="AM15" s="5" t="n"/>
-      <c r="AN15" s="5" t="n"/>
-      <c r="AO15" s="5" t="n"/>
-      <c r="AP15" s="5" t="n"/>
-      <c r="AQ15" s="5" t="n"/>
-      <c r="AR15" s="5" t="n"/>
-      <c r="AS15" s="5" t="n"/>
-      <c r="AT15" s="5" t="n"/>
-      <c r="AU15" s="5" t="n"/>
-      <c r="AV15" s="5" t="n"/>
-      <c r="AW15" s="5" t="n"/>
-      <c r="AX15" s="5" t="n"/>
-      <c r="AY15" s="5" t="n"/>
-      <c r="AZ15" s="5" t="n"/>
-      <c r="BA15" s="5" t="n"/>
-      <c r="BB15" s="5" t="n"/>
-      <c r="BC15" s="5" t="n"/>
-      <c r="BD15" s="5" t="n"/>
-      <c r="BE15">
-        <f>IF(COUNT(B15:BD15)=0,"",SUM(B15:BD15))</f>
-        <v/>
-      </c>
-      <c r="BF15">
-        <f>COUNT(B15:BD15)</f>
-        <v/>
-      </c>
-      <c r="BG15">
-        <f>IF(OR(BE15="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE15,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE15,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK15">
+        <f>IF(COUNT(B15:AJ15)=0,"",SUM(B15:AJ15))</f>
+        <v/>
+      </c>
+      <c r="AL15">
+        <f>COUNT(B15:AJ15)</f>
+        <v/>
+      </c>
+      <c r="AM15">
+        <f>IF(OR(AK15="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK15,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK15,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2101,36 +1621,16 @@
       <c r="AH16" s="5" t="n"/>
       <c r="AI16" s="5" t="n"/>
       <c r="AJ16" s="5" t="n"/>
-      <c r="AK16" s="5" t="n"/>
-      <c r="AL16" s="5" t="n"/>
-      <c r="AM16" s="5" t="n"/>
-      <c r="AN16" s="5" t="n"/>
-      <c r="AO16" s="5" t="n"/>
-      <c r="AP16" s="5" t="n"/>
-      <c r="AQ16" s="5" t="n"/>
-      <c r="AR16" s="5" t="n"/>
-      <c r="AS16" s="5" t="n"/>
-      <c r="AT16" s="5" t="n"/>
-      <c r="AU16" s="5" t="n"/>
-      <c r="AV16" s="5" t="n"/>
-      <c r="AW16" s="5" t="n"/>
-      <c r="AX16" s="5" t="n"/>
-      <c r="AY16" s="5" t="n"/>
-      <c r="AZ16" s="5" t="n"/>
-      <c r="BA16" s="5" t="n"/>
-      <c r="BB16" s="5" t="n"/>
-      <c r="BC16" s="5" t="n"/>
-      <c r="BD16" s="5" t="n"/>
-      <c r="BE16">
-        <f>IF(COUNT(B16:BD16)=0,"",SUM(B16:BD16))</f>
-        <v/>
-      </c>
-      <c r="BF16">
-        <f>COUNT(B16:BD16)</f>
-        <v/>
-      </c>
-      <c r="BG16">
-        <f>IF(OR(BE16="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE16,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE16,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK16">
+        <f>IF(COUNT(B16:AJ16)=0,"",SUM(B16:AJ16))</f>
+        <v/>
+      </c>
+      <c r="AL16">
+        <f>COUNT(B16:AJ16)</f>
+        <v/>
+      </c>
+      <c r="AM16">
+        <f>IF(OR(AK16="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK16,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK16,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2173,36 +1673,16 @@
       <c r="AH17" s="5" t="n"/>
       <c r="AI17" s="5" t="n"/>
       <c r="AJ17" s="5" t="n"/>
-      <c r="AK17" s="5" t="n"/>
-      <c r="AL17" s="5" t="n"/>
-      <c r="AM17" s="5" t="n"/>
-      <c r="AN17" s="5" t="n"/>
-      <c r="AO17" s="5" t="n"/>
-      <c r="AP17" s="5" t="n"/>
-      <c r="AQ17" s="5" t="n"/>
-      <c r="AR17" s="5" t="n"/>
-      <c r="AS17" s="5" t="n"/>
-      <c r="AT17" s="5" t="n"/>
-      <c r="AU17" s="5" t="n"/>
-      <c r="AV17" s="5" t="n"/>
-      <c r="AW17" s="5" t="n"/>
-      <c r="AX17" s="5" t="n"/>
-      <c r="AY17" s="5" t="n"/>
-      <c r="AZ17" s="5" t="n"/>
-      <c r="BA17" s="5" t="n"/>
-      <c r="BB17" s="5" t="n"/>
-      <c r="BC17" s="5" t="n"/>
-      <c r="BD17" s="5" t="n"/>
-      <c r="BE17">
-        <f>IF(COUNT(B17:BD17)=0,"",SUM(B17:BD17))</f>
-        <v/>
-      </c>
-      <c r="BF17">
-        <f>COUNT(B17:BD17)</f>
-        <v/>
-      </c>
-      <c r="BG17">
-        <f>IF(OR(BE17="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE17,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE17,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK17">
+        <f>IF(COUNT(B17:AJ17)=0,"",SUM(B17:AJ17))</f>
+        <v/>
+      </c>
+      <c r="AL17">
+        <f>COUNT(B17:AJ17)</f>
+        <v/>
+      </c>
+      <c r="AM17">
+        <f>IF(OR(AK17="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK17,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK17,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2245,36 +1725,16 @@
       <c r="AH18" s="5" t="n"/>
       <c r="AI18" s="5" t="n"/>
       <c r="AJ18" s="5" t="n"/>
-      <c r="AK18" s="5" t="n"/>
-      <c r="AL18" s="5" t="n"/>
-      <c r="AM18" s="5" t="n"/>
-      <c r="AN18" s="5" t="n"/>
-      <c r="AO18" s="5" t="n"/>
-      <c r="AP18" s="5" t="n"/>
-      <c r="AQ18" s="5" t="n"/>
-      <c r="AR18" s="5" t="n"/>
-      <c r="AS18" s="5" t="n"/>
-      <c r="AT18" s="5" t="n"/>
-      <c r="AU18" s="5" t="n"/>
-      <c r="AV18" s="5" t="n"/>
-      <c r="AW18" s="5" t="n"/>
-      <c r="AX18" s="5" t="n"/>
-      <c r="AY18" s="5" t="n"/>
-      <c r="AZ18" s="5" t="n"/>
-      <c r="BA18" s="5" t="n"/>
-      <c r="BB18" s="5" t="n"/>
-      <c r="BC18" s="5" t="n"/>
-      <c r="BD18" s="5" t="n"/>
-      <c r="BE18">
-        <f>IF(COUNT(B18:BD18)=0,"",SUM(B18:BD18))</f>
-        <v/>
-      </c>
-      <c r="BF18">
-        <f>COUNT(B18:BD18)</f>
-        <v/>
-      </c>
-      <c r="BG18">
-        <f>IF(OR(BE18="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE18,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE18,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK18">
+        <f>IF(COUNT(B18:AJ18)=0,"",SUM(B18:AJ18))</f>
+        <v/>
+      </c>
+      <c r="AL18">
+        <f>COUNT(B18:AJ18)</f>
+        <v/>
+      </c>
+      <c r="AM18">
+        <f>IF(OR(AK18="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK18,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK18,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2317,36 +1777,16 @@
       <c r="AH19" s="5" t="n"/>
       <c r="AI19" s="5" t="n"/>
       <c r="AJ19" s="5" t="n"/>
-      <c r="AK19" s="5" t="n"/>
-      <c r="AL19" s="5" t="n"/>
-      <c r="AM19" s="5" t="n"/>
-      <c r="AN19" s="5" t="n"/>
-      <c r="AO19" s="5" t="n"/>
-      <c r="AP19" s="5" t="n"/>
-      <c r="AQ19" s="5" t="n"/>
-      <c r="AR19" s="5" t="n"/>
-      <c r="AS19" s="5" t="n"/>
-      <c r="AT19" s="5" t="n"/>
-      <c r="AU19" s="5" t="n"/>
-      <c r="AV19" s="5" t="n"/>
-      <c r="AW19" s="5" t="n"/>
-      <c r="AX19" s="5" t="n"/>
-      <c r="AY19" s="5" t="n"/>
-      <c r="AZ19" s="5" t="n"/>
-      <c r="BA19" s="5" t="n"/>
-      <c r="BB19" s="5" t="n"/>
-      <c r="BC19" s="5" t="n"/>
-      <c r="BD19" s="5" t="n"/>
-      <c r="BE19">
-        <f>IF(COUNT(B19:BD19)=0,"",SUM(B19:BD19))</f>
-        <v/>
-      </c>
-      <c r="BF19">
-        <f>COUNT(B19:BD19)</f>
-        <v/>
-      </c>
-      <c r="BG19">
-        <f>IF(OR(BE19="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE19,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE19,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK19">
+        <f>IF(COUNT(B19:AJ19)=0,"",SUM(B19:AJ19))</f>
+        <v/>
+      </c>
+      <c r="AL19">
+        <f>COUNT(B19:AJ19)</f>
+        <v/>
+      </c>
+      <c r="AM19">
+        <f>IF(OR(AK19="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK19,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK19,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2389,36 +1829,16 @@
       <c r="AH20" s="5" t="n"/>
       <c r="AI20" s="5" t="n"/>
       <c r="AJ20" s="5" t="n"/>
-      <c r="AK20" s="5" t="n"/>
-      <c r="AL20" s="5" t="n"/>
-      <c r="AM20" s="5" t="n"/>
-      <c r="AN20" s="5" t="n"/>
-      <c r="AO20" s="5" t="n"/>
-      <c r="AP20" s="5" t="n"/>
-      <c r="AQ20" s="5" t="n"/>
-      <c r="AR20" s="5" t="n"/>
-      <c r="AS20" s="5" t="n"/>
-      <c r="AT20" s="5" t="n"/>
-      <c r="AU20" s="5" t="n"/>
-      <c r="AV20" s="5" t="n"/>
-      <c r="AW20" s="5" t="n"/>
-      <c r="AX20" s="5" t="n"/>
-      <c r="AY20" s="5" t="n"/>
-      <c r="AZ20" s="5" t="n"/>
-      <c r="BA20" s="5" t="n"/>
-      <c r="BB20" s="5" t="n"/>
-      <c r="BC20" s="5" t="n"/>
-      <c r="BD20" s="5" t="n"/>
-      <c r="BE20">
-        <f>IF(COUNT(B20:BD20)=0,"",SUM(B20:BD20))</f>
-        <v/>
-      </c>
-      <c r="BF20">
-        <f>COUNT(B20:BD20)</f>
-        <v/>
-      </c>
-      <c r="BG20">
-        <f>IF(OR(BE20="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE20,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE20,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK20">
+        <f>IF(COUNT(B20:AJ20)=0,"",SUM(B20:AJ20))</f>
+        <v/>
+      </c>
+      <c r="AL20">
+        <f>COUNT(B20:AJ20)</f>
+        <v/>
+      </c>
+      <c r="AM20">
+        <f>IF(OR(AK20="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK20,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK20,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2461,36 +1881,16 @@
       <c r="AH21" s="5" t="n"/>
       <c r="AI21" s="5" t="n"/>
       <c r="AJ21" s="5" t="n"/>
-      <c r="AK21" s="5" t="n"/>
-      <c r="AL21" s="5" t="n"/>
-      <c r="AM21" s="5" t="n"/>
-      <c r="AN21" s="5" t="n"/>
-      <c r="AO21" s="5" t="n"/>
-      <c r="AP21" s="5" t="n"/>
-      <c r="AQ21" s="5" t="n"/>
-      <c r="AR21" s="5" t="n"/>
-      <c r="AS21" s="5" t="n"/>
-      <c r="AT21" s="5" t="n"/>
-      <c r="AU21" s="5" t="n"/>
-      <c r="AV21" s="5" t="n"/>
-      <c r="AW21" s="5" t="n"/>
-      <c r="AX21" s="5" t="n"/>
-      <c r="AY21" s="5" t="n"/>
-      <c r="AZ21" s="5" t="n"/>
-      <c r="BA21" s="5" t="n"/>
-      <c r="BB21" s="5" t="n"/>
-      <c r="BC21" s="5" t="n"/>
-      <c r="BD21" s="5" t="n"/>
-      <c r="BE21">
-        <f>IF(COUNT(B21:BD21)=0,"",SUM(B21:BD21))</f>
-        <v/>
-      </c>
-      <c r="BF21">
-        <f>COUNT(B21:BD21)</f>
-        <v/>
-      </c>
-      <c r="BG21">
-        <f>IF(OR(BE21="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE21,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE21,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK21">
+        <f>IF(COUNT(B21:AJ21)=0,"",SUM(B21:AJ21))</f>
+        <v/>
+      </c>
+      <c r="AL21">
+        <f>COUNT(B21:AJ21)</f>
+        <v/>
+      </c>
+      <c r="AM21">
+        <f>IF(OR(AK21="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK21,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK21,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2533,36 +1933,16 @@
       <c r="AH22" s="5" t="n"/>
       <c r="AI22" s="5" t="n"/>
       <c r="AJ22" s="5" t="n"/>
-      <c r="AK22" s="5" t="n"/>
-      <c r="AL22" s="5" t="n"/>
-      <c r="AM22" s="5" t="n"/>
-      <c r="AN22" s="5" t="n"/>
-      <c r="AO22" s="5" t="n"/>
-      <c r="AP22" s="5" t="n"/>
-      <c r="AQ22" s="5" t="n"/>
-      <c r="AR22" s="5" t="n"/>
-      <c r="AS22" s="5" t="n"/>
-      <c r="AT22" s="5" t="n"/>
-      <c r="AU22" s="5" t="n"/>
-      <c r="AV22" s="5" t="n"/>
-      <c r="AW22" s="5" t="n"/>
-      <c r="AX22" s="5" t="n"/>
-      <c r="AY22" s="5" t="n"/>
-      <c r="AZ22" s="5" t="n"/>
-      <c r="BA22" s="5" t="n"/>
-      <c r="BB22" s="5" t="n"/>
-      <c r="BC22" s="5" t="n"/>
-      <c r="BD22" s="5" t="n"/>
-      <c r="BE22">
-        <f>IF(COUNT(B22:BD22)=0,"",SUM(B22:BD22))</f>
-        <v/>
-      </c>
-      <c r="BF22">
-        <f>COUNT(B22:BD22)</f>
-        <v/>
-      </c>
-      <c r="BG22">
-        <f>IF(OR(BE22="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE22,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE22,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK22">
+        <f>IF(COUNT(B22:AJ22)=0,"",SUM(B22:AJ22))</f>
+        <v/>
+      </c>
+      <c r="AL22">
+        <f>COUNT(B22:AJ22)</f>
+        <v/>
+      </c>
+      <c r="AM22">
+        <f>IF(OR(AK22="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK22,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK22,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2605,36 +1985,16 @@
       <c r="AH23" s="5" t="n"/>
       <c r="AI23" s="5" t="n"/>
       <c r="AJ23" s="5" t="n"/>
-      <c r="AK23" s="5" t="n"/>
-      <c r="AL23" s="5" t="n"/>
-      <c r="AM23" s="5" t="n"/>
-      <c r="AN23" s="5" t="n"/>
-      <c r="AO23" s="5" t="n"/>
-      <c r="AP23" s="5" t="n"/>
-      <c r="AQ23" s="5" t="n"/>
-      <c r="AR23" s="5" t="n"/>
-      <c r="AS23" s="5" t="n"/>
-      <c r="AT23" s="5" t="n"/>
-      <c r="AU23" s="5" t="n"/>
-      <c r="AV23" s="5" t="n"/>
-      <c r="AW23" s="5" t="n"/>
-      <c r="AX23" s="5" t="n"/>
-      <c r="AY23" s="5" t="n"/>
-      <c r="AZ23" s="5" t="n"/>
-      <c r="BA23" s="5" t="n"/>
-      <c r="BB23" s="5" t="n"/>
-      <c r="BC23" s="5" t="n"/>
-      <c r="BD23" s="5" t="n"/>
-      <c r="BE23">
-        <f>IF(COUNT(B23:BD23)=0,"",SUM(B23:BD23))</f>
-        <v/>
-      </c>
-      <c r="BF23">
-        <f>COUNT(B23:BD23)</f>
-        <v/>
-      </c>
-      <c r="BG23">
-        <f>IF(OR(BE23="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE23,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE23,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK23">
+        <f>IF(COUNT(B23:AJ23)=0,"",SUM(B23:AJ23))</f>
+        <v/>
+      </c>
+      <c r="AL23">
+        <f>COUNT(B23:AJ23)</f>
+        <v/>
+      </c>
+      <c r="AM23">
+        <f>IF(OR(AK23="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK23,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK23,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2677,36 +2037,16 @@
       <c r="AH24" s="5" t="n"/>
       <c r="AI24" s="5" t="n"/>
       <c r="AJ24" s="5" t="n"/>
-      <c r="AK24" s="5" t="n"/>
-      <c r="AL24" s="5" t="n"/>
-      <c r="AM24" s="5" t="n"/>
-      <c r="AN24" s="5" t="n"/>
-      <c r="AO24" s="5" t="n"/>
-      <c r="AP24" s="5" t="n"/>
-      <c r="AQ24" s="5" t="n"/>
-      <c r="AR24" s="5" t="n"/>
-      <c r="AS24" s="5" t="n"/>
-      <c r="AT24" s="5" t="n"/>
-      <c r="AU24" s="5" t="n"/>
-      <c r="AV24" s="5" t="n"/>
-      <c r="AW24" s="5" t="n"/>
-      <c r="AX24" s="5" t="n"/>
-      <c r="AY24" s="5" t="n"/>
-      <c r="AZ24" s="5" t="n"/>
-      <c r="BA24" s="5" t="n"/>
-      <c r="BB24" s="5" t="n"/>
-      <c r="BC24" s="5" t="n"/>
-      <c r="BD24" s="5" t="n"/>
-      <c r="BE24">
-        <f>IF(COUNT(B24:BD24)=0,"",SUM(B24:BD24))</f>
-        <v/>
-      </c>
-      <c r="BF24">
-        <f>COUNT(B24:BD24)</f>
-        <v/>
-      </c>
-      <c r="BG24">
-        <f>IF(OR(BE24="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE24,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE24,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK24">
+        <f>IF(COUNT(B24:AJ24)=0,"",SUM(B24:AJ24))</f>
+        <v/>
+      </c>
+      <c r="AL24">
+        <f>COUNT(B24:AJ24)</f>
+        <v/>
+      </c>
+      <c r="AM24">
+        <f>IF(OR(AK24="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK24,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK24,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2749,36 +2089,16 @@
       <c r="AH25" s="5" t="n"/>
       <c r="AI25" s="5" t="n"/>
       <c r="AJ25" s="5" t="n"/>
-      <c r="AK25" s="5" t="n"/>
-      <c r="AL25" s="5" t="n"/>
-      <c r="AM25" s="5" t="n"/>
-      <c r="AN25" s="5" t="n"/>
-      <c r="AO25" s="5" t="n"/>
-      <c r="AP25" s="5" t="n"/>
-      <c r="AQ25" s="5" t="n"/>
-      <c r="AR25" s="5" t="n"/>
-      <c r="AS25" s="5" t="n"/>
-      <c r="AT25" s="5" t="n"/>
-      <c r="AU25" s="5" t="n"/>
-      <c r="AV25" s="5" t="n"/>
-      <c r="AW25" s="5" t="n"/>
-      <c r="AX25" s="5" t="n"/>
-      <c r="AY25" s="5" t="n"/>
-      <c r="AZ25" s="5" t="n"/>
-      <c r="BA25" s="5" t="n"/>
-      <c r="BB25" s="5" t="n"/>
-      <c r="BC25" s="5" t="n"/>
-      <c r="BD25" s="5" t="n"/>
-      <c r="BE25">
-        <f>IF(COUNT(B25:BD25)=0,"",SUM(B25:BD25))</f>
-        <v/>
-      </c>
-      <c r="BF25">
-        <f>COUNT(B25:BD25)</f>
-        <v/>
-      </c>
-      <c r="BG25">
-        <f>IF(OR(BE25="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE25,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE25,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK25">
+        <f>IF(COUNT(B25:AJ25)=0,"",SUM(B25:AJ25))</f>
+        <v/>
+      </c>
+      <c r="AL25">
+        <f>COUNT(B25:AJ25)</f>
+        <v/>
+      </c>
+      <c r="AM25">
+        <f>IF(OR(AK25="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK25,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK25,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2821,36 +2141,16 @@
       <c r="AH26" s="5" t="n"/>
       <c r="AI26" s="5" t="n"/>
       <c r="AJ26" s="5" t="n"/>
-      <c r="AK26" s="5" t="n"/>
-      <c r="AL26" s="5" t="n"/>
-      <c r="AM26" s="5" t="n"/>
-      <c r="AN26" s="5" t="n"/>
-      <c r="AO26" s="5" t="n"/>
-      <c r="AP26" s="5" t="n"/>
-      <c r="AQ26" s="5" t="n"/>
-      <c r="AR26" s="5" t="n"/>
-      <c r="AS26" s="5" t="n"/>
-      <c r="AT26" s="5" t="n"/>
-      <c r="AU26" s="5" t="n"/>
-      <c r="AV26" s="5" t="n"/>
-      <c r="AW26" s="5" t="n"/>
-      <c r="AX26" s="5" t="n"/>
-      <c r="AY26" s="5" t="n"/>
-      <c r="AZ26" s="5" t="n"/>
-      <c r="BA26" s="5" t="n"/>
-      <c r="BB26" s="5" t="n"/>
-      <c r="BC26" s="5" t="n"/>
-      <c r="BD26" s="5" t="n"/>
-      <c r="BE26">
-        <f>IF(COUNT(B26:BD26)=0,"",SUM(B26:BD26))</f>
-        <v/>
-      </c>
-      <c r="BF26">
-        <f>COUNT(B26:BD26)</f>
-        <v/>
-      </c>
-      <c r="BG26">
-        <f>IF(OR(BE26="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE26,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE26,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK26">
+        <f>IF(COUNT(B26:AJ26)=0,"",SUM(B26:AJ26))</f>
+        <v/>
+      </c>
+      <c r="AL26">
+        <f>COUNT(B26:AJ26)</f>
+        <v/>
+      </c>
+      <c r="AM26">
+        <f>IF(OR(AK26="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK26,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK26,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2893,36 +2193,16 @@
       <c r="AH27" s="5" t="n"/>
       <c r="AI27" s="5" t="n"/>
       <c r="AJ27" s="5" t="n"/>
-      <c r="AK27" s="5" t="n"/>
-      <c r="AL27" s="5" t="n"/>
-      <c r="AM27" s="5" t="n"/>
-      <c r="AN27" s="5" t="n"/>
-      <c r="AO27" s="5" t="n"/>
-      <c r="AP27" s="5" t="n"/>
-      <c r="AQ27" s="5" t="n"/>
-      <c r="AR27" s="5" t="n"/>
-      <c r="AS27" s="5" t="n"/>
-      <c r="AT27" s="5" t="n"/>
-      <c r="AU27" s="5" t="n"/>
-      <c r="AV27" s="5" t="n"/>
-      <c r="AW27" s="5" t="n"/>
-      <c r="AX27" s="5" t="n"/>
-      <c r="AY27" s="5" t="n"/>
-      <c r="AZ27" s="5" t="n"/>
-      <c r="BA27" s="5" t="n"/>
-      <c r="BB27" s="5" t="n"/>
-      <c r="BC27" s="5" t="n"/>
-      <c r="BD27" s="5" t="n"/>
-      <c r="BE27">
-        <f>IF(COUNT(B27:BD27)=0,"",SUM(B27:BD27))</f>
-        <v/>
-      </c>
-      <c r="BF27">
-        <f>COUNT(B27:BD27)</f>
-        <v/>
-      </c>
-      <c r="BG27">
-        <f>IF(OR(BE27="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE27,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE27,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK27">
+        <f>IF(COUNT(B27:AJ27)=0,"",SUM(B27:AJ27))</f>
+        <v/>
+      </c>
+      <c r="AL27">
+        <f>COUNT(B27:AJ27)</f>
+        <v/>
+      </c>
+      <c r="AM27">
+        <f>IF(OR(AK27="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK27,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK27,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2965,36 +2245,16 @@
       <c r="AH28" s="5" t="n"/>
       <c r="AI28" s="5" t="n"/>
       <c r="AJ28" s="5" t="n"/>
-      <c r="AK28" s="5" t="n"/>
-      <c r="AL28" s="5" t="n"/>
-      <c r="AM28" s="5" t="n"/>
-      <c r="AN28" s="5" t="n"/>
-      <c r="AO28" s="5" t="n"/>
-      <c r="AP28" s="5" t="n"/>
-      <c r="AQ28" s="5" t="n"/>
-      <c r="AR28" s="5" t="n"/>
-      <c r="AS28" s="5" t="n"/>
-      <c r="AT28" s="5" t="n"/>
-      <c r="AU28" s="5" t="n"/>
-      <c r="AV28" s="5" t="n"/>
-      <c r="AW28" s="5" t="n"/>
-      <c r="AX28" s="5" t="n"/>
-      <c r="AY28" s="5" t="n"/>
-      <c r="AZ28" s="5" t="n"/>
-      <c r="BA28" s="5" t="n"/>
-      <c r="BB28" s="5" t="n"/>
-      <c r="BC28" s="5" t="n"/>
-      <c r="BD28" s="5" t="n"/>
-      <c r="BE28">
-        <f>IF(COUNT(B28:BD28)=0,"",SUM(B28:BD28))</f>
-        <v/>
-      </c>
-      <c r="BF28">
-        <f>COUNT(B28:BD28)</f>
-        <v/>
-      </c>
-      <c r="BG28">
-        <f>IF(OR(BE28="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE28,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE28,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK28">
+        <f>IF(COUNT(B28:AJ28)=0,"",SUM(B28:AJ28))</f>
+        <v/>
+      </c>
+      <c r="AL28">
+        <f>COUNT(B28:AJ28)</f>
+        <v/>
+      </c>
+      <c r="AM28">
+        <f>IF(OR(AK28="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK28,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK28,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3037,36 +2297,16 @@
       <c r="AH29" s="5" t="n"/>
       <c r="AI29" s="5" t="n"/>
       <c r="AJ29" s="5" t="n"/>
-      <c r="AK29" s="5" t="n"/>
-      <c r="AL29" s="5" t="n"/>
-      <c r="AM29" s="5" t="n"/>
-      <c r="AN29" s="5" t="n"/>
-      <c r="AO29" s="5" t="n"/>
-      <c r="AP29" s="5" t="n"/>
-      <c r="AQ29" s="5" t="n"/>
-      <c r="AR29" s="5" t="n"/>
-      <c r="AS29" s="5" t="n"/>
-      <c r="AT29" s="5" t="n"/>
-      <c r="AU29" s="5" t="n"/>
-      <c r="AV29" s="5" t="n"/>
-      <c r="AW29" s="5" t="n"/>
-      <c r="AX29" s="5" t="n"/>
-      <c r="AY29" s="5" t="n"/>
-      <c r="AZ29" s="5" t="n"/>
-      <c r="BA29" s="5" t="n"/>
-      <c r="BB29" s="5" t="n"/>
-      <c r="BC29" s="5" t="n"/>
-      <c r="BD29" s="5" t="n"/>
-      <c r="BE29">
-        <f>IF(COUNT(B29:BD29)=0,"",SUM(B29:BD29))</f>
-        <v/>
-      </c>
-      <c r="BF29">
-        <f>COUNT(B29:BD29)</f>
-        <v/>
-      </c>
-      <c r="BG29">
-        <f>IF(OR(BE29="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE29,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE29,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK29">
+        <f>IF(COUNT(B29:AJ29)=0,"",SUM(B29:AJ29))</f>
+        <v/>
+      </c>
+      <c r="AL29">
+        <f>COUNT(B29:AJ29)</f>
+        <v/>
+      </c>
+      <c r="AM29">
+        <f>IF(OR(AK29="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK29,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK29,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3109,36 +2349,16 @@
       <c r="AH30" s="5" t="n"/>
       <c r="AI30" s="5" t="n"/>
       <c r="AJ30" s="5" t="n"/>
-      <c r="AK30" s="5" t="n"/>
-      <c r="AL30" s="5" t="n"/>
-      <c r="AM30" s="5" t="n"/>
-      <c r="AN30" s="5" t="n"/>
-      <c r="AO30" s="5" t="n"/>
-      <c r="AP30" s="5" t="n"/>
-      <c r="AQ30" s="5" t="n"/>
-      <c r="AR30" s="5" t="n"/>
-      <c r="AS30" s="5" t="n"/>
-      <c r="AT30" s="5" t="n"/>
-      <c r="AU30" s="5" t="n"/>
-      <c r="AV30" s="5" t="n"/>
-      <c r="AW30" s="5" t="n"/>
-      <c r="AX30" s="5" t="n"/>
-      <c r="AY30" s="5" t="n"/>
-      <c r="AZ30" s="5" t="n"/>
-      <c r="BA30" s="5" t="n"/>
-      <c r="BB30" s="5" t="n"/>
-      <c r="BC30" s="5" t="n"/>
-      <c r="BD30" s="5" t="n"/>
-      <c r="BE30">
-        <f>IF(COUNT(B30:BD30)=0,"",SUM(B30:BD30))</f>
-        <v/>
-      </c>
-      <c r="BF30">
-        <f>COUNT(B30:BD30)</f>
-        <v/>
-      </c>
-      <c r="BG30">
-        <f>IF(OR(BE30="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE30,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE30,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK30">
+        <f>IF(COUNT(B30:AJ30)=0,"",SUM(B30:AJ30))</f>
+        <v/>
+      </c>
+      <c r="AL30">
+        <f>COUNT(B30:AJ30)</f>
+        <v/>
+      </c>
+      <c r="AM30">
+        <f>IF(OR(AK30="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK30,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK30,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3181,36 +2401,16 @@
       <c r="AH31" s="5" t="n"/>
       <c r="AI31" s="5" t="n"/>
       <c r="AJ31" s="5" t="n"/>
-      <c r="AK31" s="5" t="n"/>
-      <c r="AL31" s="5" t="n"/>
-      <c r="AM31" s="5" t="n"/>
-      <c r="AN31" s="5" t="n"/>
-      <c r="AO31" s="5" t="n"/>
-      <c r="AP31" s="5" t="n"/>
-      <c r="AQ31" s="5" t="n"/>
-      <c r="AR31" s="5" t="n"/>
-      <c r="AS31" s="5" t="n"/>
-      <c r="AT31" s="5" t="n"/>
-      <c r="AU31" s="5" t="n"/>
-      <c r="AV31" s="5" t="n"/>
-      <c r="AW31" s="5" t="n"/>
-      <c r="AX31" s="5" t="n"/>
-      <c r="AY31" s="5" t="n"/>
-      <c r="AZ31" s="5" t="n"/>
-      <c r="BA31" s="5" t="n"/>
-      <c r="BB31" s="5" t="n"/>
-      <c r="BC31" s="5" t="n"/>
-      <c r="BD31" s="5" t="n"/>
-      <c r="BE31">
-        <f>IF(COUNT(B31:BD31)=0,"",SUM(B31:BD31))</f>
-        <v/>
-      </c>
-      <c r="BF31">
-        <f>COUNT(B31:BD31)</f>
-        <v/>
-      </c>
-      <c r="BG31">
-        <f>IF(OR(BE31="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE31,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE31,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK31">
+        <f>IF(COUNT(B31:AJ31)=0,"",SUM(B31:AJ31))</f>
+        <v/>
+      </c>
+      <c r="AL31">
+        <f>COUNT(B31:AJ31)</f>
+        <v/>
+      </c>
+      <c r="AM31">
+        <f>IF(OR(AK31="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK31,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK31,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3253,36 +2453,16 @@
       <c r="AH32" s="5" t="n"/>
       <c r="AI32" s="5" t="n"/>
       <c r="AJ32" s="5" t="n"/>
-      <c r="AK32" s="5" t="n"/>
-      <c r="AL32" s="5" t="n"/>
-      <c r="AM32" s="5" t="n"/>
-      <c r="AN32" s="5" t="n"/>
-      <c r="AO32" s="5" t="n"/>
-      <c r="AP32" s="5" t="n"/>
-      <c r="AQ32" s="5" t="n"/>
-      <c r="AR32" s="5" t="n"/>
-      <c r="AS32" s="5" t="n"/>
-      <c r="AT32" s="5" t="n"/>
-      <c r="AU32" s="5" t="n"/>
-      <c r="AV32" s="5" t="n"/>
-      <c r="AW32" s="5" t="n"/>
-      <c r="AX32" s="5" t="n"/>
-      <c r="AY32" s="5" t="n"/>
-      <c r="AZ32" s="5" t="n"/>
-      <c r="BA32" s="5" t="n"/>
-      <c r="BB32" s="5" t="n"/>
-      <c r="BC32" s="5" t="n"/>
-      <c r="BD32" s="5" t="n"/>
-      <c r="BE32">
-        <f>IF(COUNT(B32:BD32)=0,"",SUM(B32:BD32))</f>
-        <v/>
-      </c>
-      <c r="BF32">
-        <f>COUNT(B32:BD32)</f>
-        <v/>
-      </c>
-      <c r="BG32">
-        <f>IF(OR(BE32="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE32,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE32,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK32">
+        <f>IF(COUNT(B32:AJ32)=0,"",SUM(B32:AJ32))</f>
+        <v/>
+      </c>
+      <c r="AL32">
+        <f>COUNT(B32:AJ32)</f>
+        <v/>
+      </c>
+      <c r="AM32">
+        <f>IF(OR(AK32="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK32,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK32,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3325,36 +2505,16 @@
       <c r="AH33" s="5" t="n"/>
       <c r="AI33" s="5" t="n"/>
       <c r="AJ33" s="5" t="n"/>
-      <c r="AK33" s="5" t="n"/>
-      <c r="AL33" s="5" t="n"/>
-      <c r="AM33" s="5" t="n"/>
-      <c r="AN33" s="5" t="n"/>
-      <c r="AO33" s="5" t="n"/>
-      <c r="AP33" s="5" t="n"/>
-      <c r="AQ33" s="5" t="n"/>
-      <c r="AR33" s="5" t="n"/>
-      <c r="AS33" s="5" t="n"/>
-      <c r="AT33" s="5" t="n"/>
-      <c r="AU33" s="5" t="n"/>
-      <c r="AV33" s="5" t="n"/>
-      <c r="AW33" s="5" t="n"/>
-      <c r="AX33" s="5" t="n"/>
-      <c r="AY33" s="5" t="n"/>
-      <c r="AZ33" s="5" t="n"/>
-      <c r="BA33" s="5" t="n"/>
-      <c r="BB33" s="5" t="n"/>
-      <c r="BC33" s="5" t="n"/>
-      <c r="BD33" s="5" t="n"/>
-      <c r="BE33">
-        <f>IF(COUNT(B33:BD33)=0,"",SUM(B33:BD33))</f>
-        <v/>
-      </c>
-      <c r="BF33">
-        <f>COUNT(B33:BD33)</f>
-        <v/>
-      </c>
-      <c r="BG33">
-        <f>IF(OR(BE33="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE33,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE33,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK33">
+        <f>IF(COUNT(B33:AJ33)=0,"",SUM(B33:AJ33))</f>
+        <v/>
+      </c>
+      <c r="AL33">
+        <f>COUNT(B33:AJ33)</f>
+        <v/>
+      </c>
+      <c r="AM33">
+        <f>IF(OR(AK33="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK33,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK33,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3397,36 +2557,16 @@
       <c r="AH34" s="5" t="n"/>
       <c r="AI34" s="5" t="n"/>
       <c r="AJ34" s="5" t="n"/>
-      <c r="AK34" s="5" t="n"/>
-      <c r="AL34" s="5" t="n"/>
-      <c r="AM34" s="5" t="n"/>
-      <c r="AN34" s="5" t="n"/>
-      <c r="AO34" s="5" t="n"/>
-      <c r="AP34" s="5" t="n"/>
-      <c r="AQ34" s="5" t="n"/>
-      <c r="AR34" s="5" t="n"/>
-      <c r="AS34" s="5" t="n"/>
-      <c r="AT34" s="5" t="n"/>
-      <c r="AU34" s="5" t="n"/>
-      <c r="AV34" s="5" t="n"/>
-      <c r="AW34" s="5" t="n"/>
-      <c r="AX34" s="5" t="n"/>
-      <c r="AY34" s="5" t="n"/>
-      <c r="AZ34" s="5" t="n"/>
-      <c r="BA34" s="5" t="n"/>
-      <c r="BB34" s="5" t="n"/>
-      <c r="BC34" s="5" t="n"/>
-      <c r="BD34" s="5" t="n"/>
-      <c r="BE34">
-        <f>IF(COUNT(B34:BD34)=0,"",SUM(B34:BD34))</f>
-        <v/>
-      </c>
-      <c r="BF34">
-        <f>COUNT(B34:BD34)</f>
-        <v/>
-      </c>
-      <c r="BG34">
-        <f>IF(OR(BE34="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE34,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE34,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK34">
+        <f>IF(COUNT(B34:AJ34)=0,"",SUM(B34:AJ34))</f>
+        <v/>
+      </c>
+      <c r="AL34">
+        <f>COUNT(B34:AJ34)</f>
+        <v/>
+      </c>
+      <c r="AM34">
+        <f>IF(OR(AK34="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK34,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK34,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3469,36 +2609,16 @@
       <c r="AH35" s="5" t="n"/>
       <c r="AI35" s="5" t="n"/>
       <c r="AJ35" s="5" t="n"/>
-      <c r="AK35" s="5" t="n"/>
-      <c r="AL35" s="5" t="n"/>
-      <c r="AM35" s="5" t="n"/>
-      <c r="AN35" s="5" t="n"/>
-      <c r="AO35" s="5" t="n"/>
-      <c r="AP35" s="5" t="n"/>
-      <c r="AQ35" s="5" t="n"/>
-      <c r="AR35" s="5" t="n"/>
-      <c r="AS35" s="5" t="n"/>
-      <c r="AT35" s="5" t="n"/>
-      <c r="AU35" s="5" t="n"/>
-      <c r="AV35" s="5" t="n"/>
-      <c r="AW35" s="5" t="n"/>
-      <c r="AX35" s="5" t="n"/>
-      <c r="AY35" s="5" t="n"/>
-      <c r="AZ35" s="5" t="n"/>
-      <c r="BA35" s="5" t="n"/>
-      <c r="BB35" s="5" t="n"/>
-      <c r="BC35" s="5" t="n"/>
-      <c r="BD35" s="5" t="n"/>
-      <c r="BE35">
-        <f>IF(COUNT(B35:BD35)=0,"",SUM(B35:BD35))</f>
-        <v/>
-      </c>
-      <c r="BF35">
-        <f>COUNT(B35:BD35)</f>
-        <v/>
-      </c>
-      <c r="BG35">
-        <f>IF(OR(BE35="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE35,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE35,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK35">
+        <f>IF(COUNT(B35:AJ35)=0,"",SUM(B35:AJ35))</f>
+        <v/>
+      </c>
+      <c r="AL35">
+        <f>COUNT(B35:AJ35)</f>
+        <v/>
+      </c>
+      <c r="AM35">
+        <f>IF(OR(AK35="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK35,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK35,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3541,36 +2661,16 @@
       <c r="AH36" s="5" t="n"/>
       <c r="AI36" s="5" t="n"/>
       <c r="AJ36" s="5" t="n"/>
-      <c r="AK36" s="5" t="n"/>
-      <c r="AL36" s="5" t="n"/>
-      <c r="AM36" s="5" t="n"/>
-      <c r="AN36" s="5" t="n"/>
-      <c r="AO36" s="5" t="n"/>
-      <c r="AP36" s="5" t="n"/>
-      <c r="AQ36" s="5" t="n"/>
-      <c r="AR36" s="5" t="n"/>
-      <c r="AS36" s="5" t="n"/>
-      <c r="AT36" s="5" t="n"/>
-      <c r="AU36" s="5" t="n"/>
-      <c r="AV36" s="5" t="n"/>
-      <c r="AW36" s="5" t="n"/>
-      <c r="AX36" s="5" t="n"/>
-      <c r="AY36" s="5" t="n"/>
-      <c r="AZ36" s="5" t="n"/>
-      <c r="BA36" s="5" t="n"/>
-      <c r="BB36" s="5" t="n"/>
-      <c r="BC36" s="5" t="n"/>
-      <c r="BD36" s="5" t="n"/>
-      <c r="BE36">
-        <f>IF(COUNT(B36:BD36)=0,"",SUM(B36:BD36))</f>
-        <v/>
-      </c>
-      <c r="BF36">
-        <f>COUNT(B36:BD36)</f>
-        <v/>
-      </c>
-      <c r="BG36">
-        <f>IF(OR(BE36="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE36,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE36,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK36">
+        <f>IF(COUNT(B36:AJ36)=0,"",SUM(B36:AJ36))</f>
+        <v/>
+      </c>
+      <c r="AL36">
+        <f>COUNT(B36:AJ36)</f>
+        <v/>
+      </c>
+      <c r="AM36">
+        <f>IF(OR(AK36="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK36,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK36,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3613,36 +2713,16 @@
       <c r="AH37" s="5" t="n"/>
       <c r="AI37" s="5" t="n"/>
       <c r="AJ37" s="5" t="n"/>
-      <c r="AK37" s="5" t="n"/>
-      <c r="AL37" s="5" t="n"/>
-      <c r="AM37" s="5" t="n"/>
-      <c r="AN37" s="5" t="n"/>
-      <c r="AO37" s="5" t="n"/>
-      <c r="AP37" s="5" t="n"/>
-      <c r="AQ37" s="5" t="n"/>
-      <c r="AR37" s="5" t="n"/>
-      <c r="AS37" s="5" t="n"/>
-      <c r="AT37" s="5" t="n"/>
-      <c r="AU37" s="5" t="n"/>
-      <c r="AV37" s="5" t="n"/>
-      <c r="AW37" s="5" t="n"/>
-      <c r="AX37" s="5" t="n"/>
-      <c r="AY37" s="5" t="n"/>
-      <c r="AZ37" s="5" t="n"/>
-      <c r="BA37" s="5" t="n"/>
-      <c r="BB37" s="5" t="n"/>
-      <c r="BC37" s="5" t="n"/>
-      <c r="BD37" s="5" t="n"/>
-      <c r="BE37">
-        <f>IF(COUNT(B37:BD37)=0,"",SUM(B37:BD37))</f>
-        <v/>
-      </c>
-      <c r="BF37">
-        <f>COUNT(B37:BD37)</f>
-        <v/>
-      </c>
-      <c r="BG37">
-        <f>IF(OR(BE37="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE37,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE37,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK37">
+        <f>IF(COUNT(B37:AJ37)=0,"",SUM(B37:AJ37))</f>
+        <v/>
+      </c>
+      <c r="AL37">
+        <f>COUNT(B37:AJ37)</f>
+        <v/>
+      </c>
+      <c r="AM37">
+        <f>IF(OR(AK37="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK37,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK37,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3685,36 +2765,16 @@
       <c r="AH38" s="5" t="n"/>
       <c r="AI38" s="5" t="n"/>
       <c r="AJ38" s="5" t="n"/>
-      <c r="AK38" s="5" t="n"/>
-      <c r="AL38" s="5" t="n"/>
-      <c r="AM38" s="5" t="n"/>
-      <c r="AN38" s="5" t="n"/>
-      <c r="AO38" s="5" t="n"/>
-      <c r="AP38" s="5" t="n"/>
-      <c r="AQ38" s="5" t="n"/>
-      <c r="AR38" s="5" t="n"/>
-      <c r="AS38" s="5" t="n"/>
-      <c r="AT38" s="5" t="n"/>
-      <c r="AU38" s="5" t="n"/>
-      <c r="AV38" s="5" t="n"/>
-      <c r="AW38" s="5" t="n"/>
-      <c r="AX38" s="5" t="n"/>
-      <c r="AY38" s="5" t="n"/>
-      <c r="AZ38" s="5" t="n"/>
-      <c r="BA38" s="5" t="n"/>
-      <c r="BB38" s="5" t="n"/>
-      <c r="BC38" s="5" t="n"/>
-      <c r="BD38" s="5" t="n"/>
-      <c r="BE38">
-        <f>IF(COUNT(B38:BD38)=0,"",SUM(B38:BD38))</f>
-        <v/>
-      </c>
-      <c r="BF38">
-        <f>COUNT(B38:BD38)</f>
-        <v/>
-      </c>
-      <c r="BG38">
-        <f>IF(OR(BE38="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE38,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE38,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK38">
+        <f>IF(COUNT(B38:AJ38)=0,"",SUM(B38:AJ38))</f>
+        <v/>
+      </c>
+      <c r="AL38">
+        <f>COUNT(B38:AJ38)</f>
+        <v/>
+      </c>
+      <c r="AM38">
+        <f>IF(OR(AK38="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK38,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK38,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3757,36 +2817,16 @@
       <c r="AH39" s="5" t="n"/>
       <c r="AI39" s="5" t="n"/>
       <c r="AJ39" s="5" t="n"/>
-      <c r="AK39" s="5" t="n"/>
-      <c r="AL39" s="5" t="n"/>
-      <c r="AM39" s="5" t="n"/>
-      <c r="AN39" s="5" t="n"/>
-      <c r="AO39" s="5" t="n"/>
-      <c r="AP39" s="5" t="n"/>
-      <c r="AQ39" s="5" t="n"/>
-      <c r="AR39" s="5" t="n"/>
-      <c r="AS39" s="5" t="n"/>
-      <c r="AT39" s="5" t="n"/>
-      <c r="AU39" s="5" t="n"/>
-      <c r="AV39" s="5" t="n"/>
-      <c r="AW39" s="5" t="n"/>
-      <c r="AX39" s="5" t="n"/>
-      <c r="AY39" s="5" t="n"/>
-      <c r="AZ39" s="5" t="n"/>
-      <c r="BA39" s="5" t="n"/>
-      <c r="BB39" s="5" t="n"/>
-      <c r="BC39" s="5" t="n"/>
-      <c r="BD39" s="5" t="n"/>
-      <c r="BE39">
-        <f>IF(COUNT(B39:BD39)=0,"",SUM(B39:BD39))</f>
-        <v/>
-      </c>
-      <c r="BF39">
-        <f>COUNT(B39:BD39)</f>
-        <v/>
-      </c>
-      <c r="BG39">
-        <f>IF(OR(BE39="",COUNT($BE$5:$BE$39)&lt;3),"",IF(RANK(BE39,$BE$5:$BE$39,0)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"top",IF(RANK(BE39,$BE$5:$BE$39,1)&lt;=ROUND(COUNT($BE$5:$BE$39)/3,0),"bottom","middle")))</f>
+      <c r="AK39">
+        <f>IF(COUNT(B39:AJ39)=0,"",SUM(B39:AJ39))</f>
+        <v/>
+      </c>
+      <c r="AL39">
+        <f>COUNT(B39:AJ39)</f>
+        <v/>
+      </c>
+      <c r="AM39">
+        <f>IF(OR(AK39="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK39,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK39,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3801,7 +2841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="13" max="13"/>
@@ -3895,12 +2935,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fill in the blank</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3910,7 +2950,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G5">
@@ -3926,11 +2966,11 @@
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="L5" s="6">
@@ -3955,7 +2995,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fill in the blank</t>
+          <t>Order the steps</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3970,7 +3010,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>c, b, e, f, a, d</t>
         </is>
       </c>
       <c r="G6">
@@ -3986,11 +3026,11 @@
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="L6" s="6">
@@ -4020,7 +3060,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4030,7 +3070,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MergeError</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G7">
@@ -4046,11 +3086,11 @@
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="L7" s="6">
@@ -4075,7 +3115,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>Fill in the blank</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4090,7 +3130,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G8">
@@ -4106,11 +3146,11 @@
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="L8" s="6">
@@ -4135,22 +3175,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G9">
@@ -4166,11 +3206,11 @@
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="L9" s="6">
@@ -4195,22 +3235,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G10">
@@ -4226,11 +3266,11 @@
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="L10" s="6">
@@ -4251,26 +3291,26 @@
         <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G11">
@@ -4286,11 +3326,11 @@
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="L11" s="6">
@@ -4311,11 +3351,11 @@
         <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>Order the steps</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4325,12 +3365,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>c, e, a, d, b</t>
         </is>
       </c>
       <c r="G12">
@@ -4346,11 +3386,11 @@
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="L12" s="6">
@@ -4371,26 +3411,26 @@
         <v>9</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G13">
@@ -4406,11 +3446,11 @@
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="L13" s="6">
@@ -4431,26 +3471,26 @@
         <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G14">
@@ -4466,11 +3506,11 @@
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="L14" s="6">
@@ -4491,26 +3531,26 @@
         <v>11</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>More than one correct</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>b, d</t>
         </is>
       </c>
       <c r="G15">
@@ -4526,11 +3566,11 @@
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="L15" s="6">
@@ -4551,16 +3591,16 @@
         <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4570,7 +3610,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G16">
@@ -4586,11 +3626,11 @@
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="L16" s="6">
@@ -4611,21 +3651,21 @@
         <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4646,11 +3686,11 @@
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="L17" s="6">
@@ -4671,11 +3711,11 @@
         <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4690,7 +3730,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>a, c, d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G18">
@@ -4706,11 +3746,11 @@
         <v/>
       </c>
       <c r="J18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="L18" s="6">
@@ -4731,26 +3771,26 @@
         <v>15</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Applied maths</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G19">
@@ -4766,11 +3806,11 @@
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="L19" s="6">
@@ -4791,26 +3831,26 @@
         <v>16</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Order the steps</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>c, b, e, f, a, d</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G20">
@@ -4826,11 +3866,11 @@
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="L20" s="6">
@@ -4851,26 +3891,26 @@
         <v>17</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>346</t>
         </is>
       </c>
       <c r="G21">
@@ -4886,11 +3926,11 @@
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="L21" s="6">
@@ -4911,11 +3951,11 @@
         <v>18</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4925,7 +3965,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4946,11 +3986,11 @@
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="L22" s="6">
@@ -4971,11 +4011,11 @@
         <v>19</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4990,7 +4030,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>a, e</t>
         </is>
       </c>
       <c r="G23">
@@ -5006,11 +4046,11 @@
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="L23" s="6">
@@ -5031,11 +4071,11 @@
         <v>20</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5050,7 +4090,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G24">
@@ -5066,11 +4106,11 @@
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="L24" s="6">
@@ -5091,16 +4131,16 @@
         <v>21</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5110,7 +4150,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>b, c, d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G25">
@@ -5126,11 +4166,11 @@
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="L25" s="6">
@@ -5151,11 +4191,11 @@
         <v>22</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5165,12 +4205,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>b, d</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G26">
@@ -5186,11 +4226,11 @@
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="L26" s="6">
@@ -5211,11 +4251,11 @@
         <v>23</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>Match the following</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5225,12 +4265,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1,050</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G27">
@@ -5246,11 +4286,11 @@
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="L27" s="6">
@@ -5271,11 +4311,11 @@
         <v>24</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>Match the following</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5285,12 +4325,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1,020</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G28">
@@ -5306,11 +4346,11 @@
         <v/>
       </c>
       <c r="J28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="L28" s="6">
@@ -5331,11 +4371,11 @@
         <v>25</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>Match the following</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5350,7 +4390,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>f</t>
         </is>
       </c>
       <c r="G29">
@@ -5366,11 +4406,11 @@
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="L29" s="6">
@@ -5391,11 +4431,11 @@
         <v>26</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>Match the following</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5405,12 +4445,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G30">
@@ -5426,11 +4466,11 @@
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="L30" s="6">
@@ -5451,26 +4491,26 @@
         <v>27</v>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Applied maths</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rs 21 lakh, which overstates collections by Rs 1 lakh.</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G31">
@@ -5486,11 +4526,11 @@
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="L31" s="6">
@@ -5511,7 +4551,7 @@
         <v>28</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5520,17 +4560,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G32">
@@ -5546,11 +4586,11 @@
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="L32" s="6">
@@ -5571,11 +4611,11 @@
         <v>29</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Applied maths</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5585,12 +4625,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>0.60 dollars a trip</t>
         </is>
       </c>
       <c r="G33">
@@ -5606,11 +4646,11 @@
         <v/>
       </c>
       <c r="J33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="L33" s="6">
@@ -5631,7 +4671,7 @@
         <v>30</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5640,17 +4680,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G34">
@@ -5666,11 +4706,11 @@
         <v/>
       </c>
       <c r="J34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="L34" s="6">
@@ -5691,7 +4731,7 @@
         <v>31</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5705,12 +4745,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G35">
@@ -5726,11 +4766,11 @@
         <v/>
       </c>
       <c r="J35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="L35" s="6">
@@ -5751,11 +4791,11 @@
         <v>32</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5770,7 +4810,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>a, c, d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G36">
@@ -5786,11 +4826,11 @@
         <v/>
       </c>
       <c r="J36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="L36" s="6">
@@ -5811,11 +4851,11 @@
         <v>33</v>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5825,12 +4865,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>a, b, c</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G37">
@@ -5846,11 +4886,11 @@
         <v/>
       </c>
       <c r="J37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="K37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="L37" s="6">
@@ -5871,11 +4911,11 @@
         <v>34</v>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5885,12 +4925,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G38">
@@ -5906,11 +4946,11 @@
         <v/>
       </c>
       <c r="J38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
         <v/>
       </c>
       <c r="K38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
         <v/>
       </c>
       <c r="L38" s="6">
@@ -5931,11 +4971,11 @@
         <v>35</v>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5945,12 +4985,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G39">
@@ -5966,11 +5006,11 @@
         <v/>
       </c>
       <c r="J39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
         <v/>
       </c>
       <c r="K39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
         <v/>
       </c>
       <c r="L39" s="6">
@@ -5983,1206 +5023,6 @@
       </c>
       <c r="N39">
         <f>IF(H39=0,"",I39+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G40">
-        <f>COUNTIF(Marks!AK$5:AK$39,1)</f>
-        <v/>
-      </c>
-      <c r="H40">
-        <f>COUNT(Marks!AK$5:AK$39)</f>
-        <v/>
-      </c>
-      <c r="I40" s="6">
-        <f>IF(H40=0,"",G40/H40)</f>
-        <v/>
-      </c>
-      <c r="J40" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AK$5:AK$39)))</f>
-        <v/>
-      </c>
-      <c r="K40" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AK$5:AK$39)))</f>
-        <v/>
-      </c>
-      <c r="L40" s="6">
-        <f>IF(OR(J40="",K40=""),"",J40-K40)</f>
-        <v/>
-      </c>
-      <c r="M40">
-        <f>IF(H40=0,"",IF(I40&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L40&lt;&gt;"",N(L40)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N40">
-        <f>IF(H40=0,"",I40+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G41">
-        <f>COUNTIF(Marks!AL$5:AL$39,1)</f>
-        <v/>
-      </c>
-      <c r="H41">
-        <f>COUNT(Marks!AL$5:AL$39)</f>
-        <v/>
-      </c>
-      <c r="I41" s="6">
-        <f>IF(H41=0,"",G41/H41)</f>
-        <v/>
-      </c>
-      <c r="J41" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AL$5:AL$39)))</f>
-        <v/>
-      </c>
-      <c r="K41" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AL$5:AL$39)))</f>
-        <v/>
-      </c>
-      <c r="L41" s="6">
-        <f>IF(OR(J41="",K41=""),"",J41-K41)</f>
-        <v/>
-      </c>
-      <c r="M41">
-        <f>IF(H41=0,"",IF(I41&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L41&lt;&gt;"",N(L41)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N41">
-        <f>IF(H41=0,"",I41+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" t="n">
-        <v>4</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Applied maths</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>51 under RANK(); 50 under ROW_NUMBER().</t>
-        </is>
-      </c>
-      <c r="G42">
-        <f>COUNTIF(Marks!AM$5:AM$39,1)</f>
-        <v/>
-      </c>
-      <c r="H42">
-        <f>COUNT(Marks!AM$5:AM$39)</f>
-        <v/>
-      </c>
-      <c r="I42" s="6">
-        <f>IF(H42=0,"",G42/H42)</f>
-        <v/>
-      </c>
-      <c r="J42" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AM$5:AM$39)))</f>
-        <v/>
-      </c>
-      <c r="K42" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AM$5:AM$39)))</f>
-        <v/>
-      </c>
-      <c r="L42" s="6">
-        <f>IF(OR(J42="",K42=""),"",J42-K42)</f>
-        <v/>
-      </c>
-      <c r="M42">
-        <f>IF(H42=0,"",IF(I42&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L42&lt;&gt;"",N(L42)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N42">
-        <f>IF(H42=0,"",I42+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" t="n">
-        <v>4</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Applied maths</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>A fall of Rs 800, then a fall of Rs 300; the flag fires.</t>
-        </is>
-      </c>
-      <c r="G43">
-        <f>COUNTIF(Marks!AN$5:AN$39,1)</f>
-        <v/>
-      </c>
-      <c r="H43">
-        <f>COUNT(Marks!AN$5:AN$39)</f>
-        <v/>
-      </c>
-      <c r="I43" s="6">
-        <f>IF(H43=0,"",G43/H43)</f>
-        <v/>
-      </c>
-      <c r="J43" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AN$5:AN$39)))</f>
-        <v/>
-      </c>
-      <c r="K43" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AN$5:AN$39)))</f>
-        <v/>
-      </c>
-      <c r="L43" s="6">
-        <f>IF(OR(J43="",K43=""),"",J43-K43)</f>
-        <v/>
-      </c>
-      <c r="M43">
-        <f>IF(H43=0,"",IF(I43&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L43&lt;&gt;"",N(L43)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N43">
-        <f>IF(H43=0,"",I43+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" t="n">
-        <v>5</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G44">
-        <f>COUNTIF(Marks!AO$5:AO$39,1)</f>
-        <v/>
-      </c>
-      <c r="H44">
-        <f>COUNT(Marks!AO$5:AO$39)</f>
-        <v/>
-      </c>
-      <c r="I44" s="6">
-        <f>IF(H44=0,"",G44/H44)</f>
-        <v/>
-      </c>
-      <c r="J44" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AO$5:AO$39)))</f>
-        <v/>
-      </c>
-      <c r="K44" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AO$5:AO$39)))</f>
-        <v/>
-      </c>
-      <c r="L44" s="6">
-        <f>IF(OR(J44="",K44=""),"",J44-K44)</f>
-        <v/>
-      </c>
-      <c r="M44">
-        <f>IF(H44=0,"",IF(I44&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L44&lt;&gt;"",N(L44)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N44">
-        <f>IF(H44=0,"",I44+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" t="n">
-        <v>5</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="G45">
-        <f>COUNTIF(Marks!AP$5:AP$39,1)</f>
-        <v/>
-      </c>
-      <c r="H45">
-        <f>COUNT(Marks!AP$5:AP$39)</f>
-        <v/>
-      </c>
-      <c r="I45" s="6">
-        <f>IF(H45=0,"",G45/H45)</f>
-        <v/>
-      </c>
-      <c r="J45" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AP$5:AP$39)))</f>
-        <v/>
-      </c>
-      <c r="K45" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AP$5:AP$39)))</f>
-        <v/>
-      </c>
-      <c r="L45" s="6">
-        <f>IF(OR(J45="",K45=""),"",J45-K45)</f>
-        <v/>
-      </c>
-      <c r="M45">
-        <f>IF(H45=0,"",IF(I45&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L45&lt;&gt;"",N(L45)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N45">
-        <f>IF(H45=0,"",I45+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="G46">
-        <f>COUNTIF(Marks!AQ$5:AQ$39,1)</f>
-        <v/>
-      </c>
-      <c r="H46">
-        <f>COUNT(Marks!AQ$5:AQ$39)</f>
-        <v/>
-      </c>
-      <c r="I46" s="6">
-        <f>IF(H46=0,"",G46/H46)</f>
-        <v/>
-      </c>
-      <c r="J46" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
-        <v/>
-      </c>
-      <c r="K46" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
-        <v/>
-      </c>
-      <c r="L46" s="6">
-        <f>IF(OR(J46="",K46=""),"",J46-K46)</f>
-        <v/>
-      </c>
-      <c r="M46">
-        <f>IF(H46=0,"",IF(I46&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L46&lt;&gt;"",N(L46)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N46">
-        <f>IF(H46=0,"",I46+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" t="n">
-        <v>5</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G47">
-        <f>COUNTIF(Marks!AR$5:AR$39,1)</f>
-        <v/>
-      </c>
-      <c r="H47">
-        <f>COUNT(Marks!AR$5:AR$39)</f>
-        <v/>
-      </c>
-      <c r="I47" s="6">
-        <f>IF(H47=0,"",G47/H47)</f>
-        <v/>
-      </c>
-      <c r="J47" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AR$5:AR$39)))</f>
-        <v/>
-      </c>
-      <c r="K47" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AR$5:AR$39)))</f>
-        <v/>
-      </c>
-      <c r="L47" s="6">
-        <f>IF(OR(J47="",K47=""),"",J47-K47)</f>
-        <v/>
-      </c>
-      <c r="M47">
-        <f>IF(H47=0,"",IF(I47&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L47&lt;&gt;"",N(L47)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N47">
-        <f>IF(H47=0,"",I47+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>More than one correct</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>a, b, d</t>
-        </is>
-      </c>
-      <c r="G48">
-        <f>COUNTIF(Marks!AS$5:AS$39,1)</f>
-        <v/>
-      </c>
-      <c r="H48">
-        <f>COUNT(Marks!AS$5:AS$39)</f>
-        <v/>
-      </c>
-      <c r="I48" s="6">
-        <f>IF(H48=0,"",G48/H48)</f>
-        <v/>
-      </c>
-      <c r="J48" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AS$5:AS$39)))</f>
-        <v/>
-      </c>
-      <c r="K48" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AS$5:AS$39)))</f>
-        <v/>
-      </c>
-      <c r="L48" s="6">
-        <f>IF(OR(J48="",K48=""),"",J48-K48)</f>
-        <v/>
-      </c>
-      <c r="M48">
-        <f>IF(H48=0,"",IF(I48&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L48&lt;&gt;"",N(L48)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N48">
-        <f>IF(H48=0,"",I48+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" t="n">
-        <v>5</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>More than one correct</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>a, b, c</t>
-        </is>
-      </c>
-      <c r="G49">
-        <f>COUNTIF(Marks!AT$5:AT$39,1)</f>
-        <v/>
-      </c>
-      <c r="H49">
-        <f>COUNT(Marks!AT$5:AT$39)</f>
-        <v/>
-      </c>
-      <c r="I49" s="6">
-        <f>IF(H49=0,"",G49/H49)</f>
-        <v/>
-      </c>
-      <c r="J49" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AT$5:AT$39)))</f>
-        <v/>
-      </c>
-      <c r="K49" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AT$5:AT$39)))</f>
-        <v/>
-      </c>
-      <c r="L49" s="6">
-        <f>IF(OR(J49="",K49=""),"",J49-K49)</f>
-        <v/>
-      </c>
-      <c r="M49">
-        <f>IF(H49=0,"",IF(I49&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L49&lt;&gt;"",N(L49)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N49">
-        <f>IF(H49=0,"",I49+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" t="n">
-        <v>5</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1,060</t>
-        </is>
-      </c>
-      <c r="G50">
-        <f>COUNTIF(Marks!AU$5:AU$39,1)</f>
-        <v/>
-      </c>
-      <c r="H50">
-        <f>COUNT(Marks!AU$5:AU$39)</f>
-        <v/>
-      </c>
-      <c r="I50" s="6">
-        <f>IF(H50=0,"",G50/H50)</f>
-        <v/>
-      </c>
-      <c r="J50" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AU$5:AU$39)))</f>
-        <v/>
-      </c>
-      <c r="K50" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AU$5:AU$39)))</f>
-        <v/>
-      </c>
-      <c r="L50" s="6">
-        <f>IF(OR(J50="",K50=""),"",J50-K50)</f>
-        <v/>
-      </c>
-      <c r="M50">
-        <f>IF(H50=0,"",IF(I50&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L50&lt;&gt;"",N(L50)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N50">
-        <f>IF(H50=0,"",I50+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" t="n">
-        <v>5</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="G51">
-        <f>COUNTIF(Marks!AV$5:AV$39,1)</f>
-        <v/>
-      </c>
-      <c r="H51">
-        <f>COUNT(Marks!AV$5:AV$39)</f>
-        <v/>
-      </c>
-      <c r="I51" s="6">
-        <f>IF(H51=0,"",G51/H51)</f>
-        <v/>
-      </c>
-      <c r="J51" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AV$5:AV$39)))</f>
-        <v/>
-      </c>
-      <c r="K51" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AV$5:AV$39)))</f>
-        <v/>
-      </c>
-      <c r="L51" s="6">
-        <f>IF(OR(J51="",K51=""),"",J51-K51)</f>
-        <v/>
-      </c>
-      <c r="M51">
-        <f>IF(H51=0,"",IF(I51&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L51&lt;&gt;"",N(L51)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N51">
-        <f>IF(H51=0,"",I51+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" t="n">
-        <v>5</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G52">
-        <f>COUNTIF(Marks!AW$5:AW$39,1)</f>
-        <v/>
-      </c>
-      <c r="H52">
-        <f>COUNT(Marks!AW$5:AW$39)</f>
-        <v/>
-      </c>
-      <c r="I52" s="6">
-        <f>IF(H52=0,"",G52/H52)</f>
-        <v/>
-      </c>
-      <c r="J52" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AW$5:AW$39)))</f>
-        <v/>
-      </c>
-      <c r="K52" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AW$5:AW$39)))</f>
-        <v/>
-      </c>
-      <c r="L52" s="6">
-        <f>IF(OR(J52="",K52=""),"",J52-K52)</f>
-        <v/>
-      </c>
-      <c r="M52">
-        <f>IF(H52=0,"",IF(I52&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L52&lt;&gt;"",N(L52)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N52">
-        <f>IF(H52=0,"",I52+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" t="n">
-        <v>5</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="G53">
-        <f>COUNTIF(Marks!AX$5:AX$39,1)</f>
-        <v/>
-      </c>
-      <c r="H53">
-        <f>COUNT(Marks!AX$5:AX$39)</f>
-        <v/>
-      </c>
-      <c r="I53" s="6">
-        <f>IF(H53=0,"",G53/H53)</f>
-        <v/>
-      </c>
-      <c r="J53" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AX$5:AX$39)))</f>
-        <v/>
-      </c>
-      <c r="K53" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AX$5:AX$39)))</f>
-        <v/>
-      </c>
-      <c r="L53" s="6">
-        <f>IF(OR(J53="",K53=""),"",J53-K53)</f>
-        <v/>
-      </c>
-      <c r="M53">
-        <f>IF(H53=0,"",IF(I53&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L53&lt;&gt;"",N(L53)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N53">
-        <f>IF(H53=0,"",I53+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" t="n">
-        <v>5</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Applied maths</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>400 rows; 2.5 orders per customer.</t>
-        </is>
-      </c>
-      <c r="G54">
-        <f>COUNTIF(Marks!AY$5:AY$39,1)</f>
-        <v/>
-      </c>
-      <c r="H54">
-        <f>COUNT(Marks!AY$5:AY$39)</f>
-        <v/>
-      </c>
-      <c r="I54" s="6">
-        <f>IF(H54=0,"",G54/H54)</f>
-        <v/>
-      </c>
-      <c r="J54" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AY$5:AY$39)))</f>
-        <v/>
-      </c>
-      <c r="K54" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AY$5:AY$39)))</f>
-        <v/>
-      </c>
-      <c r="L54" s="6">
-        <f>IF(OR(J54="",K54=""),"",J54-K54)</f>
-        <v/>
-      </c>
-      <c r="M54">
-        <f>IF(H54=0,"",IF(I54&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L54&lt;&gt;"",N(L54)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N54">
-        <f>IF(H54=0,"",I54+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" t="n">
-        <v>5</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Order the steps</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>b, c, a</t>
-        </is>
-      </c>
-      <c r="G55">
-        <f>COUNTIF(Marks!AZ$5:AZ$39,1)</f>
-        <v/>
-      </c>
-      <c r="H55">
-        <f>COUNT(Marks!AZ$5:AZ$39)</f>
-        <v/>
-      </c>
-      <c r="I55" s="6">
-        <f>IF(H55=0,"",G55/H55)</f>
-        <v/>
-      </c>
-      <c r="J55" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
-        <v/>
-      </c>
-      <c r="K55" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
-        <v/>
-      </c>
-      <c r="L55" s="6">
-        <f>IF(OR(J55="",K55=""),"",J55-K55)</f>
-        <v/>
-      </c>
-      <c r="M55">
-        <f>IF(H55=0,"",IF(I55&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L55&lt;&gt;"",N(L55)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N55">
-        <f>IF(H55=0,"",I55+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" t="n">
-        <v>6</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G56">
-        <f>COUNTIF(Marks!BA$5:BA$39,1)</f>
-        <v/>
-      </c>
-      <c r="H56">
-        <f>COUNT(Marks!BA$5:BA$39)</f>
-        <v/>
-      </c>
-      <c r="I56" s="6">
-        <f>IF(H56=0,"",G56/H56)</f>
-        <v/>
-      </c>
-      <c r="J56" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BA$5:BA$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!BA$5:BA$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BA$5:BA$39)))</f>
-        <v/>
-      </c>
-      <c r="K56" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BA$5:BA$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!BA$5:BA$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BA$5:BA$39)))</f>
-        <v/>
-      </c>
-      <c r="L56" s="6">
-        <f>IF(OR(J56="",K56=""),"",J56-K56)</f>
-        <v/>
-      </c>
-      <c r="M56">
-        <f>IF(H56=0,"",IF(I56&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L56&lt;&gt;"",N(L56)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N56">
-        <f>IF(H56=0,"",I56+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" t="n">
-        <v>6</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="G57">
-        <f>COUNTIF(Marks!BB$5:BB$39,1)</f>
-        <v/>
-      </c>
-      <c r="H57">
-        <f>COUNT(Marks!BB$5:BB$39)</f>
-        <v/>
-      </c>
-      <c r="I57" s="6">
-        <f>IF(H57=0,"",G57/H57)</f>
-        <v/>
-      </c>
-      <c r="J57" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BB$5:BB$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!BB$5:BB$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BB$5:BB$39)))</f>
-        <v/>
-      </c>
-      <c r="K57" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BB$5:BB$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!BB$5:BB$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BB$5:BB$39)))</f>
-        <v/>
-      </c>
-      <c r="L57" s="6">
-        <f>IF(OR(J57="",K57=""),"",J57-K57)</f>
-        <v/>
-      </c>
-      <c r="M57">
-        <f>IF(H57=0,"",IF(I57&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L57&lt;&gt;"",N(L57)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N57">
-        <f>IF(H57=0,"",I57+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" t="n">
-        <v>6</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="G58">
-        <f>COUNTIF(Marks!BC$5:BC$39,1)</f>
-        <v/>
-      </c>
-      <c r="H58">
-        <f>COUNT(Marks!BC$5:BC$39)</f>
-        <v/>
-      </c>
-      <c r="I58" s="6">
-        <f>IF(H58=0,"",G58/H58)</f>
-        <v/>
-      </c>
-      <c r="J58" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BC$5:BC$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!BC$5:BC$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BC$5:BC$39)))</f>
-        <v/>
-      </c>
-      <c r="K58" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BC$5:BC$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!BC$5:BC$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BC$5:BC$39)))</f>
-        <v/>
-      </c>
-      <c r="L58" s="6">
-        <f>IF(OR(J58="",K58=""),"",J58-K58)</f>
-        <v/>
-      </c>
-      <c r="M58">
-        <f>IF(H58=0,"",IF(I58&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L58&lt;&gt;"",N(L58)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N58">
-        <f>IF(H58=0,"",I58+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" t="n">
-        <v>6</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G59">
-        <f>COUNTIF(Marks!BD$5:BD$39,1)</f>
-        <v/>
-      </c>
-      <c r="H59">
-        <f>COUNT(Marks!BD$5:BD$39)</f>
-        <v/>
-      </c>
-      <c r="I59" s="6">
-        <f>IF(H59=0,"",G59/H59)</f>
-        <v/>
-      </c>
-      <c r="J59" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BD$5:BD$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="top")*(Marks!BD$5:BD$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="top")*ISNUMBER(Marks!BD$5:BD$39)))</f>
-        <v/>
-      </c>
-      <c r="K59" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BD$5:BD$39))=0,"",SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*(Marks!BD$5:BD$39=1))/SUMPRODUCT((Marks!$BG$5:$BG$39="bottom")*ISNUMBER(Marks!BD$5:BD$39)))</f>
-        <v/>
-      </c>
-      <c r="L59" s="6">
-        <f>IF(OR(J59="",K59=""),"",J59-K59)</f>
-        <v/>
-      </c>
-      <c r="M59">
-        <f>IF(H59=0,"",IF(I59&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L59&lt;&gt;"",N(L59)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N59">
-        <f>IF(H59=0,"",I59+ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -7197,7 +5037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -7212,7 +5052,7 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>IF(SUM(Items!H5:H59)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
+        <f>IF(SUM(Items!H5:H39)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
         <v/>
       </c>
     </row>
@@ -7253,23 +5093,23 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A5,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A5),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A5,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A5),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(B5="","",INDEX(Items!$I$5:$I$59,MATCH(B5,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$I$5:$I$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D5">
-        <f>IF(B5="","",INDEX(Items!$B$5:$B$59,MATCH(B5,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$B$5:$B$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E5">
-        <f>IF(B5="","",INDEX(Items!$E$5:$E$59,MATCH(B5,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$E$5:$E$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F5">
-        <f>IF(B5="","",INDEX(Items!$M$5:$M$59,MATCH(B5,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$M$5:$M$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7278,23 +5118,23 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A6,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A6),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A6,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A6),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(B6="","",INDEX(Items!$I$5:$I$59,MATCH(B6,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$I$5:$I$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IF(B6="","",INDEX(Items!$B$5:$B$59,MATCH(B6,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$B$5:$B$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E6">
-        <f>IF(B6="","",INDEX(Items!$E$5:$E$59,MATCH(B6,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$E$5:$E$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IF(B6="","",INDEX(Items!$M$5:$M$59,MATCH(B6,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$M$5:$M$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7303,23 +5143,23 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A7,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A7),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A7,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A7),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(B7="","",INDEX(Items!$I$5:$I$59,MATCH(B7,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$I$5:$I$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D7">
-        <f>IF(B7="","",INDEX(Items!$B$5:$B$59,MATCH(B7,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$B$5:$B$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E7">
-        <f>IF(B7="","",INDEX(Items!$E$5:$E$59,MATCH(B7,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$E$5:$E$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F7">
-        <f>IF(B7="","",INDEX(Items!$M$5:$M$59,MATCH(B7,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$M$5:$M$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7328,23 +5168,23 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A8,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A8),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A8,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A8),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(B8="","",INDEX(Items!$I$5:$I$59,MATCH(B8,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$I$5:$I$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D8">
-        <f>IF(B8="","",INDEX(Items!$B$5:$B$59,MATCH(B8,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$B$5:$B$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E8">
-        <f>IF(B8="","",INDEX(Items!$E$5:$E$59,MATCH(B8,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$E$5:$E$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F8">
-        <f>IF(B8="","",INDEX(Items!$M$5:$M$59,MATCH(B8,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$M$5:$M$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7353,23 +5193,23 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A9,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A9),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A9,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A9),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(B9="","",INDEX(Items!$I$5:$I$59,MATCH(B9,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$I$5:$I$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D9">
-        <f>IF(B9="","",INDEX(Items!$B$5:$B$59,MATCH(B9,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$B$5:$B$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E9">
-        <f>IF(B9="","",INDEX(Items!$E$5:$E$59,MATCH(B9,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$E$5:$E$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F9">
-        <f>IF(B9="","",INDEX(Items!$M$5:$M$59,MATCH(B9,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$M$5:$M$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7378,23 +5218,23 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A10,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A10),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A10,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A10),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(B10="","",INDEX(Items!$I$5:$I$59,MATCH(B10,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$I$5:$I$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D10">
-        <f>IF(B10="","",INDEX(Items!$B$5:$B$59,MATCH(B10,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$B$5:$B$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E10">
-        <f>IF(B10="","",INDEX(Items!$E$5:$E$59,MATCH(B10,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$E$5:$E$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F10">
-        <f>IF(B10="","",INDEX(Items!$M$5:$M$59,MATCH(B10,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$M$5:$M$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7403,23 +5243,23 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A11,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A11),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A11,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A11),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(B11="","",INDEX(Items!$I$5:$I$59,MATCH(B11,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$I$5:$I$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D11">
-        <f>IF(B11="","",INDEX(Items!$B$5:$B$59,MATCH(B11,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$B$5:$B$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E11">
-        <f>IF(B11="","",INDEX(Items!$E$5:$E$59,MATCH(B11,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$E$5:$E$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F11">
-        <f>IF(B11="","",INDEX(Items!$M$5:$M$59,MATCH(B11,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$M$5:$M$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7428,23 +5268,23 @@
         <v>8</v>
       </c>
       <c r="B12">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A12,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A12),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A12,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A12),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(B12="","",INDEX(Items!$I$5:$I$59,MATCH(B12,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$I$5:$I$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IF(B12="","",INDEX(Items!$B$5:$B$59,MATCH(B12,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$B$5:$B$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IF(B12="","",INDEX(Items!$E$5:$E$59,MATCH(B12,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$E$5:$E$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IF(B12="","",INDEX(Items!$M$5:$M$59,MATCH(B12,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$M$5:$M$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7453,23 +5293,23 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A13,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A13),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A13,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A13),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(B13="","",INDEX(Items!$I$5:$I$59,MATCH(B13,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$I$5:$I$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D13">
-        <f>IF(B13="","",INDEX(Items!$B$5:$B$59,MATCH(B13,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$B$5:$B$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E13">
-        <f>IF(B13="","",INDEX(Items!$E$5:$E$59,MATCH(B13,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$E$5:$E$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F13">
-        <f>IF(B13="","",INDEX(Items!$M$5:$M$59,MATCH(B13,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$M$5:$M$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7478,23 +5318,23 @@
         <v>10</v>
       </c>
       <c r="B14">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A14,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A14),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A14,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A14),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(B14="","",INDEX(Items!$I$5:$I$59,MATCH(B14,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$I$5:$I$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D14">
-        <f>IF(B14="","",INDEX(Items!$B$5:$B$59,MATCH(B14,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$B$5:$B$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E14">
-        <f>IF(B14="","",INDEX(Items!$E$5:$E$59,MATCH(B14,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$E$5:$E$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F14">
-        <f>IF(B14="","",INDEX(Items!$M$5:$M$59,MATCH(B14,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$M$5:$M$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7503,23 +5343,23 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A15,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A15),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A15,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A15),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(B15="","",INDEX(Items!$I$5:$I$59,MATCH(B15,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$I$5:$I$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D15">
-        <f>IF(B15="","",INDEX(Items!$B$5:$B$59,MATCH(B15,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$B$5:$B$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E15">
-        <f>IF(B15="","",INDEX(Items!$E$5:$E$59,MATCH(B15,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$E$5:$E$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F15">
-        <f>IF(B15="","",INDEX(Items!$M$5:$M$59,MATCH(B15,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$M$5:$M$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7528,23 +5368,23 @@
         <v>12</v>
       </c>
       <c r="B16">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A16,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A16),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A16,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A16),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(B16="","",INDEX(Items!$I$5:$I$59,MATCH(B16,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$I$5:$I$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D16">
-        <f>IF(B16="","",INDEX(Items!$B$5:$B$59,MATCH(B16,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$B$5:$B$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E16">
-        <f>IF(B16="","",INDEX(Items!$E$5:$E$59,MATCH(B16,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$E$5:$E$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F16">
-        <f>IF(B16="","",INDEX(Items!$M$5:$M$59,MATCH(B16,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$M$5:$M$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7553,23 +5393,23 @@
         <v>13</v>
       </c>
       <c r="B17">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A17,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A17),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A17,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A17),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(B17="","",INDEX(Items!$I$5:$I$59,MATCH(B17,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$I$5:$I$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D17">
-        <f>IF(B17="","",INDEX(Items!$B$5:$B$59,MATCH(B17,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$B$5:$B$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E17">
-        <f>IF(B17="","",INDEX(Items!$E$5:$E$59,MATCH(B17,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$E$5:$E$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F17">
-        <f>IF(B17="","",INDEX(Items!$M$5:$M$59,MATCH(B17,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$M$5:$M$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7578,23 +5418,23 @@
         <v>14</v>
       </c>
       <c r="B18">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A18,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A18),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A18,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A18),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(B18="","",INDEX(Items!$I$5:$I$59,MATCH(B18,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$I$5:$I$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D18">
-        <f>IF(B18="","",INDEX(Items!$B$5:$B$59,MATCH(B18,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$B$5:$B$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E18">
-        <f>IF(B18="","",INDEX(Items!$E$5:$E$59,MATCH(B18,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$E$5:$E$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F18">
-        <f>IF(B18="","",INDEX(Items!$M$5:$M$59,MATCH(B18,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$M$5:$M$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7603,23 +5443,23 @@
         <v>15</v>
       </c>
       <c r="B19">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A19,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A19),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A19,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A19),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(B19="","",INDEX(Items!$I$5:$I$59,MATCH(B19,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$I$5:$I$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D19">
-        <f>IF(B19="","",INDEX(Items!$B$5:$B$59,MATCH(B19,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$B$5:$B$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E19">
-        <f>IF(B19="","",INDEX(Items!$E$5:$E$59,MATCH(B19,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$E$5:$E$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F19">
-        <f>IF(B19="","",INDEX(Items!$M$5:$M$59,MATCH(B19,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$M$5:$M$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7628,23 +5468,23 @@
         <v>16</v>
       </c>
       <c r="B20">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A20,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A20),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A20,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A20),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(B20="","",INDEX(Items!$I$5:$I$59,MATCH(B20,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$I$5:$I$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D20">
-        <f>IF(B20="","",INDEX(Items!$B$5:$B$59,MATCH(B20,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$B$5:$B$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E20">
-        <f>IF(B20="","",INDEX(Items!$E$5:$E$59,MATCH(B20,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$E$5:$E$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F20">
-        <f>IF(B20="","",INDEX(Items!$M$5:$M$59,MATCH(B20,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$M$5:$M$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7653,23 +5493,23 @@
         <v>17</v>
       </c>
       <c r="B21">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A21,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A21),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A21,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A21),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(B21="","",INDEX(Items!$I$5:$I$59,MATCH(B21,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$I$5:$I$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D21">
-        <f>IF(B21="","",INDEX(Items!$B$5:$B$59,MATCH(B21,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$B$5:$B$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E21">
-        <f>IF(B21="","",INDEX(Items!$E$5:$E$59,MATCH(B21,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$E$5:$E$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F21">
-        <f>IF(B21="","",INDEX(Items!$M$5:$M$59,MATCH(B21,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$M$5:$M$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7678,23 +5518,23 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A22,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A22),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A22,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A22),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(B22="","",INDEX(Items!$I$5:$I$59,MATCH(B22,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$I$5:$I$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D22">
-        <f>IF(B22="","",INDEX(Items!$B$5:$B$59,MATCH(B22,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$B$5:$B$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E22">
-        <f>IF(B22="","",INDEX(Items!$E$5:$E$59,MATCH(B22,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$E$5:$E$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F22">
-        <f>IF(B22="","",INDEX(Items!$M$5:$M$59,MATCH(B22,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$M$5:$M$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7703,23 +5543,23 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A23,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A23),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A23,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A23),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(B23="","",INDEX(Items!$I$5:$I$59,MATCH(B23,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$I$5:$I$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D23">
-        <f>IF(B23="","",INDEX(Items!$B$5:$B$59,MATCH(B23,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$B$5:$B$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E23">
-        <f>IF(B23="","",INDEX(Items!$E$5:$E$59,MATCH(B23,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$E$5:$E$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F23">
-        <f>IF(B23="","",INDEX(Items!$M$5:$M$59,MATCH(B23,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$M$5:$M$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7728,23 +5568,23 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A24,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A24),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A24,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A24),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(B24="","",INDEX(Items!$I$5:$I$59,MATCH(B24,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$I$5:$I$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D24">
-        <f>IF(B24="","",INDEX(Items!$B$5:$B$59,MATCH(B24,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$B$5:$B$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E24">
-        <f>IF(B24="","",INDEX(Items!$E$5:$E$59,MATCH(B24,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$E$5:$E$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F24">
-        <f>IF(B24="","",INDEX(Items!$M$5:$M$59,MATCH(B24,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$M$5:$M$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7753,23 +5593,23 @@
         <v>21</v>
       </c>
       <c r="B25">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A25,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A25),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A25,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A25),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(B25="","",INDEX(Items!$I$5:$I$59,MATCH(B25,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$I$5:$I$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D25">
-        <f>IF(B25="","",INDEX(Items!$B$5:$B$59,MATCH(B25,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$B$5:$B$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E25">
-        <f>IF(B25="","",INDEX(Items!$E$5:$E$59,MATCH(B25,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$E$5:$E$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F25">
-        <f>IF(B25="","",INDEX(Items!$M$5:$M$59,MATCH(B25,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$M$5:$M$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7778,23 +5618,23 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A26,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A26),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A26,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A26),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(B26="","",INDEX(Items!$I$5:$I$59,MATCH(B26,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$I$5:$I$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D26">
-        <f>IF(B26="","",INDEX(Items!$B$5:$B$59,MATCH(B26,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$B$5:$B$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E26">
-        <f>IF(B26="","",INDEX(Items!$E$5:$E$59,MATCH(B26,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$E$5:$E$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F26">
-        <f>IF(B26="","",INDEX(Items!$M$5:$M$59,MATCH(B26,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$M$5:$M$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7803,23 +5643,23 @@
         <v>23</v>
       </c>
       <c r="B27">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A27,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A27),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A27,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A27),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(B27="","",INDEX(Items!$I$5:$I$59,MATCH(B27,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$I$5:$I$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D27">
-        <f>IF(B27="","",INDEX(Items!$B$5:$B$59,MATCH(B27,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$B$5:$B$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E27">
-        <f>IF(B27="","",INDEX(Items!$E$5:$E$59,MATCH(B27,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$E$5:$E$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F27">
-        <f>IF(B27="","",INDEX(Items!$M$5:$M$59,MATCH(B27,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$M$5:$M$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7828,23 +5668,23 @@
         <v>24</v>
       </c>
       <c r="B28">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A28,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A28),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A28,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A28),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(B28="","",INDEX(Items!$I$5:$I$59,MATCH(B28,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$I$5:$I$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D28">
-        <f>IF(B28="","",INDEX(Items!$B$5:$B$59,MATCH(B28,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$B$5:$B$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E28">
-        <f>IF(B28="","",INDEX(Items!$E$5:$E$59,MATCH(B28,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$E$5:$E$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F28">
-        <f>IF(B28="","",INDEX(Items!$M$5:$M$59,MATCH(B28,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$M$5:$M$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7853,23 +5693,23 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A29,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A29),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A29,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A29),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(B29="","",INDEX(Items!$I$5:$I$59,MATCH(B29,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$I$5:$I$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D29">
-        <f>IF(B29="","",INDEX(Items!$B$5:$B$59,MATCH(B29,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$B$5:$B$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E29">
-        <f>IF(B29="","",INDEX(Items!$E$5:$E$59,MATCH(B29,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$E$5:$E$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F29">
-        <f>IF(B29="","",INDEX(Items!$M$5:$M$59,MATCH(B29,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$M$5:$M$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7878,23 +5718,23 @@
         <v>26</v>
       </c>
       <c r="B30">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A30,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A30),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A30,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A30),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(B30="","",INDEX(Items!$I$5:$I$59,MATCH(B30,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$I$5:$I$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D30">
-        <f>IF(B30="","",INDEX(Items!$B$5:$B$59,MATCH(B30,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$B$5:$B$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E30">
-        <f>IF(B30="","",INDEX(Items!$E$5:$E$59,MATCH(B30,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$E$5:$E$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F30">
-        <f>IF(B30="","",INDEX(Items!$M$5:$M$59,MATCH(B30,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$M$5:$M$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7903,23 +5743,23 @@
         <v>27</v>
       </c>
       <c r="B31">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A31,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A31),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A31,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A31),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(B31="","",INDEX(Items!$I$5:$I$59,MATCH(B31,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$I$5:$I$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D31">
-        <f>IF(B31="","",INDEX(Items!$B$5:$B$59,MATCH(B31,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$B$5:$B$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E31">
-        <f>IF(B31="","",INDEX(Items!$E$5:$E$59,MATCH(B31,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$E$5:$E$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F31">
-        <f>IF(B31="","",INDEX(Items!$M$5:$M$59,MATCH(B31,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$M$5:$M$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7928,23 +5768,23 @@
         <v>28</v>
       </c>
       <c r="B32">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A32,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A32),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A32,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A32),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(B32="","",INDEX(Items!$I$5:$I$59,MATCH(B32,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$I$5:$I$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D32">
-        <f>IF(B32="","",INDEX(Items!$B$5:$B$59,MATCH(B32,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$B$5:$B$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E32">
-        <f>IF(B32="","",INDEX(Items!$E$5:$E$59,MATCH(B32,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$E$5:$E$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F32">
-        <f>IF(B32="","",INDEX(Items!$M$5:$M$59,MATCH(B32,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$M$5:$M$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7953,23 +5793,23 @@
         <v>29</v>
       </c>
       <c r="B33">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A33,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A33),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A33,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A33),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(B33="","",INDEX(Items!$I$5:$I$59,MATCH(B33,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$I$5:$I$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D33">
-        <f>IF(B33="","",INDEX(Items!$B$5:$B$59,MATCH(B33,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$B$5:$B$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E33">
-        <f>IF(B33="","",INDEX(Items!$E$5:$E$59,MATCH(B33,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$E$5:$E$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F33">
-        <f>IF(B33="","",INDEX(Items!$M$5:$M$59,MATCH(B33,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$M$5:$M$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -7978,23 +5818,23 @@
         <v>30</v>
       </c>
       <c r="B34">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A34,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A34),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A34,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A34),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(B34="","",INDEX(Items!$I$5:$I$59,MATCH(B34,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$I$5:$I$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D34">
-        <f>IF(B34="","",INDEX(Items!$B$5:$B$59,MATCH(B34,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$B$5:$B$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E34">
-        <f>IF(B34="","",INDEX(Items!$E$5:$E$59,MATCH(B34,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$E$5:$E$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F34">
-        <f>IF(B34="","",INDEX(Items!$M$5:$M$59,MATCH(B34,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$M$5:$M$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -8003,23 +5843,23 @@
         <v>31</v>
       </c>
       <c r="B35">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A35,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A35),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A35,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A35),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(B35="","",INDEX(Items!$I$5:$I$59,MATCH(B35,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$I$5:$I$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D35">
-        <f>IF(B35="","",INDEX(Items!$B$5:$B$59,MATCH(B35,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$B$5:$B$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E35">
-        <f>IF(B35="","",INDEX(Items!$E$5:$E$59,MATCH(B35,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$E$5:$E$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F35">
-        <f>IF(B35="","",INDEX(Items!$M$5:$M$59,MATCH(B35,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$M$5:$M$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -8028,23 +5868,23 @@
         <v>32</v>
       </c>
       <c r="B36">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A36,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A36),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A36,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A36),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(B36="","",INDEX(Items!$I$5:$I$59,MATCH(B36,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$I$5:$I$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D36">
-        <f>IF(B36="","",INDEX(Items!$B$5:$B$59,MATCH(B36,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$B$5:$B$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E36">
-        <f>IF(B36="","",INDEX(Items!$E$5:$E$59,MATCH(B36,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$E$5:$E$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F36">
-        <f>IF(B36="","",INDEX(Items!$M$5:$M$59,MATCH(B36,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$M$5:$M$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -8053,23 +5893,23 @@
         <v>33</v>
       </c>
       <c r="B37">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A37,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A37),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A37,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A37),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(B37="","",INDEX(Items!$I$5:$I$59,MATCH(B37,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$I$5:$I$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D37">
-        <f>IF(B37="","",INDEX(Items!$B$5:$B$59,MATCH(B37,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$B$5:$B$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E37">
-        <f>IF(B37="","",INDEX(Items!$E$5:$E$59,MATCH(B37,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$E$5:$E$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F37">
-        <f>IF(B37="","",INDEX(Items!$M$5:$M$59,MATCH(B37,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$M$5:$M$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -8078,23 +5918,23 @@
         <v>34</v>
       </c>
       <c r="B38">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A38,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A38),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A38,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A38),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(B38="","",INDEX(Items!$I$5:$I$59,MATCH(B38,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$I$5:$I$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D38">
-        <f>IF(B38="","",INDEX(Items!$B$5:$B$59,MATCH(B38,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$B$5:$B$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E38">
-        <f>IF(B38="","",INDEX(Items!$E$5:$E$59,MATCH(B38,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$E$5:$E$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F38">
-        <f>IF(B38="","",INDEX(Items!$M$5:$M$59,MATCH(B38,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$M$5:$M$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -8103,523 +5943,23 @@
         <v>35</v>
       </c>
       <c r="B39">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A39,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A39),Items!$N$5:$N$59,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A39,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A39),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(B39="","",INDEX(Items!$I$5:$I$59,MATCH(B39,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$I$5:$I$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D39">
-        <f>IF(B39="","",INDEX(Items!$B$5:$B$59,MATCH(B39,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$B$5:$B$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E39">
-        <f>IF(B39="","",INDEX(Items!$E$5:$E$59,MATCH(B39,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$E$5:$E$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F39">
-        <f>IF(B39="","",INDEX(Items!$M$5:$M$59,MATCH(B39,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A40,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A40),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C40" s="6">
-        <f>IF(B40="","",INDEX(Items!$I$5:$I$59,MATCH(B40,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D40">
-        <f>IF(B40="","",INDEX(Items!$B$5:$B$59,MATCH(B40,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E40">
-        <f>IF(B40="","",INDEX(Items!$E$5:$E$59,MATCH(B40,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F40">
-        <f>IF(B40="","",INDEX(Items!$M$5:$M$59,MATCH(B40,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A41,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A41),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C41" s="6">
-        <f>IF(B41="","",INDEX(Items!$I$5:$I$59,MATCH(B41,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D41">
-        <f>IF(B41="","",INDEX(Items!$B$5:$B$59,MATCH(B41,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E41">
-        <f>IF(B41="","",INDEX(Items!$E$5:$E$59,MATCH(B41,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F41">
-        <f>IF(B41="","",INDEX(Items!$M$5:$M$59,MATCH(B41,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A42,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A42),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C42" s="6">
-        <f>IF(B42="","",INDEX(Items!$I$5:$I$59,MATCH(B42,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D42">
-        <f>IF(B42="","",INDEX(Items!$B$5:$B$59,MATCH(B42,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E42">
-        <f>IF(B42="","",INDEX(Items!$E$5:$E$59,MATCH(B42,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F42">
-        <f>IF(B42="","",INDEX(Items!$M$5:$M$59,MATCH(B42,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A43,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A43),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C43" s="6">
-        <f>IF(B43="","",INDEX(Items!$I$5:$I$59,MATCH(B43,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D43">
-        <f>IF(B43="","",INDEX(Items!$B$5:$B$59,MATCH(B43,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E43">
-        <f>IF(B43="","",INDEX(Items!$E$5:$E$59,MATCH(B43,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F43">
-        <f>IF(B43="","",INDEX(Items!$M$5:$M$59,MATCH(B43,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A44,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A44),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C44" s="6">
-        <f>IF(B44="","",INDEX(Items!$I$5:$I$59,MATCH(B44,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D44">
-        <f>IF(B44="","",INDEX(Items!$B$5:$B$59,MATCH(B44,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E44">
-        <f>IF(B44="","",INDEX(Items!$E$5:$E$59,MATCH(B44,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F44">
-        <f>IF(B44="","",INDEX(Items!$M$5:$M$59,MATCH(B44,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A45,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A45),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C45" s="6">
-        <f>IF(B45="","",INDEX(Items!$I$5:$I$59,MATCH(B45,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D45">
-        <f>IF(B45="","",INDEX(Items!$B$5:$B$59,MATCH(B45,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E45">
-        <f>IF(B45="","",INDEX(Items!$E$5:$E$59,MATCH(B45,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F45">
-        <f>IF(B45="","",INDEX(Items!$M$5:$M$59,MATCH(B45,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A46,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A46),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C46" s="6">
-        <f>IF(B46="","",INDEX(Items!$I$5:$I$59,MATCH(B46,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D46">
-        <f>IF(B46="","",INDEX(Items!$B$5:$B$59,MATCH(B46,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E46">
-        <f>IF(B46="","",INDEX(Items!$E$5:$E$59,MATCH(B46,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F46">
-        <f>IF(B46="","",INDEX(Items!$M$5:$M$59,MATCH(B46,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A47,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A47),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C47" s="6">
-        <f>IF(B47="","",INDEX(Items!$I$5:$I$59,MATCH(B47,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D47">
-        <f>IF(B47="","",INDEX(Items!$B$5:$B$59,MATCH(B47,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E47">
-        <f>IF(B47="","",INDEX(Items!$E$5:$E$59,MATCH(B47,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F47">
-        <f>IF(B47="","",INDEX(Items!$M$5:$M$59,MATCH(B47,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A48,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A48),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C48" s="6">
-        <f>IF(B48="","",INDEX(Items!$I$5:$I$59,MATCH(B48,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D48">
-        <f>IF(B48="","",INDEX(Items!$B$5:$B$59,MATCH(B48,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E48">
-        <f>IF(B48="","",INDEX(Items!$E$5:$E$59,MATCH(B48,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F48">
-        <f>IF(B48="","",INDEX(Items!$M$5:$M$59,MATCH(B48,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A49,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A49),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C49" s="6">
-        <f>IF(B49="","",INDEX(Items!$I$5:$I$59,MATCH(B49,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D49">
-        <f>IF(B49="","",INDEX(Items!$B$5:$B$59,MATCH(B49,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E49">
-        <f>IF(B49="","",INDEX(Items!$E$5:$E$59,MATCH(B49,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F49">
-        <f>IF(B49="","",INDEX(Items!$M$5:$M$59,MATCH(B49,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A50,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A50),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C50" s="6">
-        <f>IF(B50="","",INDEX(Items!$I$5:$I$59,MATCH(B50,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D50">
-        <f>IF(B50="","",INDEX(Items!$B$5:$B$59,MATCH(B50,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E50">
-        <f>IF(B50="","",INDEX(Items!$E$5:$E$59,MATCH(B50,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F50">
-        <f>IF(B50="","",INDEX(Items!$M$5:$M$59,MATCH(B50,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A51,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A51),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C51" s="6">
-        <f>IF(B51="","",INDEX(Items!$I$5:$I$59,MATCH(B51,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D51">
-        <f>IF(B51="","",INDEX(Items!$B$5:$B$59,MATCH(B51,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E51">
-        <f>IF(B51="","",INDEX(Items!$E$5:$E$59,MATCH(B51,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F51">
-        <f>IF(B51="","",INDEX(Items!$M$5:$M$59,MATCH(B51,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A52,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A52),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C52" s="6">
-        <f>IF(B52="","",INDEX(Items!$I$5:$I$59,MATCH(B52,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D52">
-        <f>IF(B52="","",INDEX(Items!$B$5:$B$59,MATCH(B52,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E52">
-        <f>IF(B52="","",INDEX(Items!$E$5:$E$59,MATCH(B52,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F52">
-        <f>IF(B52="","",INDEX(Items!$M$5:$M$59,MATCH(B52,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A53,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A53),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C53" s="6">
-        <f>IF(B53="","",INDEX(Items!$I$5:$I$59,MATCH(B53,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D53">
-        <f>IF(B53="","",INDEX(Items!$B$5:$B$59,MATCH(B53,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E53">
-        <f>IF(B53="","",INDEX(Items!$E$5:$E$59,MATCH(B53,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F53">
-        <f>IF(B53="","",INDEX(Items!$M$5:$M$59,MATCH(B53,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A54,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A54),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C54" s="6">
-        <f>IF(B54="","",INDEX(Items!$I$5:$I$59,MATCH(B54,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D54">
-        <f>IF(B54="","",INDEX(Items!$B$5:$B$59,MATCH(B54,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E54">
-        <f>IF(B54="","",INDEX(Items!$E$5:$E$59,MATCH(B54,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F54">
-        <f>IF(B54="","",INDEX(Items!$M$5:$M$59,MATCH(B54,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A55,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A55),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C55" s="6">
-        <f>IF(B55="","",INDEX(Items!$I$5:$I$59,MATCH(B55,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D55">
-        <f>IF(B55="","",INDEX(Items!$B$5:$B$59,MATCH(B55,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E55">
-        <f>IF(B55="","",INDEX(Items!$E$5:$E$59,MATCH(B55,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F55">
-        <f>IF(B55="","",INDEX(Items!$M$5:$M$59,MATCH(B55,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A56,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A56),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C56" s="6">
-        <f>IF(B56="","",INDEX(Items!$I$5:$I$59,MATCH(B56,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D56">
-        <f>IF(B56="","",INDEX(Items!$B$5:$B$59,MATCH(B56,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E56">
-        <f>IF(B56="","",INDEX(Items!$E$5:$E$59,MATCH(B56,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F56">
-        <f>IF(B56="","",INDEX(Items!$M$5:$M$59,MATCH(B56,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A57,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A57),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C57" s="6">
-        <f>IF(B57="","",INDEX(Items!$I$5:$I$59,MATCH(B57,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D57">
-        <f>IF(B57="","",INDEX(Items!$B$5:$B$59,MATCH(B57,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E57">
-        <f>IF(B57="","",INDEX(Items!$E$5:$E$59,MATCH(B57,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F57">
-        <f>IF(B57="","",INDEX(Items!$M$5:$M$59,MATCH(B57,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A58,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A58),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C58" s="6">
-        <f>IF(B58="","",INDEX(Items!$I$5:$I$59,MATCH(B58,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D58">
-        <f>IF(B58="","",INDEX(Items!$B$5:$B$59,MATCH(B58,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E58">
-        <f>IF(B58="","",INDEX(Items!$E$5:$E$59,MATCH(B58,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F58">
-        <f>IF(B58="","",INDEX(Items!$M$5:$M$59,MATCH(B58,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59">
-        <f>IF(COUNT(Items!$N$5:$N$59)&lt;A59,"",INDEX(Items!$A$5:$A$59,MATCH(SMALL(Items!$N$5:$N$59,A59),Items!$N$5:$N$59,0)))</f>
-        <v/>
-      </c>
-      <c r="C59" s="6">
-        <f>IF(B59="","",INDEX(Items!$I$5:$I$59,MATCH(B59,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="D59">
-        <f>IF(B59="","",INDEX(Items!$B$5:$B$59,MATCH(B59,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="E59">
-        <f>IF(B59="","",INDEX(Items!$E$5:$E$59,MATCH(B59,Items!$A$5:$A$59,0)))</f>
-        <v/>
-      </c>
-      <c r="F59">
-        <f>IF(B59="","",INDEX(Items!$M$5:$M$59,MATCH(B59,Items!$A$5:$A$59,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$M$5:$M$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -8681,11 +6021,11 @@
         </is>
       </c>
       <c r="C5">
-        <f>COUNTIF(Items!$E$5:$E$59,A5)</f>
+        <f>COUNTIF(Items!$E$5:$E$39,A5)</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$59=A5)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$E$5:$E$59=A5)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$E$5:$E$59=A5)*Items!$H$5:$H$59))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$39=A5)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$E$5:$E$39=A5)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$E$5:$E$39=A5)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -8701,11 +6041,11 @@
         </is>
       </c>
       <c r="C6">
-        <f>COUNTIF(Items!$E$5:$E$59,A6)</f>
+        <f>COUNTIF(Items!$E$5:$E$39,A6)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$59=A6)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$E$5:$E$59=A6)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$E$5:$E$59=A6)*Items!$H$5:$H$59))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$39=A6)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$E$5:$E$39=A6)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$E$5:$E$39=A6)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -8721,11 +6061,11 @@
         </is>
       </c>
       <c r="C7">
-        <f>COUNTIF(Items!$E$5:$E$59,A7)</f>
+        <f>COUNTIF(Items!$E$5:$E$39,A7)</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$59=A7)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$E$5:$E$59=A7)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$E$5:$E$59=A7)*Items!$H$5:$H$59))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$39=A7)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$E$5:$E$39=A7)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$E$5:$E$39=A7)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -8735,15 +6075,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Part 1. The week's rules, cold</t>
+          <t>Part 1. Anand's Monday numbers</t>
         </is>
       </c>
       <c r="C8">
-        <f>COUNTIF(Items!$B$5:$B$59,A8)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A8)</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A8)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A8)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A8)*Items!$H$5:$H$59))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A8)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A8)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A8)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -8753,15 +6093,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Part 2. Asking the warehouse</t>
+          <t>Part 2. Booked against collected</t>
         </is>
       </c>
       <c r="C9">
-        <f>COUNTIF(Items!$B$5:$B$59,A9)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A9)</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A9)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A9)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A9)*Items!$H$5:$H$59))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A9)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A9)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A9)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -8771,15 +6111,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Part 3. Joins that keep their rows</t>
+          <t>Part 3. The protect list and the plan line</t>
         </is>
       </c>
       <c r="C10">
-        <f>COUNTIF(Items!$B$5:$B$59,A10)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A10)</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A10)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A10)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A10)*Items!$H$5:$H$59))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A10)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A10)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A10)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -8789,15 +6129,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Part 4. Windows: rank, lag and running totals</t>
+          <t>Part 4. One row per customer</t>
         </is>
       </c>
       <c r="C11">
-        <f>COUNTIF(Items!$B$5:$B$59,A11)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A11)</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A11)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A11)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A11)*Items!$H$5:$H$59))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A11)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A11)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A11)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -8807,15 +6147,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Part 5. pandas and the last mile to Excel</t>
+          <t>Part 5. The last mile, and spreadsheets in public</t>
         </is>
       </c>
       <c r="C12">
-        <f>COUNTIF(Items!$B$5:$B$59,A12)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A12)</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A12)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A12)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A12)*Items!$H$5:$H$59))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A12)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A12)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A12)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -8825,15 +6165,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Part 6. Read the code, read the data</t>
+          <t>Part 6. Read the code, read the data: an AI team's tables</t>
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(Items!$B$5:$B$59,A13)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A13)</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$59=A13)*Items!$H$5:$H$59)=0,"",SUMPRODUCT((Items!$B$5:$B$59=A13)*Items!$G$5:$G$59)/SUMPRODUCT((Items!$B$5:$B$59=A13)*Items!$H$5:$H$59))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A13)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A13)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A13)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -8885,15 +6225,15 @@
         <v>1</v>
       </c>
       <c r="B5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
     </row>
@@ -8902,15 +6242,15 @@
         <v>2</v>
       </c>
       <c r="B6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
     </row>
@@ -8919,15 +6259,15 @@
         <v>3</v>
       </c>
       <c r="B7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
     </row>
@@ -8936,15 +6276,15 @@
         <v>4</v>
       </c>
       <c r="B8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
     </row>
@@ -8953,15 +6293,15 @@
         <v>5</v>
       </c>
       <c r="B9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
     </row>
@@ -8970,15 +6310,15 @@
         <v>6</v>
       </c>
       <c r="B10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
     </row>
@@ -8987,15 +6327,15 @@
         <v>7</v>
       </c>
       <c r="B11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
     </row>
@@ -9004,15 +6344,15 @@
         <v>8</v>
       </c>
       <c r="B12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
     </row>
@@ -9021,15 +6361,15 @@
         <v>9</v>
       </c>
       <c r="B13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
     </row>
@@ -9038,15 +6378,15 @@
         <v>10</v>
       </c>
       <c r="B14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
     </row>
@@ -9055,15 +6395,15 @@
         <v>11</v>
       </c>
       <c r="B15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="D15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
     </row>
@@ -9072,15 +6412,15 @@
         <v>12</v>
       </c>
       <c r="B16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="D16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
     </row>
@@ -9089,15 +6429,15 @@
         <v>13</v>
       </c>
       <c r="B17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="D17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
     </row>
@@ -9106,15 +6446,15 @@
         <v>14</v>
       </c>
       <c r="B18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="D18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
     </row>
@@ -9123,15 +6463,15 @@
         <v>15</v>
       </c>
       <c r="B19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
     </row>
@@ -9140,15 +6480,15 @@
         <v>16</v>
       </c>
       <c r="B20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="D20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
     </row>
@@ -9157,15 +6497,15 @@
         <v>17</v>
       </c>
       <c r="B21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="D21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
     </row>
@@ -9174,15 +6514,15 @@
         <v>18</v>
       </c>
       <c r="B22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="D22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
     </row>
@@ -9191,15 +6531,15 @@
         <v>19</v>
       </c>
       <c r="B23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="D23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
     </row>
@@ -9208,15 +6548,15 @@
         <v>20</v>
       </c>
       <c r="B24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
     </row>
@@ -9225,15 +6565,15 @@
         <v>21</v>
       </c>
       <c r="B25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
     </row>
@@ -9242,15 +6582,15 @@
         <v>22</v>
       </c>
       <c r="B26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
     </row>
@@ -9259,15 +6599,15 @@
         <v>23</v>
       </c>
       <c r="B27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
     </row>
@@ -9276,15 +6616,15 @@
         <v>24</v>
       </c>
       <c r="B28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
     </row>
@@ -9293,15 +6633,15 @@
         <v>25</v>
       </c>
       <c r="B29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
     </row>
@@ -9310,15 +6650,15 @@
         <v>26</v>
       </c>
       <c r="B30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
     </row>
@@ -9327,15 +6667,15 @@
         <v>27</v>
       </c>
       <c r="B31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
     </row>
@@ -9344,15 +6684,15 @@
         <v>28</v>
       </c>
       <c r="B32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
     </row>
@@ -9361,15 +6701,15 @@
         <v>29</v>
       </c>
       <c r="B33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
     </row>
@@ -9378,15 +6718,15 @@
         <v>30</v>
       </c>
       <c r="B34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
     </row>
@@ -9395,15 +6735,15 @@
         <v>31</v>
       </c>
       <c r="B35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
     </row>
@@ -9412,15 +6752,15 @@
         <v>32</v>
       </c>
       <c r="B36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
     </row>
@@ -9429,15 +6769,15 @@
         <v>33</v>
       </c>
       <c r="B37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
     </row>
@@ -9446,15 +6786,15 @@
         <v>34</v>
       </c>
       <c r="B38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
     </row>
@@ -9463,15 +6803,15 @@
         <v>35</v>
       </c>
       <c r="B39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$3:$BD$3=B$4)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$3:$BD$3=C$4)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="D39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$3:$BD$3=D$4)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
     </row>
@@ -9622,27 +6962,27 @@
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="I5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="L5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="M5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="N5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$5:$BD$5))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$5:$BD$5=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$5:$BD$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
     </row>
@@ -9657,27 +6997,27 @@
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="I6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="L6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="M6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="N6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$6:$BD$6))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$6:$BD$6=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$6:$BD$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
     </row>
@@ -9692,27 +7032,27 @@
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="I7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="L7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="M7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="N7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$7:$BD$7))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$7:$BD$7=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$7:$BD$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
     </row>
@@ -9727,27 +7067,27 @@
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
       <c r="I8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="L8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="M8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="N8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$8:$BD$8))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$8:$BD$8=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$8:$BD$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
     </row>
@@ -9762,27 +7102,27 @@
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
       <c r="I9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="L9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="M9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="N9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$9:$BD$9))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$9:$BD$9=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$9:$BD$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
     </row>
@@ -9797,27 +7137,27 @@
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
       <c r="I10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="L10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="M10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="N10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$10:$BD$10))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$10:$BD$10=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$10:$BD$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
     </row>
@@ -9832,27 +7172,27 @@
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
       <c r="I11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="L11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="M11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="N11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$11:$BD$11))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$11:$BD$11=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$11:$BD$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
     </row>
@@ -9867,27 +7207,27 @@
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
       <c r="I12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="L12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="M12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="N12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$12:$BD$12))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$12:$BD$12=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$12:$BD$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
     </row>
@@ -9902,27 +7242,27 @@
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="I13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="L13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="M13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="N13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$13:$BD$13))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$13:$BD$13=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$13:$BD$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
     </row>
@@ -9937,27 +7277,27 @@
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="I14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="L14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="M14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="N14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$14:$BD$14))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$14:$BD$14=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$14:$BD$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
     </row>
@@ -9972,27 +7312,27 @@
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="I15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="L15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="M15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="N15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$15:$BD$15))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$15:$BD$15=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$15:$BD$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
     </row>
@@ -10007,27 +7347,27 @@
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
       <c r="I16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="L16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="M16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="N16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$16:$BD$16))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$16:$BD$16=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$16:$BD$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
     </row>
@@ -10042,27 +7382,27 @@
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="I17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="L17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="M17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="N17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$17:$BD$17))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$17:$BD$17=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$17:$BD$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
     </row>
@@ -10077,27 +7417,27 @@
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="I18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="J18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="L18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="M18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="N18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$18:$BD$18))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$18:$BD$18=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$18:$BD$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
     </row>
@@ -10112,27 +7452,27 @@
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="I19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="L19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="M19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="N19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$19:$BD$19))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$19:$BD$19=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$19:$BD$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
     </row>
@@ -10147,27 +7487,27 @@
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="I20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="L20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="M20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="N20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$20:$BD$20))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$20:$BD$20=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$20:$BD$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
     </row>
@@ -10182,27 +7522,27 @@
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="I21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="L21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="M21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="N21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$21:$BD$21))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$21:$BD$21=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$21:$BD$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
     </row>
@@ -10217,27 +7557,27 @@
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="I22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="L22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="M22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="N22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$22:$BD$22))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$22:$BD$22=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$22:$BD$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
     </row>
@@ -10252,27 +7592,27 @@
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="I23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="L23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="M23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="N23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$23:$BD$23))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$23:$BD$23=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$23:$BD$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
     </row>
@@ -10287,27 +7627,27 @@
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="I24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="L24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="M24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="N24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$24:$BD$24))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$24:$BD$24=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$24:$BD$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
     </row>
@@ -10322,27 +7662,27 @@
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="I25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="L25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="M25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="N25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$25:$BD$25))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$25:$BD$25=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$25:$BD$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
     </row>
@@ -10357,27 +7697,27 @@
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="I26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="L26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="M26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="N26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$26:$BD$26))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$26:$BD$26=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$26:$BD$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
     </row>
@@ -10392,27 +7732,27 @@
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="I27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="L27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="M27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="N27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$27:$BD$27))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$27:$BD$27=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$27:$BD$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
     </row>
@@ -10427,27 +7767,27 @@
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="I28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="J28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="L28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="M28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="N28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$28:$BD$28))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$28:$BD$28=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$28:$BD$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
     </row>
@@ -10462,27 +7802,27 @@
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
       <c r="I29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="L29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="M29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="N29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$29:$BD$29))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$29:$BD$29=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$29:$BD$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
     </row>
@@ -10497,27 +7837,27 @@
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
       <c r="I30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="L30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="M30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="N30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$30:$BD$30))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$30:$BD$30=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$30:$BD$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
     </row>
@@ -10532,27 +7872,27 @@
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>
       <c r="I31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="L31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="M31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="N31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$31:$BD$31))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$31:$BD$31=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$31:$BD$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
     </row>
@@ -10567,27 +7907,27 @@
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
       <c r="I32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="L32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="M32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="N32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$32:$BD$32))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$32:$BD$32=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$32:$BD$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
     </row>
@@ -10602,27 +7942,27 @@
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
       <c r="I33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="J33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="L33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="M33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="N33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$33:$BD$33))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$33:$BD$33=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$33:$BD$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
     </row>
@@ -10637,27 +7977,27 @@
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
       <c r="I34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="J34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="L34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="M34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="N34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$34:$BD$34))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$34:$BD$34=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$34:$BD$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
     </row>
@@ -10672,27 +8012,27 @@
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="5" t="n"/>
       <c r="I35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="J35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="L35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="M35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="N35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$35:$BD$35))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$35:$BD$35=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$35:$BD$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
     </row>
@@ -10707,27 +8047,27 @@
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="I36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="J36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="L36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="M36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="N36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$36:$BD$36))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$36:$BD$36=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$36:$BD$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
     </row>
@@ -10742,27 +8082,27 @@
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
       <c r="I37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="J37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="K37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="L37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="M37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="N37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$37:$BD$37))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$37:$BD$37=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$37:$BD$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
     </row>
@@ -10777,27 +8117,27 @@
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="5" t="n"/>
       <c r="I38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="J38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="K38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="L38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="M38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="N38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$38:$BD$38))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$38:$BD$38=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$38:$BD$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
     </row>
@@ -10812,27 +8152,27 @@
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
       <c r="I39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=I$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="J39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=J$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="K39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=K$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="L39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=L$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="M39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=M$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="N39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$39:$BD$39))=0,"",SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*(Marks!$B$39:$BD$39=1))/SUMPRODUCT((Marks!$B$2:$BD$2=N$3)*ISNUMBER(Marks!$B$39:$BD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
     </row>
@@ -10868,7 +8208,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Part 1. The week's rules, cold</t>
+          <t>Part 1. Anand's Monday numbers</t>
         </is>
       </c>
       <c r="B43" s="7">
@@ -10887,7 +8227,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Part 2. Asking the warehouse</t>
+          <t>Part 2. Booked against collected</t>
         </is>
       </c>
       <c r="B44" s="7">
@@ -10906,7 +8246,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Part 3. Joins that keep their rows</t>
+          <t>Part 3. The protect list and the plan line</t>
         </is>
       </c>
       <c r="B45" s="7">
@@ -10925,7 +8265,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Part 4. Windows: rank, lag and running totals</t>
+          <t>Part 4. One row per customer</t>
         </is>
       </c>
       <c r="B46" s="7">
@@ -10944,7 +8284,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Part 5. pandas and the last mile to Excel</t>
+          <t>Part 5. The last mile, and spreadsheets in public</t>
         </is>
       </c>
       <c r="B47" s="7">
@@ -10963,7 +8303,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Part 6. Read the code, read the data</t>
+          <t>Part 6. Read the code, read the data: an AI team's tables</t>
         </is>
       </c>
       <c r="B48" s="7">

--- a/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
@@ -2935,7 +2935,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Applied maths</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>It prints 2 and 1. The true figures are 2.36 and 1.84, a fall of about 22 percent.</t>
         </is>
       </c>
       <c r="G5">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G9">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>c, e, a, d, b</t>
+          <t>e, f, b, c, a</t>
         </is>
       </c>
       <c r="G12">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G17">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G24">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Applied maths</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>B8 returns -0.5; the six rows average 1.0; the formula understates growth by 1.5 points and turns growth into a fall.</t>
         </is>
       </c>
       <c r="G31">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G32">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.60 dollars a trip</t>
+          <t>2.00 dollars, about 8.5 percent of the 23.50 dollars charged</t>
         </is>
       </c>
       <c r="G33">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G36">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">

--- a/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM39"/>
+  <dimension ref="A1:AK39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,10 +586,10 @@
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
         <v>5</v>
@@ -607,10 +607,10 @@
         <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -624,12 +624,6 @@
       <c r="AH2" t="n">
         <v>6</v>
       </c>
-      <c r="AI2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -644,170 +638,160 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>[D]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>[D]</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>[D]</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>[D]</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>[D]</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
@@ -986,25 +970,15 @@
       </c>
       <c r="AI4" s="4" t="inlineStr">
         <is>
-          <t>Q34</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="AJ4" s="4" t="inlineStr">
         <is>
-          <t>Q35</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="AK4" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="AL4" s="4" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="AM4" s="4" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
@@ -1047,18 +1021,16 @@
       <c r="AF5" s="5" t="n"/>
       <c r="AG5" s="5" t="n"/>
       <c r="AH5" s="5" t="n"/>
-      <c r="AI5" s="5" t="n"/>
-      <c r="AJ5" s="5" t="n"/>
+      <c r="AI5">
+        <f>IF(COUNT(B5:AH5)=0,"",SUM(B5:AH5))</f>
+        <v/>
+      </c>
+      <c r="AJ5">
+        <f>COUNT(B5:AH5)</f>
+        <v/>
+      </c>
       <c r="AK5">
-        <f>IF(COUNT(B5:AJ5)=0,"",SUM(B5:AJ5))</f>
-        <v/>
-      </c>
-      <c r="AL5">
-        <f>COUNT(B5:AJ5)</f>
-        <v/>
-      </c>
-      <c r="AM5">
-        <f>IF(OR(AK5="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK5,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK5,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI5="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI5,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI5,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1099,18 +1071,16 @@
       <c r="AF6" s="5" t="n"/>
       <c r="AG6" s="5" t="n"/>
       <c r="AH6" s="5" t="n"/>
-      <c r="AI6" s="5" t="n"/>
-      <c r="AJ6" s="5" t="n"/>
+      <c r="AI6">
+        <f>IF(COUNT(B6:AH6)=0,"",SUM(B6:AH6))</f>
+        <v/>
+      </c>
+      <c r="AJ6">
+        <f>COUNT(B6:AH6)</f>
+        <v/>
+      </c>
       <c r="AK6">
-        <f>IF(COUNT(B6:AJ6)=0,"",SUM(B6:AJ6))</f>
-        <v/>
-      </c>
-      <c r="AL6">
-        <f>COUNT(B6:AJ6)</f>
-        <v/>
-      </c>
-      <c r="AM6">
-        <f>IF(OR(AK6="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK6,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK6,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI6="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI6,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI6,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1151,18 +1121,16 @@
       <c r="AF7" s="5" t="n"/>
       <c r="AG7" s="5" t="n"/>
       <c r="AH7" s="5" t="n"/>
-      <c r="AI7" s="5" t="n"/>
-      <c r="AJ7" s="5" t="n"/>
+      <c r="AI7">
+        <f>IF(COUNT(B7:AH7)=0,"",SUM(B7:AH7))</f>
+        <v/>
+      </c>
+      <c r="AJ7">
+        <f>COUNT(B7:AH7)</f>
+        <v/>
+      </c>
       <c r="AK7">
-        <f>IF(COUNT(B7:AJ7)=0,"",SUM(B7:AJ7))</f>
-        <v/>
-      </c>
-      <c r="AL7">
-        <f>COUNT(B7:AJ7)</f>
-        <v/>
-      </c>
-      <c r="AM7">
-        <f>IF(OR(AK7="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK7,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK7,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI7="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI7,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI7,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1203,18 +1171,16 @@
       <c r="AF8" s="5" t="n"/>
       <c r="AG8" s="5" t="n"/>
       <c r="AH8" s="5" t="n"/>
-      <c r="AI8" s="5" t="n"/>
-      <c r="AJ8" s="5" t="n"/>
+      <c r="AI8">
+        <f>IF(COUNT(B8:AH8)=0,"",SUM(B8:AH8))</f>
+        <v/>
+      </c>
+      <c r="AJ8">
+        <f>COUNT(B8:AH8)</f>
+        <v/>
+      </c>
       <c r="AK8">
-        <f>IF(COUNT(B8:AJ8)=0,"",SUM(B8:AJ8))</f>
-        <v/>
-      </c>
-      <c r="AL8">
-        <f>COUNT(B8:AJ8)</f>
-        <v/>
-      </c>
-      <c r="AM8">
-        <f>IF(OR(AK8="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK8,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK8,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI8="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI8,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI8,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1255,18 +1221,16 @@
       <c r="AF9" s="5" t="n"/>
       <c r="AG9" s="5" t="n"/>
       <c r="AH9" s="5" t="n"/>
-      <c r="AI9" s="5" t="n"/>
-      <c r="AJ9" s="5" t="n"/>
+      <c r="AI9">
+        <f>IF(COUNT(B9:AH9)=0,"",SUM(B9:AH9))</f>
+        <v/>
+      </c>
+      <c r="AJ9">
+        <f>COUNT(B9:AH9)</f>
+        <v/>
+      </c>
       <c r="AK9">
-        <f>IF(COUNT(B9:AJ9)=0,"",SUM(B9:AJ9))</f>
-        <v/>
-      </c>
-      <c r="AL9">
-        <f>COUNT(B9:AJ9)</f>
-        <v/>
-      </c>
-      <c r="AM9">
-        <f>IF(OR(AK9="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK9,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK9,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI9="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI9,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI9,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1307,18 +1271,16 @@
       <c r="AF10" s="5" t="n"/>
       <c r="AG10" s="5" t="n"/>
       <c r="AH10" s="5" t="n"/>
-      <c r="AI10" s="5" t="n"/>
-      <c r="AJ10" s="5" t="n"/>
+      <c r="AI10">
+        <f>IF(COUNT(B10:AH10)=0,"",SUM(B10:AH10))</f>
+        <v/>
+      </c>
+      <c r="AJ10">
+        <f>COUNT(B10:AH10)</f>
+        <v/>
+      </c>
       <c r="AK10">
-        <f>IF(COUNT(B10:AJ10)=0,"",SUM(B10:AJ10))</f>
-        <v/>
-      </c>
-      <c r="AL10">
-        <f>COUNT(B10:AJ10)</f>
-        <v/>
-      </c>
-      <c r="AM10">
-        <f>IF(OR(AK10="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK10,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK10,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI10="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI10,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI10,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1359,18 +1321,16 @@
       <c r="AF11" s="5" t="n"/>
       <c r="AG11" s="5" t="n"/>
       <c r="AH11" s="5" t="n"/>
-      <c r="AI11" s="5" t="n"/>
-      <c r="AJ11" s="5" t="n"/>
+      <c r="AI11">
+        <f>IF(COUNT(B11:AH11)=0,"",SUM(B11:AH11))</f>
+        <v/>
+      </c>
+      <c r="AJ11">
+        <f>COUNT(B11:AH11)</f>
+        <v/>
+      </c>
       <c r="AK11">
-        <f>IF(COUNT(B11:AJ11)=0,"",SUM(B11:AJ11))</f>
-        <v/>
-      </c>
-      <c r="AL11">
-        <f>COUNT(B11:AJ11)</f>
-        <v/>
-      </c>
-      <c r="AM11">
-        <f>IF(OR(AK11="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK11,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK11,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI11="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI11,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI11,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1411,18 +1371,16 @@
       <c r="AF12" s="5" t="n"/>
       <c r="AG12" s="5" t="n"/>
       <c r="AH12" s="5" t="n"/>
-      <c r="AI12" s="5" t="n"/>
-      <c r="AJ12" s="5" t="n"/>
+      <c r="AI12">
+        <f>IF(COUNT(B12:AH12)=0,"",SUM(B12:AH12))</f>
+        <v/>
+      </c>
+      <c r="AJ12">
+        <f>COUNT(B12:AH12)</f>
+        <v/>
+      </c>
       <c r="AK12">
-        <f>IF(COUNT(B12:AJ12)=0,"",SUM(B12:AJ12))</f>
-        <v/>
-      </c>
-      <c r="AL12">
-        <f>COUNT(B12:AJ12)</f>
-        <v/>
-      </c>
-      <c r="AM12">
-        <f>IF(OR(AK12="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK12,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK12,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI12="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI12,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI12,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1463,18 +1421,16 @@
       <c r="AF13" s="5" t="n"/>
       <c r="AG13" s="5" t="n"/>
       <c r="AH13" s="5" t="n"/>
-      <c r="AI13" s="5" t="n"/>
-      <c r="AJ13" s="5" t="n"/>
+      <c r="AI13">
+        <f>IF(COUNT(B13:AH13)=0,"",SUM(B13:AH13))</f>
+        <v/>
+      </c>
+      <c r="AJ13">
+        <f>COUNT(B13:AH13)</f>
+        <v/>
+      </c>
       <c r="AK13">
-        <f>IF(COUNT(B13:AJ13)=0,"",SUM(B13:AJ13))</f>
-        <v/>
-      </c>
-      <c r="AL13">
-        <f>COUNT(B13:AJ13)</f>
-        <v/>
-      </c>
-      <c r="AM13">
-        <f>IF(OR(AK13="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK13,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK13,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI13="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI13,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI13,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1515,18 +1471,16 @@
       <c r="AF14" s="5" t="n"/>
       <c r="AG14" s="5" t="n"/>
       <c r="AH14" s="5" t="n"/>
-      <c r="AI14" s="5" t="n"/>
-      <c r="AJ14" s="5" t="n"/>
+      <c r="AI14">
+        <f>IF(COUNT(B14:AH14)=0,"",SUM(B14:AH14))</f>
+        <v/>
+      </c>
+      <c r="AJ14">
+        <f>COUNT(B14:AH14)</f>
+        <v/>
+      </c>
       <c r="AK14">
-        <f>IF(COUNT(B14:AJ14)=0,"",SUM(B14:AJ14))</f>
-        <v/>
-      </c>
-      <c r="AL14">
-        <f>COUNT(B14:AJ14)</f>
-        <v/>
-      </c>
-      <c r="AM14">
-        <f>IF(OR(AK14="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK14,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK14,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI14="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI14,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI14,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1567,18 +1521,16 @@
       <c r="AF15" s="5" t="n"/>
       <c r="AG15" s="5" t="n"/>
       <c r="AH15" s="5" t="n"/>
-      <c r="AI15" s="5" t="n"/>
-      <c r="AJ15" s="5" t="n"/>
+      <c r="AI15">
+        <f>IF(COUNT(B15:AH15)=0,"",SUM(B15:AH15))</f>
+        <v/>
+      </c>
+      <c r="AJ15">
+        <f>COUNT(B15:AH15)</f>
+        <v/>
+      </c>
       <c r="AK15">
-        <f>IF(COUNT(B15:AJ15)=0,"",SUM(B15:AJ15))</f>
-        <v/>
-      </c>
-      <c r="AL15">
-        <f>COUNT(B15:AJ15)</f>
-        <v/>
-      </c>
-      <c r="AM15">
-        <f>IF(OR(AK15="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK15,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK15,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI15="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI15,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI15,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1619,18 +1571,16 @@
       <c r="AF16" s="5" t="n"/>
       <c r="AG16" s="5" t="n"/>
       <c r="AH16" s="5" t="n"/>
-      <c r="AI16" s="5" t="n"/>
-      <c r="AJ16" s="5" t="n"/>
+      <c r="AI16">
+        <f>IF(COUNT(B16:AH16)=0,"",SUM(B16:AH16))</f>
+        <v/>
+      </c>
+      <c r="AJ16">
+        <f>COUNT(B16:AH16)</f>
+        <v/>
+      </c>
       <c r="AK16">
-        <f>IF(COUNT(B16:AJ16)=0,"",SUM(B16:AJ16))</f>
-        <v/>
-      </c>
-      <c r="AL16">
-        <f>COUNT(B16:AJ16)</f>
-        <v/>
-      </c>
-      <c r="AM16">
-        <f>IF(OR(AK16="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK16,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK16,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI16="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI16,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI16,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1671,18 +1621,16 @@
       <c r="AF17" s="5" t="n"/>
       <c r="AG17" s="5" t="n"/>
       <c r="AH17" s="5" t="n"/>
-      <c r="AI17" s="5" t="n"/>
-      <c r="AJ17" s="5" t="n"/>
+      <c r="AI17">
+        <f>IF(COUNT(B17:AH17)=0,"",SUM(B17:AH17))</f>
+        <v/>
+      </c>
+      <c r="AJ17">
+        <f>COUNT(B17:AH17)</f>
+        <v/>
+      </c>
       <c r="AK17">
-        <f>IF(COUNT(B17:AJ17)=0,"",SUM(B17:AJ17))</f>
-        <v/>
-      </c>
-      <c r="AL17">
-        <f>COUNT(B17:AJ17)</f>
-        <v/>
-      </c>
-      <c r="AM17">
-        <f>IF(OR(AK17="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK17,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK17,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI17="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI17,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI17,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1723,18 +1671,16 @@
       <c r="AF18" s="5" t="n"/>
       <c r="AG18" s="5" t="n"/>
       <c r="AH18" s="5" t="n"/>
-      <c r="AI18" s="5" t="n"/>
-      <c r="AJ18" s="5" t="n"/>
+      <c r="AI18">
+        <f>IF(COUNT(B18:AH18)=0,"",SUM(B18:AH18))</f>
+        <v/>
+      </c>
+      <c r="AJ18">
+        <f>COUNT(B18:AH18)</f>
+        <v/>
+      </c>
       <c r="AK18">
-        <f>IF(COUNT(B18:AJ18)=0,"",SUM(B18:AJ18))</f>
-        <v/>
-      </c>
-      <c r="AL18">
-        <f>COUNT(B18:AJ18)</f>
-        <v/>
-      </c>
-      <c r="AM18">
-        <f>IF(OR(AK18="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK18,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK18,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI18="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI18,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI18,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1775,18 +1721,16 @@
       <c r="AF19" s="5" t="n"/>
       <c r="AG19" s="5" t="n"/>
       <c r="AH19" s="5" t="n"/>
-      <c r="AI19" s="5" t="n"/>
-      <c r="AJ19" s="5" t="n"/>
+      <c r="AI19">
+        <f>IF(COUNT(B19:AH19)=0,"",SUM(B19:AH19))</f>
+        <v/>
+      </c>
+      <c r="AJ19">
+        <f>COUNT(B19:AH19)</f>
+        <v/>
+      </c>
       <c r="AK19">
-        <f>IF(COUNT(B19:AJ19)=0,"",SUM(B19:AJ19))</f>
-        <v/>
-      </c>
-      <c r="AL19">
-        <f>COUNT(B19:AJ19)</f>
-        <v/>
-      </c>
-      <c r="AM19">
-        <f>IF(OR(AK19="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK19,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK19,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI19="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI19,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI19,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1827,18 +1771,16 @@
       <c r="AF20" s="5" t="n"/>
       <c r="AG20" s="5" t="n"/>
       <c r="AH20" s="5" t="n"/>
-      <c r="AI20" s="5" t="n"/>
-      <c r="AJ20" s="5" t="n"/>
+      <c r="AI20">
+        <f>IF(COUNT(B20:AH20)=0,"",SUM(B20:AH20))</f>
+        <v/>
+      </c>
+      <c r="AJ20">
+        <f>COUNT(B20:AH20)</f>
+        <v/>
+      </c>
       <c r="AK20">
-        <f>IF(COUNT(B20:AJ20)=0,"",SUM(B20:AJ20))</f>
-        <v/>
-      </c>
-      <c r="AL20">
-        <f>COUNT(B20:AJ20)</f>
-        <v/>
-      </c>
-      <c r="AM20">
-        <f>IF(OR(AK20="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK20,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK20,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI20="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI20,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI20,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1879,18 +1821,16 @@
       <c r="AF21" s="5" t="n"/>
       <c r="AG21" s="5" t="n"/>
       <c r="AH21" s="5" t="n"/>
-      <c r="AI21" s="5" t="n"/>
-      <c r="AJ21" s="5" t="n"/>
+      <c r="AI21">
+        <f>IF(COUNT(B21:AH21)=0,"",SUM(B21:AH21))</f>
+        <v/>
+      </c>
+      <c r="AJ21">
+        <f>COUNT(B21:AH21)</f>
+        <v/>
+      </c>
       <c r="AK21">
-        <f>IF(COUNT(B21:AJ21)=0,"",SUM(B21:AJ21))</f>
-        <v/>
-      </c>
-      <c r="AL21">
-        <f>COUNT(B21:AJ21)</f>
-        <v/>
-      </c>
-      <c r="AM21">
-        <f>IF(OR(AK21="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK21,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK21,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI21="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI21,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI21,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1931,18 +1871,16 @@
       <c r="AF22" s="5" t="n"/>
       <c r="AG22" s="5" t="n"/>
       <c r="AH22" s="5" t="n"/>
-      <c r="AI22" s="5" t="n"/>
-      <c r="AJ22" s="5" t="n"/>
+      <c r="AI22">
+        <f>IF(COUNT(B22:AH22)=0,"",SUM(B22:AH22))</f>
+        <v/>
+      </c>
+      <c r="AJ22">
+        <f>COUNT(B22:AH22)</f>
+        <v/>
+      </c>
       <c r="AK22">
-        <f>IF(COUNT(B22:AJ22)=0,"",SUM(B22:AJ22))</f>
-        <v/>
-      </c>
-      <c r="AL22">
-        <f>COUNT(B22:AJ22)</f>
-        <v/>
-      </c>
-      <c r="AM22">
-        <f>IF(OR(AK22="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK22,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK22,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI22="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI22,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI22,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1983,18 +1921,16 @@
       <c r="AF23" s="5" t="n"/>
       <c r="AG23" s="5" t="n"/>
       <c r="AH23" s="5" t="n"/>
-      <c r="AI23" s="5" t="n"/>
-      <c r="AJ23" s="5" t="n"/>
+      <c r="AI23">
+        <f>IF(COUNT(B23:AH23)=0,"",SUM(B23:AH23))</f>
+        <v/>
+      </c>
+      <c r="AJ23">
+        <f>COUNT(B23:AH23)</f>
+        <v/>
+      </c>
       <c r="AK23">
-        <f>IF(COUNT(B23:AJ23)=0,"",SUM(B23:AJ23))</f>
-        <v/>
-      </c>
-      <c r="AL23">
-        <f>COUNT(B23:AJ23)</f>
-        <v/>
-      </c>
-      <c r="AM23">
-        <f>IF(OR(AK23="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK23,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK23,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI23="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI23,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI23,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2035,18 +1971,16 @@
       <c r="AF24" s="5" t="n"/>
       <c r="AG24" s="5" t="n"/>
       <c r="AH24" s="5" t="n"/>
-      <c r="AI24" s="5" t="n"/>
-      <c r="AJ24" s="5" t="n"/>
+      <c r="AI24">
+        <f>IF(COUNT(B24:AH24)=0,"",SUM(B24:AH24))</f>
+        <v/>
+      </c>
+      <c r="AJ24">
+        <f>COUNT(B24:AH24)</f>
+        <v/>
+      </c>
       <c r="AK24">
-        <f>IF(COUNT(B24:AJ24)=0,"",SUM(B24:AJ24))</f>
-        <v/>
-      </c>
-      <c r="AL24">
-        <f>COUNT(B24:AJ24)</f>
-        <v/>
-      </c>
-      <c r="AM24">
-        <f>IF(OR(AK24="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK24,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK24,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI24="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI24,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI24,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2087,18 +2021,16 @@
       <c r="AF25" s="5" t="n"/>
       <c r="AG25" s="5" t="n"/>
       <c r="AH25" s="5" t="n"/>
-      <c r="AI25" s="5" t="n"/>
-      <c r="AJ25" s="5" t="n"/>
+      <c r="AI25">
+        <f>IF(COUNT(B25:AH25)=0,"",SUM(B25:AH25))</f>
+        <v/>
+      </c>
+      <c r="AJ25">
+        <f>COUNT(B25:AH25)</f>
+        <v/>
+      </c>
       <c r="AK25">
-        <f>IF(COUNT(B25:AJ25)=0,"",SUM(B25:AJ25))</f>
-        <v/>
-      </c>
-      <c r="AL25">
-        <f>COUNT(B25:AJ25)</f>
-        <v/>
-      </c>
-      <c r="AM25">
-        <f>IF(OR(AK25="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK25,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK25,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI25="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI25,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI25,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2139,18 +2071,16 @@
       <c r="AF26" s="5" t="n"/>
       <c r="AG26" s="5" t="n"/>
       <c r="AH26" s="5" t="n"/>
-      <c r="AI26" s="5" t="n"/>
-      <c r="AJ26" s="5" t="n"/>
+      <c r="AI26">
+        <f>IF(COUNT(B26:AH26)=0,"",SUM(B26:AH26))</f>
+        <v/>
+      </c>
+      <c r="AJ26">
+        <f>COUNT(B26:AH26)</f>
+        <v/>
+      </c>
       <c r="AK26">
-        <f>IF(COUNT(B26:AJ26)=0,"",SUM(B26:AJ26))</f>
-        <v/>
-      </c>
-      <c r="AL26">
-        <f>COUNT(B26:AJ26)</f>
-        <v/>
-      </c>
-      <c r="AM26">
-        <f>IF(OR(AK26="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK26,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK26,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI26="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI26,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI26,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2191,18 +2121,16 @@
       <c r="AF27" s="5" t="n"/>
       <c r="AG27" s="5" t="n"/>
       <c r="AH27" s="5" t="n"/>
-      <c r="AI27" s="5" t="n"/>
-      <c r="AJ27" s="5" t="n"/>
+      <c r="AI27">
+        <f>IF(COUNT(B27:AH27)=0,"",SUM(B27:AH27))</f>
+        <v/>
+      </c>
+      <c r="AJ27">
+        <f>COUNT(B27:AH27)</f>
+        <v/>
+      </c>
       <c r="AK27">
-        <f>IF(COUNT(B27:AJ27)=0,"",SUM(B27:AJ27))</f>
-        <v/>
-      </c>
-      <c r="AL27">
-        <f>COUNT(B27:AJ27)</f>
-        <v/>
-      </c>
-      <c r="AM27">
-        <f>IF(OR(AK27="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK27,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK27,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI27="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI27,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI27,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2243,18 +2171,16 @@
       <c r="AF28" s="5" t="n"/>
       <c r="AG28" s="5" t="n"/>
       <c r="AH28" s="5" t="n"/>
-      <c r="AI28" s="5" t="n"/>
-      <c r="AJ28" s="5" t="n"/>
+      <c r="AI28">
+        <f>IF(COUNT(B28:AH28)=0,"",SUM(B28:AH28))</f>
+        <v/>
+      </c>
+      <c r="AJ28">
+        <f>COUNT(B28:AH28)</f>
+        <v/>
+      </c>
       <c r="AK28">
-        <f>IF(COUNT(B28:AJ28)=0,"",SUM(B28:AJ28))</f>
-        <v/>
-      </c>
-      <c r="AL28">
-        <f>COUNT(B28:AJ28)</f>
-        <v/>
-      </c>
-      <c r="AM28">
-        <f>IF(OR(AK28="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK28,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK28,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI28="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI28,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI28,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2295,18 +2221,16 @@
       <c r="AF29" s="5" t="n"/>
       <c r="AG29" s="5" t="n"/>
       <c r="AH29" s="5" t="n"/>
-      <c r="AI29" s="5" t="n"/>
-      <c r="AJ29" s="5" t="n"/>
+      <c r="AI29">
+        <f>IF(COUNT(B29:AH29)=0,"",SUM(B29:AH29))</f>
+        <v/>
+      </c>
+      <c r="AJ29">
+        <f>COUNT(B29:AH29)</f>
+        <v/>
+      </c>
       <c r="AK29">
-        <f>IF(COUNT(B29:AJ29)=0,"",SUM(B29:AJ29))</f>
-        <v/>
-      </c>
-      <c r="AL29">
-        <f>COUNT(B29:AJ29)</f>
-        <v/>
-      </c>
-      <c r="AM29">
-        <f>IF(OR(AK29="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK29,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK29,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI29="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI29,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI29,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2347,18 +2271,16 @@
       <c r="AF30" s="5" t="n"/>
       <c r="AG30" s="5" t="n"/>
       <c r="AH30" s="5" t="n"/>
-      <c r="AI30" s="5" t="n"/>
-      <c r="AJ30" s="5" t="n"/>
+      <c r="AI30">
+        <f>IF(COUNT(B30:AH30)=0,"",SUM(B30:AH30))</f>
+        <v/>
+      </c>
+      <c r="AJ30">
+        <f>COUNT(B30:AH30)</f>
+        <v/>
+      </c>
       <c r="AK30">
-        <f>IF(COUNT(B30:AJ30)=0,"",SUM(B30:AJ30))</f>
-        <v/>
-      </c>
-      <c r="AL30">
-        <f>COUNT(B30:AJ30)</f>
-        <v/>
-      </c>
-      <c r="AM30">
-        <f>IF(OR(AK30="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK30,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK30,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI30="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI30,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI30,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2399,18 +2321,16 @@
       <c r="AF31" s="5" t="n"/>
       <c r="AG31" s="5" t="n"/>
       <c r="AH31" s="5" t="n"/>
-      <c r="AI31" s="5" t="n"/>
-      <c r="AJ31" s="5" t="n"/>
+      <c r="AI31">
+        <f>IF(COUNT(B31:AH31)=0,"",SUM(B31:AH31))</f>
+        <v/>
+      </c>
+      <c r="AJ31">
+        <f>COUNT(B31:AH31)</f>
+        <v/>
+      </c>
       <c r="AK31">
-        <f>IF(COUNT(B31:AJ31)=0,"",SUM(B31:AJ31))</f>
-        <v/>
-      </c>
-      <c r="AL31">
-        <f>COUNT(B31:AJ31)</f>
-        <v/>
-      </c>
-      <c r="AM31">
-        <f>IF(OR(AK31="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK31,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK31,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI31="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI31,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI31,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2451,18 +2371,16 @@
       <c r="AF32" s="5" t="n"/>
       <c r="AG32" s="5" t="n"/>
       <c r="AH32" s="5" t="n"/>
-      <c r="AI32" s="5" t="n"/>
-      <c r="AJ32" s="5" t="n"/>
+      <c r="AI32">
+        <f>IF(COUNT(B32:AH32)=0,"",SUM(B32:AH32))</f>
+        <v/>
+      </c>
+      <c r="AJ32">
+        <f>COUNT(B32:AH32)</f>
+        <v/>
+      </c>
       <c r="AK32">
-        <f>IF(COUNT(B32:AJ32)=0,"",SUM(B32:AJ32))</f>
-        <v/>
-      </c>
-      <c r="AL32">
-        <f>COUNT(B32:AJ32)</f>
-        <v/>
-      </c>
-      <c r="AM32">
-        <f>IF(OR(AK32="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK32,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK32,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI32="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI32,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI32,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2503,18 +2421,16 @@
       <c r="AF33" s="5" t="n"/>
       <c r="AG33" s="5" t="n"/>
       <c r="AH33" s="5" t="n"/>
-      <c r="AI33" s="5" t="n"/>
-      <c r="AJ33" s="5" t="n"/>
+      <c r="AI33">
+        <f>IF(COUNT(B33:AH33)=0,"",SUM(B33:AH33))</f>
+        <v/>
+      </c>
+      <c r="AJ33">
+        <f>COUNT(B33:AH33)</f>
+        <v/>
+      </c>
       <c r="AK33">
-        <f>IF(COUNT(B33:AJ33)=0,"",SUM(B33:AJ33))</f>
-        <v/>
-      </c>
-      <c r="AL33">
-        <f>COUNT(B33:AJ33)</f>
-        <v/>
-      </c>
-      <c r="AM33">
-        <f>IF(OR(AK33="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK33,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK33,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI33="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI33,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI33,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2555,18 +2471,16 @@
       <c r="AF34" s="5" t="n"/>
       <c r="AG34" s="5" t="n"/>
       <c r="AH34" s="5" t="n"/>
-      <c r="AI34" s="5" t="n"/>
-      <c r="AJ34" s="5" t="n"/>
+      <c r="AI34">
+        <f>IF(COUNT(B34:AH34)=0,"",SUM(B34:AH34))</f>
+        <v/>
+      </c>
+      <c r="AJ34">
+        <f>COUNT(B34:AH34)</f>
+        <v/>
+      </c>
       <c r="AK34">
-        <f>IF(COUNT(B34:AJ34)=0,"",SUM(B34:AJ34))</f>
-        <v/>
-      </c>
-      <c r="AL34">
-        <f>COUNT(B34:AJ34)</f>
-        <v/>
-      </c>
-      <c r="AM34">
-        <f>IF(OR(AK34="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK34,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK34,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI34="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI34,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI34,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2607,18 +2521,16 @@
       <c r="AF35" s="5" t="n"/>
       <c r="AG35" s="5" t="n"/>
       <c r="AH35" s="5" t="n"/>
-      <c r="AI35" s="5" t="n"/>
-      <c r="AJ35" s="5" t="n"/>
+      <c r="AI35">
+        <f>IF(COUNT(B35:AH35)=0,"",SUM(B35:AH35))</f>
+        <v/>
+      </c>
+      <c r="AJ35">
+        <f>COUNT(B35:AH35)</f>
+        <v/>
+      </c>
       <c r="AK35">
-        <f>IF(COUNT(B35:AJ35)=0,"",SUM(B35:AJ35))</f>
-        <v/>
-      </c>
-      <c r="AL35">
-        <f>COUNT(B35:AJ35)</f>
-        <v/>
-      </c>
-      <c r="AM35">
-        <f>IF(OR(AK35="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK35,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK35,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI35="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI35,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI35,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2659,18 +2571,16 @@
       <c r="AF36" s="5" t="n"/>
       <c r="AG36" s="5" t="n"/>
       <c r="AH36" s="5" t="n"/>
-      <c r="AI36" s="5" t="n"/>
-      <c r="AJ36" s="5" t="n"/>
+      <c r="AI36">
+        <f>IF(COUNT(B36:AH36)=0,"",SUM(B36:AH36))</f>
+        <v/>
+      </c>
+      <c r="AJ36">
+        <f>COUNT(B36:AH36)</f>
+        <v/>
+      </c>
       <c r="AK36">
-        <f>IF(COUNT(B36:AJ36)=0,"",SUM(B36:AJ36))</f>
-        <v/>
-      </c>
-      <c r="AL36">
-        <f>COUNT(B36:AJ36)</f>
-        <v/>
-      </c>
-      <c r="AM36">
-        <f>IF(OR(AK36="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK36,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK36,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI36="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI36,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI36,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2711,18 +2621,16 @@
       <c r="AF37" s="5" t="n"/>
       <c r="AG37" s="5" t="n"/>
       <c r="AH37" s="5" t="n"/>
-      <c r="AI37" s="5" t="n"/>
-      <c r="AJ37" s="5" t="n"/>
+      <c r="AI37">
+        <f>IF(COUNT(B37:AH37)=0,"",SUM(B37:AH37))</f>
+        <v/>
+      </c>
+      <c r="AJ37">
+        <f>COUNT(B37:AH37)</f>
+        <v/>
+      </c>
       <c r="AK37">
-        <f>IF(COUNT(B37:AJ37)=0,"",SUM(B37:AJ37))</f>
-        <v/>
-      </c>
-      <c r="AL37">
-        <f>COUNT(B37:AJ37)</f>
-        <v/>
-      </c>
-      <c r="AM37">
-        <f>IF(OR(AK37="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK37,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK37,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI37="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI37,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI37,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2763,18 +2671,16 @@
       <c r="AF38" s="5" t="n"/>
       <c r="AG38" s="5" t="n"/>
       <c r="AH38" s="5" t="n"/>
-      <c r="AI38" s="5" t="n"/>
-      <c r="AJ38" s="5" t="n"/>
+      <c r="AI38">
+        <f>IF(COUNT(B38:AH38)=0,"",SUM(B38:AH38))</f>
+        <v/>
+      </c>
+      <c r="AJ38">
+        <f>COUNT(B38:AH38)</f>
+        <v/>
+      </c>
       <c r="AK38">
-        <f>IF(COUNT(B38:AJ38)=0,"",SUM(B38:AJ38))</f>
-        <v/>
-      </c>
-      <c r="AL38">
-        <f>COUNT(B38:AJ38)</f>
-        <v/>
-      </c>
-      <c r="AM38">
-        <f>IF(OR(AK38="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK38,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK38,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI38="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI38,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI38,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2815,18 +2721,16 @@
       <c r="AF39" s="5" t="n"/>
       <c r="AG39" s="5" t="n"/>
       <c r="AH39" s="5" t="n"/>
-      <c r="AI39" s="5" t="n"/>
-      <c r="AJ39" s="5" t="n"/>
+      <c r="AI39">
+        <f>IF(COUNT(B39:AH39)=0,"",SUM(B39:AH39))</f>
+        <v/>
+      </c>
+      <c r="AJ39">
+        <f>COUNT(B39:AH39)</f>
+        <v/>
+      </c>
       <c r="AK39">
-        <f>IF(COUNT(B39:AJ39)=0,"",SUM(B39:AJ39))</f>
-        <v/>
-      </c>
-      <c r="AL39">
-        <f>COUNT(B39:AJ39)</f>
-        <v/>
-      </c>
-      <c r="AM39">
-        <f>IF(OR(AK39="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK39,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK39,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AI39="",COUNT($AI$5:$AI$39)&lt;3),"",IF(RANK(AI39,$AI$5:$AI$39,0)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"top",IF(RANK(AI39,$AI$5:$AI$39,1)&lt;=ROUND(COUNT($AI$5:$AI$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2841,7 +2745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="13" max="13"/>
@@ -2950,7 +2854,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>It prints 2 and 1. The true figures are 2.36 and 1.84, a fall of about 22 percent.</t>
+          <t>It prints 2 and 1. The note should say orders per member fell about 22 percent, from 2.36 to 1.84.</t>
         </is>
       </c>
       <c r="G5">
@@ -2966,11 +2870,11 @@
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="L5" s="6">
@@ -2995,22 +2899,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Order the steps</t>
+          <t>Fill in the blank</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>c, b, e, f, a, d</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G6">
@@ -3026,11 +2930,11 @@
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="L6" s="6">
@@ -3065,12 +2969,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G7">
@@ -3086,11 +2990,11 @@
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="L7" s="6">
@@ -3115,22 +3019,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fill in the blank</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G8">
@@ -3146,11 +3050,11 @@
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="L8" s="6">
@@ -3190,7 +3094,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G9">
@@ -3206,11 +3110,11 @@
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="L9" s="6">
@@ -3266,11 +3170,11 @@
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="L10" s="6">
@@ -3310,7 +3214,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G11">
@@ -3326,11 +3230,11 @@
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="L11" s="6">
@@ -3386,11 +3290,11 @@
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="L12" s="6">
@@ -3446,11 +3350,11 @@
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="L13" s="6">
@@ -3480,7 +3384,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3506,11 +3410,11 @@
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="L14" s="6">
@@ -3550,7 +3454,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>b, d</t>
+          <t>c, e</t>
         </is>
       </c>
       <c r="G15">
@@ -3566,11 +3470,11 @@
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="L15" s="6">
@@ -3595,7 +3499,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3605,12 +3509,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G16">
@@ -3626,11 +3530,11 @@
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="L16" s="6">
@@ -3655,7 +3559,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3665,12 +3569,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G17">
@@ -3686,11 +3590,11 @@
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="L17" s="6">
@@ -3730,7 +3634,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G18">
@@ -3746,11 +3650,11 @@
         <v/>
       </c>
       <c r="J18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="L18" s="6">
@@ -3790,7 +3694,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G19">
@@ -3806,11 +3710,11 @@
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="L19" s="6">
@@ -3850,7 +3754,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G20">
@@ -3866,11 +3770,11 @@
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="L20" s="6">
@@ -3900,7 +3804,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3910,7 +3814,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G21">
@@ -3926,11 +3830,11 @@
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="L21" s="6">
@@ -3960,12 +3864,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3986,11 +3890,11 @@
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="L22" s="6">
@@ -4015,22 +3919,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>a, e</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G23">
@@ -4046,11 +3950,11 @@
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="L23" s="6">
@@ -4075,7 +3979,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4090,7 +3994,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G24">
@@ -4106,11 +4010,11 @@
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="L24" s="6">
@@ -4131,26 +4035,26 @@
         <v>21</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Match the following</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G25">
@@ -4166,11 +4070,11 @@
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="L25" s="6">
@@ -4191,21 +4095,21 @@
         <v>22</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Match the following</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4226,11 +4130,11 @@
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="L26" s="6">
@@ -4270,7 +4174,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>f</t>
         </is>
       </c>
       <c r="G27">
@@ -4286,11 +4190,11 @@
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="L27" s="6">
@@ -4325,12 +4229,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G28">
@@ -4346,11 +4250,11 @@
         <v/>
       </c>
       <c r="J28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="L28" s="6">
@@ -4375,12 +4279,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Match the following</t>
+          <t>Applied maths</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4390,7 +4294,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>The sheet reports -0.5 against 1.5, a gap of 2 points; B8 stops at row 5, and over all six countries both columns average 1.5, so the gap disappears.</t>
         </is>
       </c>
       <c r="G29">
@@ -4406,11 +4310,11 @@
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="L29" s="6">
@@ -4435,12 +4339,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Match the following</t>
+          <t>Applied maths</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4450,7 +4354,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Column D halves every change, 0.130 against 0.261, so the value at risk should read 140 million dollars, 20 million over the limit.</t>
         </is>
       </c>
       <c r="G30">
@@ -4466,11 +4370,11 @@
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="L30" s="6">
@@ -4510,7 +4414,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>B8 returns -0.5; the six rows average 1.0; the formula understates growth by 1.5 points and turns growth into a fall.</t>
+          <t>2.00 dollars, about 8.5 percent of the 23.50 dollars charged</t>
         </is>
       </c>
       <c r="G31">
@@ -4526,11 +4430,11 @@
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="L31" s="6">
@@ -4551,7 +4455,7 @@
         <v>28</v>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4565,12 +4469,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G32">
@@ -4586,11 +4490,11 @@
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="L32" s="6">
@@ -4611,11 +4515,11 @@
         <v>29</v>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Applied maths</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4625,12 +4529,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2.00 dollars, about 8.5 percent of the 23.50 dollars charged</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G33">
@@ -4646,11 +4550,11 @@
         <v/>
       </c>
       <c r="J33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="L33" s="6">
@@ -4685,12 +4589,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G34">
@@ -4706,11 +4610,11 @@
         <v/>
       </c>
       <c r="J34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="L34" s="6">
@@ -4745,12 +4649,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G35">
@@ -4766,11 +4670,11 @@
         <v/>
       </c>
       <c r="J35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="L35" s="6">
@@ -4805,7 +4709,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4826,11 +4730,11 @@
         <v/>
       </c>
       <c r="J36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="L36" s="6">
@@ -4860,7 +4764,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4870,7 +4774,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G37">
@@ -4886,11 +4790,11 @@
         <v/>
       </c>
       <c r="J37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="K37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AK$5:$AK$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="L37" s="6">
@@ -4903,126 +4807,6 @@
       </c>
       <c r="N37">
         <f>IF(H37=0,"",I37+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" t="n">
-        <v>6</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G38">
-        <f>COUNTIF(Marks!AI$5:AI$39,1)</f>
-        <v/>
-      </c>
-      <c r="H38">
-        <f>COUNT(Marks!AI$5:AI$39)</f>
-        <v/>
-      </c>
-      <c r="I38" s="6">
-        <f>IF(H38=0,"",G38/H38)</f>
-        <v/>
-      </c>
-      <c r="J38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
-        <v/>
-      </c>
-      <c r="K38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
-        <v/>
-      </c>
-      <c r="L38" s="6">
-        <f>IF(OR(J38="",K38=""),"",J38-K38)</f>
-        <v/>
-      </c>
-      <c r="M38">
-        <f>IF(H38=0,"",IF(I38&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L38&lt;&gt;"",N(L38)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N38">
-        <f>IF(H38=0,"",I38+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" t="n">
-        <v>6</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="G39">
-        <f>COUNTIF(Marks!AJ$5:AJ$39,1)</f>
-        <v/>
-      </c>
-      <c r="H39">
-        <f>COUNT(Marks!AJ$5:AJ$39)</f>
-        <v/>
-      </c>
-      <c r="I39" s="6">
-        <f>IF(H39=0,"",G39/H39)</f>
-        <v/>
-      </c>
-      <c r="J39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
-        <v/>
-      </c>
-      <c r="K39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
-        <v/>
-      </c>
-      <c r="L39" s="6">
-        <f>IF(OR(J39="",K39=""),"",J39-K39)</f>
-        <v/>
-      </c>
-      <c r="M39">
-        <f>IF(H39=0,"",IF(I39&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L39&lt;&gt;"",N(L39)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N39">
-        <f>IF(H39=0,"",I39+ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -5037,7 +4821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -5052,7 +4836,7 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>IF(SUM(Items!H5:H39)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
+        <f>IF(SUM(Items!H5:H37)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
         <v/>
       </c>
     </row>
@@ -5093,23 +4877,23 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A5,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A5),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A5,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A5),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(B5="","",INDEX(Items!$I$5:$I$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$I$5:$I$37,MATCH(B5,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D5">
-        <f>IF(B5="","",INDEX(Items!$B$5:$B$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$B$5:$B$37,MATCH(B5,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E5">
-        <f>IF(B5="","",INDEX(Items!$E$5:$E$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$E$5:$E$37,MATCH(B5,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F5">
-        <f>IF(B5="","",INDEX(Items!$M$5:$M$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$M$5:$M$37,MATCH(B5,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5118,23 +4902,23 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A6,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A6),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A6,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A6),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(B6="","",INDEX(Items!$I$5:$I$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$I$5:$I$37,MATCH(B6,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IF(B6="","",INDEX(Items!$B$5:$B$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$B$5:$B$37,MATCH(B6,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E6">
-        <f>IF(B6="","",INDEX(Items!$E$5:$E$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$E$5:$E$37,MATCH(B6,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IF(B6="","",INDEX(Items!$M$5:$M$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$M$5:$M$37,MATCH(B6,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5143,23 +4927,23 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A7,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A7),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A7,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A7),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(B7="","",INDEX(Items!$I$5:$I$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$I$5:$I$37,MATCH(B7,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D7">
-        <f>IF(B7="","",INDEX(Items!$B$5:$B$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$B$5:$B$37,MATCH(B7,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E7">
-        <f>IF(B7="","",INDEX(Items!$E$5:$E$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$E$5:$E$37,MATCH(B7,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F7">
-        <f>IF(B7="","",INDEX(Items!$M$5:$M$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$M$5:$M$37,MATCH(B7,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5168,23 +4952,23 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A8,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A8),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A8,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A8),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(B8="","",INDEX(Items!$I$5:$I$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$I$5:$I$37,MATCH(B8,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D8">
-        <f>IF(B8="","",INDEX(Items!$B$5:$B$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$B$5:$B$37,MATCH(B8,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E8">
-        <f>IF(B8="","",INDEX(Items!$E$5:$E$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$E$5:$E$37,MATCH(B8,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F8">
-        <f>IF(B8="","",INDEX(Items!$M$5:$M$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$M$5:$M$37,MATCH(B8,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5193,23 +4977,23 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A9,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A9),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A9,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A9),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(B9="","",INDEX(Items!$I$5:$I$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$I$5:$I$37,MATCH(B9,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D9">
-        <f>IF(B9="","",INDEX(Items!$B$5:$B$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$B$5:$B$37,MATCH(B9,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E9">
-        <f>IF(B9="","",INDEX(Items!$E$5:$E$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$E$5:$E$37,MATCH(B9,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F9">
-        <f>IF(B9="","",INDEX(Items!$M$5:$M$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$M$5:$M$37,MATCH(B9,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5218,23 +5002,23 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A10,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A10),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A10,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A10),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(B10="","",INDEX(Items!$I$5:$I$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$I$5:$I$37,MATCH(B10,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D10">
-        <f>IF(B10="","",INDEX(Items!$B$5:$B$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$B$5:$B$37,MATCH(B10,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E10">
-        <f>IF(B10="","",INDEX(Items!$E$5:$E$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$E$5:$E$37,MATCH(B10,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F10">
-        <f>IF(B10="","",INDEX(Items!$M$5:$M$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$M$5:$M$37,MATCH(B10,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5243,23 +5027,23 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A11,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A11),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A11,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A11),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(B11="","",INDEX(Items!$I$5:$I$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$I$5:$I$37,MATCH(B11,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D11">
-        <f>IF(B11="","",INDEX(Items!$B$5:$B$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$B$5:$B$37,MATCH(B11,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E11">
-        <f>IF(B11="","",INDEX(Items!$E$5:$E$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$E$5:$E$37,MATCH(B11,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F11">
-        <f>IF(B11="","",INDEX(Items!$M$5:$M$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$M$5:$M$37,MATCH(B11,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5268,23 +5052,23 @@
         <v>8</v>
       </c>
       <c r="B12">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A12,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A12),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A12,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A12),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(B12="","",INDEX(Items!$I$5:$I$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$I$5:$I$37,MATCH(B12,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IF(B12="","",INDEX(Items!$B$5:$B$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$B$5:$B$37,MATCH(B12,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IF(B12="","",INDEX(Items!$E$5:$E$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$E$5:$E$37,MATCH(B12,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IF(B12="","",INDEX(Items!$M$5:$M$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$M$5:$M$37,MATCH(B12,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5293,23 +5077,23 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A13,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A13),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A13,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A13),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(B13="","",INDEX(Items!$I$5:$I$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$I$5:$I$37,MATCH(B13,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D13">
-        <f>IF(B13="","",INDEX(Items!$B$5:$B$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$B$5:$B$37,MATCH(B13,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E13">
-        <f>IF(B13="","",INDEX(Items!$E$5:$E$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$E$5:$E$37,MATCH(B13,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F13">
-        <f>IF(B13="","",INDEX(Items!$M$5:$M$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$M$5:$M$37,MATCH(B13,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5318,23 +5102,23 @@
         <v>10</v>
       </c>
       <c r="B14">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A14,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A14),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A14,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A14),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(B14="","",INDEX(Items!$I$5:$I$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$I$5:$I$37,MATCH(B14,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D14">
-        <f>IF(B14="","",INDEX(Items!$B$5:$B$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$B$5:$B$37,MATCH(B14,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E14">
-        <f>IF(B14="","",INDEX(Items!$E$5:$E$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$E$5:$E$37,MATCH(B14,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F14">
-        <f>IF(B14="","",INDEX(Items!$M$5:$M$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$M$5:$M$37,MATCH(B14,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5343,23 +5127,23 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A15,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A15),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A15,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A15),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(B15="","",INDEX(Items!$I$5:$I$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$I$5:$I$37,MATCH(B15,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D15">
-        <f>IF(B15="","",INDEX(Items!$B$5:$B$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$B$5:$B$37,MATCH(B15,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E15">
-        <f>IF(B15="","",INDEX(Items!$E$5:$E$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$E$5:$E$37,MATCH(B15,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F15">
-        <f>IF(B15="","",INDEX(Items!$M$5:$M$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$M$5:$M$37,MATCH(B15,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5368,23 +5152,23 @@
         <v>12</v>
       </c>
       <c r="B16">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A16,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A16),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A16,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A16),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(B16="","",INDEX(Items!$I$5:$I$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$I$5:$I$37,MATCH(B16,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D16">
-        <f>IF(B16="","",INDEX(Items!$B$5:$B$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$B$5:$B$37,MATCH(B16,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E16">
-        <f>IF(B16="","",INDEX(Items!$E$5:$E$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$E$5:$E$37,MATCH(B16,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F16">
-        <f>IF(B16="","",INDEX(Items!$M$5:$M$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$M$5:$M$37,MATCH(B16,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5393,23 +5177,23 @@
         <v>13</v>
       </c>
       <c r="B17">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A17,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A17),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A17,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A17),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(B17="","",INDEX(Items!$I$5:$I$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$I$5:$I$37,MATCH(B17,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D17">
-        <f>IF(B17="","",INDEX(Items!$B$5:$B$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$B$5:$B$37,MATCH(B17,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E17">
-        <f>IF(B17="","",INDEX(Items!$E$5:$E$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$E$5:$E$37,MATCH(B17,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F17">
-        <f>IF(B17="","",INDEX(Items!$M$5:$M$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$M$5:$M$37,MATCH(B17,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5418,23 +5202,23 @@
         <v>14</v>
       </c>
       <c r="B18">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A18,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A18),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A18,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A18),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(B18="","",INDEX(Items!$I$5:$I$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$I$5:$I$37,MATCH(B18,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D18">
-        <f>IF(B18="","",INDEX(Items!$B$5:$B$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$B$5:$B$37,MATCH(B18,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E18">
-        <f>IF(B18="","",INDEX(Items!$E$5:$E$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$E$5:$E$37,MATCH(B18,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F18">
-        <f>IF(B18="","",INDEX(Items!$M$5:$M$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$M$5:$M$37,MATCH(B18,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5443,23 +5227,23 @@
         <v>15</v>
       </c>
       <c r="B19">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A19,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A19),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A19,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A19),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(B19="","",INDEX(Items!$I$5:$I$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$I$5:$I$37,MATCH(B19,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D19">
-        <f>IF(B19="","",INDEX(Items!$B$5:$B$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$B$5:$B$37,MATCH(B19,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E19">
-        <f>IF(B19="","",INDEX(Items!$E$5:$E$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$E$5:$E$37,MATCH(B19,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F19">
-        <f>IF(B19="","",INDEX(Items!$M$5:$M$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$M$5:$M$37,MATCH(B19,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5468,23 +5252,23 @@
         <v>16</v>
       </c>
       <c r="B20">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A20,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A20),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A20,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A20),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(B20="","",INDEX(Items!$I$5:$I$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$I$5:$I$37,MATCH(B20,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D20">
-        <f>IF(B20="","",INDEX(Items!$B$5:$B$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$B$5:$B$37,MATCH(B20,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E20">
-        <f>IF(B20="","",INDEX(Items!$E$5:$E$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$E$5:$E$37,MATCH(B20,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F20">
-        <f>IF(B20="","",INDEX(Items!$M$5:$M$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$M$5:$M$37,MATCH(B20,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5493,23 +5277,23 @@
         <v>17</v>
       </c>
       <c r="B21">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A21,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A21),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A21,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A21),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(B21="","",INDEX(Items!$I$5:$I$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$I$5:$I$37,MATCH(B21,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D21">
-        <f>IF(B21="","",INDEX(Items!$B$5:$B$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$B$5:$B$37,MATCH(B21,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E21">
-        <f>IF(B21="","",INDEX(Items!$E$5:$E$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$E$5:$E$37,MATCH(B21,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F21">
-        <f>IF(B21="","",INDEX(Items!$M$5:$M$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$M$5:$M$37,MATCH(B21,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5518,23 +5302,23 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A22,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A22),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A22,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A22),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(B22="","",INDEX(Items!$I$5:$I$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$I$5:$I$37,MATCH(B22,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D22">
-        <f>IF(B22="","",INDEX(Items!$B$5:$B$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$B$5:$B$37,MATCH(B22,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E22">
-        <f>IF(B22="","",INDEX(Items!$E$5:$E$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$E$5:$E$37,MATCH(B22,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F22">
-        <f>IF(B22="","",INDEX(Items!$M$5:$M$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$M$5:$M$37,MATCH(B22,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5543,23 +5327,23 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A23,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A23),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A23,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A23),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(B23="","",INDEX(Items!$I$5:$I$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$I$5:$I$37,MATCH(B23,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D23">
-        <f>IF(B23="","",INDEX(Items!$B$5:$B$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$B$5:$B$37,MATCH(B23,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E23">
-        <f>IF(B23="","",INDEX(Items!$E$5:$E$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$E$5:$E$37,MATCH(B23,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F23">
-        <f>IF(B23="","",INDEX(Items!$M$5:$M$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$M$5:$M$37,MATCH(B23,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5568,23 +5352,23 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A24,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A24),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A24,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A24),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(B24="","",INDEX(Items!$I$5:$I$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$I$5:$I$37,MATCH(B24,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D24">
-        <f>IF(B24="","",INDEX(Items!$B$5:$B$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$B$5:$B$37,MATCH(B24,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E24">
-        <f>IF(B24="","",INDEX(Items!$E$5:$E$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$E$5:$E$37,MATCH(B24,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F24">
-        <f>IF(B24="","",INDEX(Items!$M$5:$M$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$M$5:$M$37,MATCH(B24,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5593,23 +5377,23 @@
         <v>21</v>
       </c>
       <c r="B25">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A25,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A25),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A25,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A25),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(B25="","",INDEX(Items!$I$5:$I$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$I$5:$I$37,MATCH(B25,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D25">
-        <f>IF(B25="","",INDEX(Items!$B$5:$B$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$B$5:$B$37,MATCH(B25,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E25">
-        <f>IF(B25="","",INDEX(Items!$E$5:$E$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$E$5:$E$37,MATCH(B25,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F25">
-        <f>IF(B25="","",INDEX(Items!$M$5:$M$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$M$5:$M$37,MATCH(B25,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5618,23 +5402,23 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A26,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A26),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A26,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A26),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(B26="","",INDEX(Items!$I$5:$I$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$I$5:$I$37,MATCH(B26,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D26">
-        <f>IF(B26="","",INDEX(Items!$B$5:$B$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$B$5:$B$37,MATCH(B26,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E26">
-        <f>IF(B26="","",INDEX(Items!$E$5:$E$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$E$5:$E$37,MATCH(B26,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F26">
-        <f>IF(B26="","",INDEX(Items!$M$5:$M$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$M$5:$M$37,MATCH(B26,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5643,23 +5427,23 @@
         <v>23</v>
       </c>
       <c r="B27">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A27,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A27),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A27,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A27),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(B27="","",INDEX(Items!$I$5:$I$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$I$5:$I$37,MATCH(B27,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D27">
-        <f>IF(B27="","",INDEX(Items!$B$5:$B$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$B$5:$B$37,MATCH(B27,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E27">
-        <f>IF(B27="","",INDEX(Items!$E$5:$E$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$E$5:$E$37,MATCH(B27,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F27">
-        <f>IF(B27="","",INDEX(Items!$M$5:$M$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$M$5:$M$37,MATCH(B27,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5668,23 +5452,23 @@
         <v>24</v>
       </c>
       <c r="B28">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A28,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A28),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A28,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A28),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(B28="","",INDEX(Items!$I$5:$I$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$I$5:$I$37,MATCH(B28,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D28">
-        <f>IF(B28="","",INDEX(Items!$B$5:$B$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$B$5:$B$37,MATCH(B28,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E28">
-        <f>IF(B28="","",INDEX(Items!$E$5:$E$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$E$5:$E$37,MATCH(B28,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F28">
-        <f>IF(B28="","",INDEX(Items!$M$5:$M$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$M$5:$M$37,MATCH(B28,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5693,23 +5477,23 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A29,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A29),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A29,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A29),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(B29="","",INDEX(Items!$I$5:$I$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$I$5:$I$37,MATCH(B29,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D29">
-        <f>IF(B29="","",INDEX(Items!$B$5:$B$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$B$5:$B$37,MATCH(B29,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E29">
-        <f>IF(B29="","",INDEX(Items!$E$5:$E$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$E$5:$E$37,MATCH(B29,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F29">
-        <f>IF(B29="","",INDEX(Items!$M$5:$M$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$M$5:$M$37,MATCH(B29,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5718,23 +5502,23 @@
         <v>26</v>
       </c>
       <c r="B30">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A30,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A30),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A30,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A30),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(B30="","",INDEX(Items!$I$5:$I$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$I$5:$I$37,MATCH(B30,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D30">
-        <f>IF(B30="","",INDEX(Items!$B$5:$B$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$B$5:$B$37,MATCH(B30,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E30">
-        <f>IF(B30="","",INDEX(Items!$E$5:$E$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$E$5:$E$37,MATCH(B30,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F30">
-        <f>IF(B30="","",INDEX(Items!$M$5:$M$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$M$5:$M$37,MATCH(B30,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5743,23 +5527,23 @@
         <v>27</v>
       </c>
       <c r="B31">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A31,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A31),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A31,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A31),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(B31="","",INDEX(Items!$I$5:$I$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$I$5:$I$37,MATCH(B31,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D31">
-        <f>IF(B31="","",INDEX(Items!$B$5:$B$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$B$5:$B$37,MATCH(B31,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E31">
-        <f>IF(B31="","",INDEX(Items!$E$5:$E$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$E$5:$E$37,MATCH(B31,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F31">
-        <f>IF(B31="","",INDEX(Items!$M$5:$M$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$M$5:$M$37,MATCH(B31,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5768,23 +5552,23 @@
         <v>28</v>
       </c>
       <c r="B32">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A32,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A32),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A32,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A32),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(B32="","",INDEX(Items!$I$5:$I$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$I$5:$I$37,MATCH(B32,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D32">
-        <f>IF(B32="","",INDEX(Items!$B$5:$B$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$B$5:$B$37,MATCH(B32,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E32">
-        <f>IF(B32="","",INDEX(Items!$E$5:$E$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$E$5:$E$37,MATCH(B32,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F32">
-        <f>IF(B32="","",INDEX(Items!$M$5:$M$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$M$5:$M$37,MATCH(B32,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5793,23 +5577,23 @@
         <v>29</v>
       </c>
       <c r="B33">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A33,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A33),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A33,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A33),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(B33="","",INDEX(Items!$I$5:$I$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$I$5:$I$37,MATCH(B33,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D33">
-        <f>IF(B33="","",INDEX(Items!$B$5:$B$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$B$5:$B$37,MATCH(B33,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E33">
-        <f>IF(B33="","",INDEX(Items!$E$5:$E$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$E$5:$E$37,MATCH(B33,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F33">
-        <f>IF(B33="","",INDEX(Items!$M$5:$M$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$M$5:$M$37,MATCH(B33,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5818,23 +5602,23 @@
         <v>30</v>
       </c>
       <c r="B34">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A34,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A34),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A34,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A34),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(B34="","",INDEX(Items!$I$5:$I$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$I$5:$I$37,MATCH(B34,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D34">
-        <f>IF(B34="","",INDEX(Items!$B$5:$B$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$B$5:$B$37,MATCH(B34,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E34">
-        <f>IF(B34="","",INDEX(Items!$E$5:$E$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$E$5:$E$37,MATCH(B34,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F34">
-        <f>IF(B34="","",INDEX(Items!$M$5:$M$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$M$5:$M$37,MATCH(B34,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5843,23 +5627,23 @@
         <v>31</v>
       </c>
       <c r="B35">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A35,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A35),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A35,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A35),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(B35="","",INDEX(Items!$I$5:$I$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$I$5:$I$37,MATCH(B35,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D35">
-        <f>IF(B35="","",INDEX(Items!$B$5:$B$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$B$5:$B$37,MATCH(B35,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E35">
-        <f>IF(B35="","",INDEX(Items!$E$5:$E$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$E$5:$E$37,MATCH(B35,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F35">
-        <f>IF(B35="","",INDEX(Items!$M$5:$M$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$M$5:$M$37,MATCH(B35,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5868,23 +5652,23 @@
         <v>32</v>
       </c>
       <c r="B36">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A36,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A36),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A36,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A36),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(B36="","",INDEX(Items!$I$5:$I$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$I$5:$I$37,MATCH(B36,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D36">
-        <f>IF(B36="","",INDEX(Items!$B$5:$B$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$B$5:$B$37,MATCH(B36,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E36">
-        <f>IF(B36="","",INDEX(Items!$E$5:$E$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$E$5:$E$37,MATCH(B36,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F36">
-        <f>IF(B36="","",INDEX(Items!$M$5:$M$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$M$5:$M$37,MATCH(B36,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -5893,73 +5677,23 @@
         <v>33</v>
       </c>
       <c r="B37">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A37,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A37),Items!$N$5:$N$39,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$37)&lt;A37,"",INDEX(Items!$A$5:$A$37,MATCH(SMALL(Items!$N$5:$N$37,A37),Items!$N$5:$N$37,0)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(B37="","",INDEX(Items!$I$5:$I$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$I$5:$I$37,MATCH(B37,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="D37">
-        <f>IF(B37="","",INDEX(Items!$B$5:$B$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$B$5:$B$37,MATCH(B37,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="E37">
-        <f>IF(B37="","",INDEX(Items!$E$5:$E$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$E$5:$E$37,MATCH(B37,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
       <c r="F37">
-        <f>IF(B37="","",INDEX(Items!$M$5:$M$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A38,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A38),Items!$N$5:$N$39,0)))</f>
-        <v/>
-      </c>
-      <c r="C38" s="6">
-        <f>IF(B38="","",INDEX(Items!$I$5:$I$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
-        <v/>
-      </c>
-      <c r="D38">
-        <f>IF(B38="","",INDEX(Items!$B$5:$B$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
-        <v/>
-      </c>
-      <c r="E38">
-        <f>IF(B38="","",INDEX(Items!$E$5:$E$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
-        <v/>
-      </c>
-      <c r="F38">
-        <f>IF(B38="","",INDEX(Items!$M$5:$M$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39">
-        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A39,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A39),Items!$N$5:$N$39,0)))</f>
-        <v/>
-      </c>
-      <c r="C39" s="6">
-        <f>IF(B39="","",INDEX(Items!$I$5:$I$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
-        <v/>
-      </c>
-      <c r="D39">
-        <f>IF(B39="","",INDEX(Items!$B$5:$B$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
-        <v/>
-      </c>
-      <c r="E39">
-        <f>IF(B39="","",INDEX(Items!$E$5:$E$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
-        <v/>
-      </c>
-      <c r="F39">
-        <f>IF(B39="","",INDEX(Items!$M$5:$M$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$M$5:$M$37,MATCH(B37,Items!$A$5:$A$37,0)))</f>
         <v/>
       </c>
     </row>
@@ -6021,11 +5755,11 @@
         </is>
       </c>
       <c r="C5">
-        <f>COUNTIF(Items!$E$5:$E$39,A5)</f>
+        <f>COUNTIF(Items!$E$5:$E$37,A5)</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$39=A5)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$E$5:$E$39=A5)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$E$5:$E$39=A5)*Items!$H$5:$H$39))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$37=A5)*Items!$H$5:$H$37)=0,"",SUMPRODUCT((Items!$E$5:$E$37=A5)*Items!$G$5:$G$37)/SUMPRODUCT((Items!$E$5:$E$37=A5)*Items!$H$5:$H$37))</f>
         <v/>
       </c>
     </row>
@@ -6041,11 +5775,11 @@
         </is>
       </c>
       <c r="C6">
-        <f>COUNTIF(Items!$E$5:$E$39,A6)</f>
+        <f>COUNTIF(Items!$E$5:$E$37,A6)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$39=A6)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$E$5:$E$39=A6)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$E$5:$E$39=A6)*Items!$H$5:$H$39))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$37=A6)*Items!$H$5:$H$37)=0,"",SUMPRODUCT((Items!$E$5:$E$37=A6)*Items!$G$5:$G$37)/SUMPRODUCT((Items!$E$5:$E$37=A6)*Items!$H$5:$H$37))</f>
         <v/>
       </c>
     </row>
@@ -6061,11 +5795,11 @@
         </is>
       </c>
       <c r="C7">
-        <f>COUNTIF(Items!$E$5:$E$39,A7)</f>
+        <f>COUNTIF(Items!$E$5:$E$37,A7)</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$39=A7)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$E$5:$E$39=A7)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$E$5:$E$39=A7)*Items!$H$5:$H$39))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$37=A7)*Items!$H$5:$H$37)=0,"",SUMPRODUCT((Items!$E$5:$E$37=A7)*Items!$G$5:$G$37)/SUMPRODUCT((Items!$E$5:$E$37=A7)*Items!$H$5:$H$37))</f>
         <v/>
       </c>
     </row>
@@ -6079,11 +5813,11 @@
         </is>
       </c>
       <c r="C8">
-        <f>COUNTIF(Items!$B$5:$B$39,A8)</f>
+        <f>COUNTIF(Items!$B$5:$B$37,A8)</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A8)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A8)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A8)*Items!$H$5:$H$39))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$37=A8)*Items!$H$5:$H$37)=0,"",SUMPRODUCT((Items!$B$5:$B$37=A8)*Items!$G$5:$G$37)/SUMPRODUCT((Items!$B$5:$B$37=A8)*Items!$H$5:$H$37))</f>
         <v/>
       </c>
     </row>
@@ -6097,11 +5831,11 @@
         </is>
       </c>
       <c r="C9">
-        <f>COUNTIF(Items!$B$5:$B$39,A9)</f>
+        <f>COUNTIF(Items!$B$5:$B$37,A9)</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A9)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A9)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A9)*Items!$H$5:$H$39))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$37=A9)*Items!$H$5:$H$37)=0,"",SUMPRODUCT((Items!$B$5:$B$37=A9)*Items!$G$5:$G$37)/SUMPRODUCT((Items!$B$5:$B$37=A9)*Items!$H$5:$H$37))</f>
         <v/>
       </c>
     </row>
@@ -6115,11 +5849,11 @@
         </is>
       </c>
       <c r="C10">
-        <f>COUNTIF(Items!$B$5:$B$39,A10)</f>
+        <f>COUNTIF(Items!$B$5:$B$37,A10)</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A10)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A10)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A10)*Items!$H$5:$H$39))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$37=A10)*Items!$H$5:$H$37)=0,"",SUMPRODUCT((Items!$B$5:$B$37=A10)*Items!$G$5:$G$37)/SUMPRODUCT((Items!$B$5:$B$37=A10)*Items!$H$5:$H$37))</f>
         <v/>
       </c>
     </row>
@@ -6133,11 +5867,11 @@
         </is>
       </c>
       <c r="C11">
-        <f>COUNTIF(Items!$B$5:$B$39,A11)</f>
+        <f>COUNTIF(Items!$B$5:$B$37,A11)</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A11)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A11)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A11)*Items!$H$5:$H$39))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$37=A11)*Items!$H$5:$H$37)=0,"",SUMPRODUCT((Items!$B$5:$B$37=A11)*Items!$G$5:$G$37)/SUMPRODUCT((Items!$B$5:$B$37=A11)*Items!$H$5:$H$37))</f>
         <v/>
       </c>
     </row>
@@ -6151,11 +5885,11 @@
         </is>
       </c>
       <c r="C12">
-        <f>COUNTIF(Items!$B$5:$B$39,A12)</f>
+        <f>COUNTIF(Items!$B$5:$B$37,A12)</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A12)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A12)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A12)*Items!$H$5:$H$39))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$37=A12)*Items!$H$5:$H$37)=0,"",SUMPRODUCT((Items!$B$5:$B$37=A12)*Items!$G$5:$G$37)/SUMPRODUCT((Items!$B$5:$B$37=A12)*Items!$H$5:$H$37))</f>
         <v/>
       </c>
     </row>
@@ -6169,11 +5903,11 @@
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(Items!$B$5:$B$39,A13)</f>
+        <f>COUNTIF(Items!$B$5:$B$37,A13)</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A13)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A13)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A13)*Items!$H$5:$H$39))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$37=A13)*Items!$H$5:$H$37)=0,"",SUMPRODUCT((Items!$B$5:$B$37=A13)*Items!$G$5:$G$37)/SUMPRODUCT((Items!$B$5:$B$37=A13)*Items!$H$5:$H$37))</f>
         <v/>
       </c>
     </row>
@@ -6225,15 +5959,15 @@
         <v>1</v>
       </c>
       <c r="B5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$5:$AH$5))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$5:$AH$5=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$5:$AH$5)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$5:$AH$5))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$5:$AH$5=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$5:$AH$5)))</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$5:$AH$5))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$5:$AH$5=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$5:$AH$5)))</f>
         <v/>
       </c>
     </row>
@@ -6242,15 +5976,15 @@
         <v>2</v>
       </c>
       <c r="B6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$6:$AH$6))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$6:$AH$6=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$6:$AH$6)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$6:$AH$6))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$6:$AH$6=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$6:$AH$6)))</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$6:$AH$6))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$6:$AH$6=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$6:$AH$6)))</f>
         <v/>
       </c>
     </row>
@@ -6259,15 +5993,15 @@
         <v>3</v>
       </c>
       <c r="B7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$7:$AH$7))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$7:$AH$7=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$7:$AH$7)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$7:$AH$7))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$7:$AH$7=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$7:$AH$7)))</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$7:$AH$7))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$7:$AH$7=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$7:$AH$7)))</f>
         <v/>
       </c>
     </row>
@@ -6276,15 +6010,15 @@
         <v>4</v>
       </c>
       <c r="B8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$8:$AH$8))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$8:$AH$8=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$8:$AH$8)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$8:$AH$8))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$8:$AH$8=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$8:$AH$8)))</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$8:$AH$8))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$8:$AH$8=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$8:$AH$8)))</f>
         <v/>
       </c>
     </row>
@@ -6293,15 +6027,15 @@
         <v>5</v>
       </c>
       <c r="B9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$9:$AH$9))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$9:$AH$9=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$9:$AH$9)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$9:$AH$9))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$9:$AH$9=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$9:$AH$9)))</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$9:$AH$9))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$9:$AH$9=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$9:$AH$9)))</f>
         <v/>
       </c>
     </row>
@@ -6310,15 +6044,15 @@
         <v>6</v>
       </c>
       <c r="B10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$10:$AH$10))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$10:$AH$10=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$10:$AH$10)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$10:$AH$10))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$10:$AH$10=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$10:$AH$10)))</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$10:$AH$10))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$10:$AH$10=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$10:$AH$10)))</f>
         <v/>
       </c>
     </row>
@@ -6327,15 +6061,15 @@
         <v>7</v>
       </c>
       <c r="B11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$11:$AH$11))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$11:$AH$11=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$11:$AH$11)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$11:$AH$11))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$11:$AH$11=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$11:$AH$11)))</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$11:$AH$11))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$11:$AH$11=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$11:$AH$11)))</f>
         <v/>
       </c>
     </row>
@@ -6344,15 +6078,15 @@
         <v>8</v>
       </c>
       <c r="B12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$12:$AH$12))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$12:$AH$12=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$12:$AH$12)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$12:$AH$12))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$12:$AH$12=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$12:$AH$12)))</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$12:$AH$12))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$12:$AH$12=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$12:$AH$12)))</f>
         <v/>
       </c>
     </row>
@@ -6361,15 +6095,15 @@
         <v>9</v>
       </c>
       <c r="B13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$13:$AH$13))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$13:$AH$13=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$13:$AH$13)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$13:$AH$13))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$13:$AH$13=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$13:$AH$13)))</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$13:$AH$13))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$13:$AH$13=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$13:$AH$13)))</f>
         <v/>
       </c>
     </row>
@@ -6378,15 +6112,15 @@
         <v>10</v>
       </c>
       <c r="B14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$14:$AH$14))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$14:$AH$14=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$14:$AH$14)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$14:$AH$14))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$14:$AH$14=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$14:$AH$14)))</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$14:$AH$14))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$14:$AH$14=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$14:$AH$14)))</f>
         <v/>
       </c>
     </row>
@@ -6395,15 +6129,15 @@
         <v>11</v>
       </c>
       <c r="B15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$15:$AH$15))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$15:$AH$15=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$15:$AH$15)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$15:$AH$15))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$15:$AH$15=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$15:$AH$15)))</f>
         <v/>
       </c>
       <c r="D15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$15:$AH$15))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$15:$AH$15=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$15:$AH$15)))</f>
         <v/>
       </c>
     </row>
@@ -6412,15 +6146,15 @@
         <v>12</v>
       </c>
       <c r="B16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$16:$AH$16))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$16:$AH$16=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$16:$AH$16)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$16:$AH$16))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$16:$AH$16=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$16:$AH$16)))</f>
         <v/>
       </c>
       <c r="D16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$16:$AH$16))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$16:$AH$16=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$16:$AH$16)))</f>
         <v/>
       </c>
     </row>
@@ -6429,15 +6163,15 @@
         <v>13</v>
       </c>
       <c r="B17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$17:$AH$17))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$17:$AH$17=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$17:$AH$17)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$17:$AH$17))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$17:$AH$17=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$17:$AH$17)))</f>
         <v/>
       </c>
       <c r="D17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$17:$AH$17))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$17:$AH$17=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$17:$AH$17)))</f>
         <v/>
       </c>
     </row>
@@ -6446,15 +6180,15 @@
         <v>14</v>
       </c>
       <c r="B18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$18:$AH$18))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$18:$AH$18=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$18:$AH$18)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$18:$AH$18))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$18:$AH$18=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$18:$AH$18)))</f>
         <v/>
       </c>
       <c r="D18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$18:$AH$18))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$18:$AH$18=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$18:$AH$18)))</f>
         <v/>
       </c>
     </row>
@@ -6463,15 +6197,15 @@
         <v>15</v>
       </c>
       <c r="B19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$19:$AH$19))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$19:$AH$19=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$19:$AH$19)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$19:$AH$19))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$19:$AH$19=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$19:$AH$19)))</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$19:$AH$19))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$19:$AH$19=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$19:$AH$19)))</f>
         <v/>
       </c>
     </row>
@@ -6480,15 +6214,15 @@
         <v>16</v>
       </c>
       <c r="B20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$20:$AH$20))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$20:$AH$20=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$20:$AH$20)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$20:$AH$20))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$20:$AH$20=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$20:$AH$20)))</f>
         <v/>
       </c>
       <c r="D20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$20:$AH$20))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$20:$AH$20=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$20:$AH$20)))</f>
         <v/>
       </c>
     </row>
@@ -6497,15 +6231,15 @@
         <v>17</v>
       </c>
       <c r="B21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$21:$AH$21))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$21:$AH$21=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$21:$AH$21)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$21:$AH$21))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$21:$AH$21=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$21:$AH$21)))</f>
         <v/>
       </c>
       <c r="D21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$21:$AH$21))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$21:$AH$21=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$21:$AH$21)))</f>
         <v/>
       </c>
     </row>
@@ -6514,15 +6248,15 @@
         <v>18</v>
       </c>
       <c r="B22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$22:$AH$22))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$22:$AH$22=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$22:$AH$22)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$22:$AH$22))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$22:$AH$22=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$22:$AH$22)))</f>
         <v/>
       </c>
       <c r="D22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$22:$AH$22))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$22:$AH$22=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$22:$AH$22)))</f>
         <v/>
       </c>
     </row>
@@ -6531,15 +6265,15 @@
         <v>19</v>
       </c>
       <c r="B23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$23:$AH$23))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$23:$AH$23=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$23:$AH$23)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$23:$AH$23))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$23:$AH$23=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$23:$AH$23)))</f>
         <v/>
       </c>
       <c r="D23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$23:$AH$23))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$23:$AH$23=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$23:$AH$23)))</f>
         <v/>
       </c>
     </row>
@@ -6548,15 +6282,15 @@
         <v>20</v>
       </c>
       <c r="B24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$24:$AH$24))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$24:$AH$24=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$24:$AH$24)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$24:$AH$24))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$24:$AH$24=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$24:$AH$24)))</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$24:$AH$24))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$24:$AH$24=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$24:$AH$24)))</f>
         <v/>
       </c>
     </row>
@@ -6565,15 +6299,15 @@
         <v>21</v>
       </c>
       <c r="B25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$25:$AH$25))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$25:$AH$25=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$25:$AH$25)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$25:$AH$25))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$25:$AH$25=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$25:$AH$25)))</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$25:$AH$25))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$25:$AH$25=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$25:$AH$25)))</f>
         <v/>
       </c>
     </row>
@@ -6582,15 +6316,15 @@
         <v>22</v>
       </c>
       <c r="B26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$26:$AH$26))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$26:$AH$26=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$26:$AH$26)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$26:$AH$26))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$26:$AH$26=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$26:$AH$26)))</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$26:$AH$26))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$26:$AH$26=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$26:$AH$26)))</f>
         <v/>
       </c>
     </row>
@@ -6599,15 +6333,15 @@
         <v>23</v>
       </c>
       <c r="B27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$27:$AH$27))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$27:$AH$27=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$27:$AH$27)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$27:$AH$27))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$27:$AH$27=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$27:$AH$27)))</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$27:$AH$27))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$27:$AH$27=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$27:$AH$27)))</f>
         <v/>
       </c>
     </row>
@@ -6616,15 +6350,15 @@
         <v>24</v>
       </c>
       <c r="B28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$28:$AH$28))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$28:$AH$28=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$28:$AH$28)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$28:$AH$28))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$28:$AH$28=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$28:$AH$28)))</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$28:$AH$28))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$28:$AH$28=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$28:$AH$28)))</f>
         <v/>
       </c>
     </row>
@@ -6633,15 +6367,15 @@
         <v>25</v>
       </c>
       <c r="B29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$29:$AH$29))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$29:$AH$29=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$29:$AH$29)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$29:$AH$29))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$29:$AH$29=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$29:$AH$29)))</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$29:$AH$29))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$29:$AH$29=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$29:$AH$29)))</f>
         <v/>
       </c>
     </row>
@@ -6650,15 +6384,15 @@
         <v>26</v>
       </c>
       <c r="B30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$30:$AH$30))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$30:$AH$30=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$30:$AH$30)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$30:$AH$30))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$30:$AH$30=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$30:$AH$30)))</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$30:$AH$30))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$30:$AH$30=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$30:$AH$30)))</f>
         <v/>
       </c>
     </row>
@@ -6667,15 +6401,15 @@
         <v>27</v>
       </c>
       <c r="B31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$31:$AH$31))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$31:$AH$31=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$31:$AH$31)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$31:$AH$31))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$31:$AH$31=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$31:$AH$31)))</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$31:$AH$31))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$31:$AH$31=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$31:$AH$31)))</f>
         <v/>
       </c>
     </row>
@@ -6684,15 +6418,15 @@
         <v>28</v>
       </c>
       <c r="B32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$32:$AH$32))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$32:$AH$32=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$32:$AH$32)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$32:$AH$32))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$32:$AH$32=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$32:$AH$32)))</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$32:$AH$32))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$32:$AH$32=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$32:$AH$32)))</f>
         <v/>
       </c>
     </row>
@@ -6701,15 +6435,15 @@
         <v>29</v>
       </c>
       <c r="B33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$33:$AH$33))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$33:$AH$33=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$33:$AH$33)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$33:$AH$33))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$33:$AH$33=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$33:$AH$33)))</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$33:$AH$33))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$33:$AH$33=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$33:$AH$33)))</f>
         <v/>
       </c>
     </row>
@@ -6718,15 +6452,15 @@
         <v>30</v>
       </c>
       <c r="B34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$34:$AH$34))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$34:$AH$34=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$34:$AH$34)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$34:$AH$34))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$34:$AH$34=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$34:$AH$34)))</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$34:$AH$34))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$34:$AH$34=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$34:$AH$34)))</f>
         <v/>
       </c>
     </row>
@@ -6735,15 +6469,15 @@
         <v>31</v>
       </c>
       <c r="B35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$35:$AH$35))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$35:$AH$35=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$35:$AH$35)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$35:$AH$35))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$35:$AH$35=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$35:$AH$35)))</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$35:$AH$35))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$35:$AH$35=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$35:$AH$35)))</f>
         <v/>
       </c>
     </row>
@@ -6752,15 +6486,15 @@
         <v>32</v>
       </c>
       <c r="B36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$36:$AH$36))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$36:$AH$36=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$36:$AH$36)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$36:$AH$36))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$36:$AH$36=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$36:$AH$36)))</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$36:$AH$36))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$36:$AH$36=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$36:$AH$36)))</f>
         <v/>
       </c>
     </row>
@@ -6769,15 +6503,15 @@
         <v>33</v>
       </c>
       <c r="B37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$37:$AH$37))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$37:$AH$37=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$37:$AH$37)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$37:$AH$37))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$37:$AH$37=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$37:$AH$37)))</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$37:$AH$37))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$37:$AH$37=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$37:$AH$37)))</f>
         <v/>
       </c>
     </row>
@@ -6786,15 +6520,15 @@
         <v>34</v>
       </c>
       <c r="B38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$38:$AH$38))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$38:$AH$38=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$38:$AH$38)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$38:$AH$38))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$38:$AH$38=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$38:$AH$38)))</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$38:$AH$38))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$38:$AH$38=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$38:$AH$38)))</f>
         <v/>
       </c>
     </row>
@@ -6803,15 +6537,15 @@
         <v>35</v>
       </c>
       <c r="B39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$39:$AH$39))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*(Marks!$B$39:$AH$39=1))/SUMPRODUCT((Marks!$B$3:$AH$3=B$4)*ISNUMBER(Marks!$B$39:$AH$39)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$39:$AH$39))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*(Marks!$B$39:$AH$39=1))/SUMPRODUCT((Marks!$B$3:$AH$3=C$4)*ISNUMBER(Marks!$B$39:$AH$39)))</f>
         <v/>
       </c>
       <c r="D39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$39:$AH$39))=0,"",SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*(Marks!$B$39:$AH$39=1))/SUMPRODUCT((Marks!$B$3:$AH$3=D$4)*ISNUMBER(Marks!$B$39:$AH$39)))</f>
         <v/>
       </c>
     </row>
@@ -6962,27 +6696,27 @@
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="I5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$5:$AH$5))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$5:$AH$5=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$5:$AH$5)))</f>
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$5:$AH$5))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$5:$AH$5=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$5:$AH$5)))</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$5:$AH$5))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$5:$AH$5=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$5:$AH$5)))</f>
         <v/>
       </c>
       <c r="L5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$5:$AH$5))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$5:$AH$5=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$5:$AH$5)))</f>
         <v/>
       </c>
       <c r="M5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$5:$AH$5))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$5:$AH$5=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$5:$AH$5)))</f>
         <v/>
       </c>
       <c r="N5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$5:$AH$5))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$5:$AH$5=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$5:$AH$5)))</f>
         <v/>
       </c>
     </row>
@@ -6997,27 +6731,27 @@
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="I6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$6:$AH$6))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$6:$AH$6=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$6:$AH$6)))</f>
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$6:$AH$6))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$6:$AH$6=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$6:$AH$6)))</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$6:$AH$6))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$6:$AH$6=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$6:$AH$6)))</f>
         <v/>
       </c>
       <c r="L6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$6:$AH$6))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$6:$AH$6=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$6:$AH$6)))</f>
         <v/>
       </c>
       <c r="M6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$6:$AH$6))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$6:$AH$6=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$6:$AH$6)))</f>
         <v/>
       </c>
       <c r="N6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$6:$AH$6))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$6:$AH$6=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$6:$AH$6)))</f>
         <v/>
       </c>
     </row>
@@ -7032,27 +6766,27 @@
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="I7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$7:$AH$7))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$7:$AH$7=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$7:$AH$7)))</f>
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$7:$AH$7))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$7:$AH$7=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$7:$AH$7)))</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$7:$AH$7))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$7:$AH$7=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$7:$AH$7)))</f>
         <v/>
       </c>
       <c r="L7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$7:$AH$7))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$7:$AH$7=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$7:$AH$7)))</f>
         <v/>
       </c>
       <c r="M7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$7:$AH$7))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$7:$AH$7=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$7:$AH$7)))</f>
         <v/>
       </c>
       <c r="N7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$7:$AH$7))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$7:$AH$7=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$7:$AH$7)))</f>
         <v/>
       </c>
     </row>
@@ -7067,27 +6801,27 @@
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
       <c r="I8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$8:$AH$8))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$8:$AH$8=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$8:$AH$8)))</f>
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$8:$AH$8))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$8:$AH$8=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$8:$AH$8)))</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$8:$AH$8))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$8:$AH$8=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$8:$AH$8)))</f>
         <v/>
       </c>
       <c r="L8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$8:$AH$8))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$8:$AH$8=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$8:$AH$8)))</f>
         <v/>
       </c>
       <c r="M8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$8:$AH$8))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$8:$AH$8=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$8:$AH$8)))</f>
         <v/>
       </c>
       <c r="N8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$8:$AH$8))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$8:$AH$8=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$8:$AH$8)))</f>
         <v/>
       </c>
     </row>
@@ -7102,27 +6836,27 @@
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
       <c r="I9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$9:$AH$9))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$9:$AH$9=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$9:$AH$9)))</f>
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$9:$AH$9))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$9:$AH$9=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$9:$AH$9)))</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$9:$AH$9))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$9:$AH$9=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$9:$AH$9)))</f>
         <v/>
       </c>
       <c r="L9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$9:$AH$9))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$9:$AH$9=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$9:$AH$9)))</f>
         <v/>
       </c>
       <c r="M9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$9:$AH$9))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$9:$AH$9=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$9:$AH$9)))</f>
         <v/>
       </c>
       <c r="N9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$9:$AH$9))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$9:$AH$9=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$9:$AH$9)))</f>
         <v/>
       </c>
     </row>
@@ -7137,27 +6871,27 @@
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
       <c r="I10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$10:$AH$10))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$10:$AH$10=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$10:$AH$10)))</f>
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$10:$AH$10))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$10:$AH$10=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$10:$AH$10)))</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$10:$AH$10))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$10:$AH$10=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$10:$AH$10)))</f>
         <v/>
       </c>
       <c r="L10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$10:$AH$10))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$10:$AH$10=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$10:$AH$10)))</f>
         <v/>
       </c>
       <c r="M10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$10:$AH$10))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$10:$AH$10=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$10:$AH$10)))</f>
         <v/>
       </c>
       <c r="N10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$10:$AH$10))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$10:$AH$10=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$10:$AH$10)))</f>
         <v/>
       </c>
     </row>
@@ -7172,27 +6906,27 @@
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
       <c r="I11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$11:$AH$11))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$11:$AH$11=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$11:$AH$11)))</f>
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$11:$AH$11))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$11:$AH$11=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$11:$AH$11)))</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$11:$AH$11))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$11:$AH$11=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$11:$AH$11)))</f>
         <v/>
       </c>
       <c r="L11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$11:$AH$11))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$11:$AH$11=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$11:$AH$11)))</f>
         <v/>
       </c>
       <c r="M11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$11:$AH$11))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$11:$AH$11=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$11:$AH$11)))</f>
         <v/>
       </c>
       <c r="N11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$11:$AH$11))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$11:$AH$11=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$11:$AH$11)))</f>
         <v/>
       </c>
     </row>
@@ -7207,27 +6941,27 @@
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
       <c r="I12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$12:$AH$12))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$12:$AH$12=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$12:$AH$12)))</f>
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$12:$AH$12))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$12:$AH$12=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$12:$AH$12)))</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$12:$AH$12))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$12:$AH$12=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$12:$AH$12)))</f>
         <v/>
       </c>
       <c r="L12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$12:$AH$12))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$12:$AH$12=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$12:$AH$12)))</f>
         <v/>
       </c>
       <c r="M12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$12:$AH$12))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$12:$AH$12=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$12:$AH$12)))</f>
         <v/>
       </c>
       <c r="N12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$12:$AH$12))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$12:$AH$12=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$12:$AH$12)))</f>
         <v/>
       </c>
     </row>
@@ -7242,27 +6976,27 @@
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="I13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$13:$AH$13))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$13:$AH$13=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$13:$AH$13)))</f>
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$13:$AH$13))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$13:$AH$13=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$13:$AH$13)))</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$13:$AH$13))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$13:$AH$13=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$13:$AH$13)))</f>
         <v/>
       </c>
       <c r="L13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$13:$AH$13))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$13:$AH$13=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$13:$AH$13)))</f>
         <v/>
       </c>
       <c r="M13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$13:$AH$13))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$13:$AH$13=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$13:$AH$13)))</f>
         <v/>
       </c>
       <c r="N13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$13:$AH$13))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$13:$AH$13=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$13:$AH$13)))</f>
         <v/>
       </c>
     </row>
@@ -7277,27 +7011,27 @@
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="I14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$14:$AH$14))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$14:$AH$14=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$14:$AH$14)))</f>
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$14:$AH$14))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$14:$AH$14=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$14:$AH$14)))</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$14:$AH$14))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$14:$AH$14=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$14:$AH$14)))</f>
         <v/>
       </c>
       <c r="L14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$14:$AH$14))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$14:$AH$14=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$14:$AH$14)))</f>
         <v/>
       </c>
       <c r="M14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$14:$AH$14))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$14:$AH$14=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$14:$AH$14)))</f>
         <v/>
       </c>
       <c r="N14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$14:$AH$14))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$14:$AH$14=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$14:$AH$14)))</f>
         <v/>
       </c>
     </row>
@@ -7312,27 +7046,27 @@
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="I15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$15:$AH$15))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$15:$AH$15=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$15:$AH$15)))</f>
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$15:$AH$15))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$15:$AH$15=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$15:$AH$15)))</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$15:$AH$15))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$15:$AH$15=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$15:$AH$15)))</f>
         <v/>
       </c>
       <c r="L15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$15:$AH$15))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$15:$AH$15=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$15:$AH$15)))</f>
         <v/>
       </c>
       <c r="M15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$15:$AH$15))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$15:$AH$15=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$15:$AH$15)))</f>
         <v/>
       </c>
       <c r="N15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$15:$AH$15))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$15:$AH$15=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$15:$AH$15)))</f>
         <v/>
       </c>
     </row>
@@ -7347,27 +7081,27 @@
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
       <c r="I16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$16:$AH$16))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$16:$AH$16=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$16:$AH$16)))</f>
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$16:$AH$16))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$16:$AH$16=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$16:$AH$16)))</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$16:$AH$16))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$16:$AH$16=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$16:$AH$16)))</f>
         <v/>
       </c>
       <c r="L16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$16:$AH$16))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$16:$AH$16=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$16:$AH$16)))</f>
         <v/>
       </c>
       <c r="M16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$16:$AH$16))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$16:$AH$16=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$16:$AH$16)))</f>
         <v/>
       </c>
       <c r="N16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$16:$AH$16))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$16:$AH$16=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$16:$AH$16)))</f>
         <v/>
       </c>
     </row>
@@ -7382,27 +7116,27 @@
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="I17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$17:$AH$17))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$17:$AH$17=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$17:$AH$17)))</f>
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$17:$AH$17))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$17:$AH$17=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$17:$AH$17)))</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$17:$AH$17))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$17:$AH$17=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$17:$AH$17)))</f>
         <v/>
       </c>
       <c r="L17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$17:$AH$17))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$17:$AH$17=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$17:$AH$17)))</f>
         <v/>
       </c>
       <c r="M17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$17:$AH$17))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$17:$AH$17=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$17:$AH$17)))</f>
         <v/>
       </c>
       <c r="N17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$17:$AH$17))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$17:$AH$17=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$17:$AH$17)))</f>
         <v/>
       </c>
     </row>
@@ -7417,27 +7151,27 @@
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="I18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$18:$AH$18))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$18:$AH$18=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$18:$AH$18)))</f>
         <v/>
       </c>
       <c r="J18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$18:$AH$18))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$18:$AH$18=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$18:$AH$18)))</f>
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$18:$AH$18))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$18:$AH$18=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$18:$AH$18)))</f>
         <v/>
       </c>
       <c r="L18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$18:$AH$18))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$18:$AH$18=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$18:$AH$18)))</f>
         <v/>
       </c>
       <c r="M18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$18:$AH$18))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$18:$AH$18=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$18:$AH$18)))</f>
         <v/>
       </c>
       <c r="N18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$18:$AH$18))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$18:$AH$18=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$18:$AH$18)))</f>
         <v/>
       </c>
     </row>
@@ -7452,27 +7186,27 @@
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="I19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$19:$AH$19))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$19:$AH$19=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$19:$AH$19)))</f>
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$19:$AH$19))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$19:$AH$19=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$19:$AH$19)))</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$19:$AH$19))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$19:$AH$19=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$19:$AH$19)))</f>
         <v/>
       </c>
       <c r="L19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$19:$AH$19))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$19:$AH$19=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$19:$AH$19)))</f>
         <v/>
       </c>
       <c r="M19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$19:$AH$19))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$19:$AH$19=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$19:$AH$19)))</f>
         <v/>
       </c>
       <c r="N19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$19:$AH$19))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$19:$AH$19=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$19:$AH$19)))</f>
         <v/>
       </c>
     </row>
@@ -7487,27 +7221,27 @@
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="I20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$20:$AH$20))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$20:$AH$20=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$20:$AH$20)))</f>
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$20:$AH$20))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$20:$AH$20=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$20:$AH$20)))</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$20:$AH$20))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$20:$AH$20=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$20:$AH$20)))</f>
         <v/>
       </c>
       <c r="L20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$20:$AH$20))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$20:$AH$20=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$20:$AH$20)))</f>
         <v/>
       </c>
       <c r="M20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$20:$AH$20))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$20:$AH$20=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$20:$AH$20)))</f>
         <v/>
       </c>
       <c r="N20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$20:$AH$20))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$20:$AH$20=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$20:$AH$20)))</f>
         <v/>
       </c>
     </row>
@@ -7522,27 +7256,27 @@
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="I21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$21:$AH$21))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$21:$AH$21=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$21:$AH$21)))</f>
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$21:$AH$21))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$21:$AH$21=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$21:$AH$21)))</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$21:$AH$21))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$21:$AH$21=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$21:$AH$21)))</f>
         <v/>
       </c>
       <c r="L21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$21:$AH$21))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$21:$AH$21=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$21:$AH$21)))</f>
         <v/>
       </c>
       <c r="M21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$21:$AH$21))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$21:$AH$21=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$21:$AH$21)))</f>
         <v/>
       </c>
       <c r="N21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$21:$AH$21))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$21:$AH$21=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$21:$AH$21)))</f>
         <v/>
       </c>
     </row>
@@ -7557,27 +7291,27 @@
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="I22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$22:$AH$22))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$22:$AH$22=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$22:$AH$22)))</f>
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$22:$AH$22))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$22:$AH$22=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$22:$AH$22)))</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$22:$AH$22))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$22:$AH$22=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$22:$AH$22)))</f>
         <v/>
       </c>
       <c r="L22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$22:$AH$22))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$22:$AH$22=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$22:$AH$22)))</f>
         <v/>
       </c>
       <c r="M22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$22:$AH$22))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$22:$AH$22=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$22:$AH$22)))</f>
         <v/>
       </c>
       <c r="N22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$22:$AH$22))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$22:$AH$22=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$22:$AH$22)))</f>
         <v/>
       </c>
     </row>
@@ -7592,27 +7326,27 @@
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="I23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$23:$AH$23))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$23:$AH$23=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$23:$AH$23)))</f>
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$23:$AH$23))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$23:$AH$23=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$23:$AH$23)))</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$23:$AH$23))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$23:$AH$23=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$23:$AH$23)))</f>
         <v/>
       </c>
       <c r="L23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$23:$AH$23))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$23:$AH$23=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$23:$AH$23)))</f>
         <v/>
       </c>
       <c r="M23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$23:$AH$23))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$23:$AH$23=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$23:$AH$23)))</f>
         <v/>
       </c>
       <c r="N23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$23:$AH$23))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$23:$AH$23=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$23:$AH$23)))</f>
         <v/>
       </c>
     </row>
@@ -7627,27 +7361,27 @@
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="I24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$24:$AH$24))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$24:$AH$24=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$24:$AH$24)))</f>
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$24:$AH$24))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$24:$AH$24=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$24:$AH$24)))</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$24:$AH$24))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$24:$AH$24=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$24:$AH$24)))</f>
         <v/>
       </c>
       <c r="L24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$24:$AH$24))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$24:$AH$24=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$24:$AH$24)))</f>
         <v/>
       </c>
       <c r="M24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$24:$AH$24))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$24:$AH$24=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$24:$AH$24)))</f>
         <v/>
       </c>
       <c r="N24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$24:$AH$24))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$24:$AH$24=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$24:$AH$24)))</f>
         <v/>
       </c>
     </row>
@@ -7662,27 +7396,27 @@
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="I25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$25:$AH$25))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$25:$AH$25=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$25:$AH$25)))</f>
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$25:$AH$25))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$25:$AH$25=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$25:$AH$25)))</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$25:$AH$25))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$25:$AH$25=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$25:$AH$25)))</f>
         <v/>
       </c>
       <c r="L25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$25:$AH$25))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$25:$AH$25=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$25:$AH$25)))</f>
         <v/>
       </c>
       <c r="M25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$25:$AH$25))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$25:$AH$25=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$25:$AH$25)))</f>
         <v/>
       </c>
       <c r="N25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$25:$AH$25))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$25:$AH$25=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$25:$AH$25)))</f>
         <v/>
       </c>
     </row>
@@ -7697,27 +7431,27 @@
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="I26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$26:$AH$26))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$26:$AH$26=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$26:$AH$26)))</f>
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$26:$AH$26))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$26:$AH$26=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$26:$AH$26)))</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$26:$AH$26))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$26:$AH$26=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$26:$AH$26)))</f>
         <v/>
       </c>
       <c r="L26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$26:$AH$26))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$26:$AH$26=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$26:$AH$26)))</f>
         <v/>
       </c>
       <c r="M26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$26:$AH$26))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$26:$AH$26=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$26:$AH$26)))</f>
         <v/>
       </c>
       <c r="N26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$26:$AH$26))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$26:$AH$26=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$26:$AH$26)))</f>
         <v/>
       </c>
     </row>
@@ -7732,27 +7466,27 @@
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="I27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$27:$AH$27))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$27:$AH$27=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$27:$AH$27)))</f>
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$27:$AH$27))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$27:$AH$27=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$27:$AH$27)))</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$27:$AH$27))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$27:$AH$27=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$27:$AH$27)))</f>
         <v/>
       </c>
       <c r="L27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$27:$AH$27))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$27:$AH$27=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$27:$AH$27)))</f>
         <v/>
       </c>
       <c r="M27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$27:$AH$27))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$27:$AH$27=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$27:$AH$27)))</f>
         <v/>
       </c>
       <c r="N27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$27:$AH$27))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$27:$AH$27=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$27:$AH$27)))</f>
         <v/>
       </c>
     </row>
@@ -7767,27 +7501,27 @@
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="I28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$28:$AH$28))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$28:$AH$28=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$28:$AH$28)))</f>
         <v/>
       </c>
       <c r="J28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$28:$AH$28))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$28:$AH$28=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$28:$AH$28)))</f>
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$28:$AH$28))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$28:$AH$28=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$28:$AH$28)))</f>
         <v/>
       </c>
       <c r="L28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$28:$AH$28))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$28:$AH$28=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$28:$AH$28)))</f>
         <v/>
       </c>
       <c r="M28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$28:$AH$28))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$28:$AH$28=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$28:$AH$28)))</f>
         <v/>
       </c>
       <c r="N28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$28:$AH$28))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$28:$AH$28=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$28:$AH$28)))</f>
         <v/>
       </c>
     </row>
@@ -7802,27 +7536,27 @@
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
       <c r="I29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$29:$AH$29))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$29:$AH$29=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$29:$AH$29)))</f>
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$29:$AH$29))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$29:$AH$29=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$29:$AH$29)))</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$29:$AH$29))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$29:$AH$29=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$29:$AH$29)))</f>
         <v/>
       </c>
       <c r="L29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$29:$AH$29))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$29:$AH$29=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$29:$AH$29)))</f>
         <v/>
       </c>
       <c r="M29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$29:$AH$29))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$29:$AH$29=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$29:$AH$29)))</f>
         <v/>
       </c>
       <c r="N29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$29:$AH$29))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$29:$AH$29=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$29:$AH$29)))</f>
         <v/>
       </c>
     </row>
@@ -7837,27 +7571,27 @@
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
       <c r="I30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$30:$AH$30))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$30:$AH$30=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$30:$AH$30)))</f>
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$30:$AH$30))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$30:$AH$30=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$30:$AH$30)))</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$30:$AH$30))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$30:$AH$30=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$30:$AH$30)))</f>
         <v/>
       </c>
       <c r="L30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$30:$AH$30))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$30:$AH$30=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$30:$AH$30)))</f>
         <v/>
       </c>
       <c r="M30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$30:$AH$30))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$30:$AH$30=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$30:$AH$30)))</f>
         <v/>
       </c>
       <c r="N30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$30:$AH$30))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$30:$AH$30=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$30:$AH$30)))</f>
         <v/>
       </c>
     </row>
@@ -7872,27 +7606,27 @@
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>
       <c r="I31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$31:$AH$31))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$31:$AH$31=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$31:$AH$31)))</f>
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$31:$AH$31))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$31:$AH$31=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$31:$AH$31)))</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$31:$AH$31))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$31:$AH$31=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$31:$AH$31)))</f>
         <v/>
       </c>
       <c r="L31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$31:$AH$31))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$31:$AH$31=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$31:$AH$31)))</f>
         <v/>
       </c>
       <c r="M31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$31:$AH$31))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$31:$AH$31=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$31:$AH$31)))</f>
         <v/>
       </c>
       <c r="N31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$31:$AH$31))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$31:$AH$31=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$31:$AH$31)))</f>
         <v/>
       </c>
     </row>
@@ -7907,27 +7641,27 @@
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
       <c r="I32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$32:$AH$32))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$32:$AH$32=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$32:$AH$32)))</f>
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$32:$AH$32))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$32:$AH$32=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$32:$AH$32)))</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$32:$AH$32))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$32:$AH$32=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$32:$AH$32)))</f>
         <v/>
       </c>
       <c r="L32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$32:$AH$32))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$32:$AH$32=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$32:$AH$32)))</f>
         <v/>
       </c>
       <c r="M32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$32:$AH$32))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$32:$AH$32=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$32:$AH$32)))</f>
         <v/>
       </c>
       <c r="N32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$32:$AH$32))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$32:$AH$32=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$32:$AH$32)))</f>
         <v/>
       </c>
     </row>
@@ -7942,27 +7676,27 @@
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
       <c r="I33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$33:$AH$33))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$33:$AH$33=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$33:$AH$33)))</f>
         <v/>
       </c>
       <c r="J33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$33:$AH$33))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$33:$AH$33=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$33:$AH$33)))</f>
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$33:$AH$33))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$33:$AH$33=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$33:$AH$33)))</f>
         <v/>
       </c>
       <c r="L33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$33:$AH$33))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$33:$AH$33=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$33:$AH$33)))</f>
         <v/>
       </c>
       <c r="M33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$33:$AH$33))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$33:$AH$33=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$33:$AH$33)))</f>
         <v/>
       </c>
       <c r="N33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$33:$AH$33))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$33:$AH$33=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$33:$AH$33)))</f>
         <v/>
       </c>
     </row>
@@ -7977,27 +7711,27 @@
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
       <c r="I34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$34:$AH$34))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$34:$AH$34=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$34:$AH$34)))</f>
         <v/>
       </c>
       <c r="J34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$34:$AH$34))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$34:$AH$34=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$34:$AH$34)))</f>
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$34:$AH$34))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$34:$AH$34=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$34:$AH$34)))</f>
         <v/>
       </c>
       <c r="L34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$34:$AH$34))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$34:$AH$34=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$34:$AH$34)))</f>
         <v/>
       </c>
       <c r="M34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$34:$AH$34))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$34:$AH$34=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$34:$AH$34)))</f>
         <v/>
       </c>
       <c r="N34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$34:$AH$34))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$34:$AH$34=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$34:$AH$34)))</f>
         <v/>
       </c>
     </row>
@@ -8012,27 +7746,27 @@
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="5" t="n"/>
       <c r="I35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$35:$AH$35))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$35:$AH$35=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$35:$AH$35)))</f>
         <v/>
       </c>
       <c r="J35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$35:$AH$35))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$35:$AH$35=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$35:$AH$35)))</f>
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$35:$AH$35))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$35:$AH$35=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$35:$AH$35)))</f>
         <v/>
       </c>
       <c r="L35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$35:$AH$35))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$35:$AH$35=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$35:$AH$35)))</f>
         <v/>
       </c>
       <c r="M35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$35:$AH$35))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$35:$AH$35=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$35:$AH$35)))</f>
         <v/>
       </c>
       <c r="N35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$35:$AH$35))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$35:$AH$35=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$35:$AH$35)))</f>
         <v/>
       </c>
     </row>
@@ -8047,27 +7781,27 @@
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="I36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$36:$AH$36))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$36:$AH$36=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$36:$AH$36)))</f>
         <v/>
       </c>
       <c r="J36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$36:$AH$36))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$36:$AH$36=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$36:$AH$36)))</f>
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$36:$AH$36))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$36:$AH$36=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$36:$AH$36)))</f>
         <v/>
       </c>
       <c r="L36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$36:$AH$36))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$36:$AH$36=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$36:$AH$36)))</f>
         <v/>
       </c>
       <c r="M36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$36:$AH$36))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$36:$AH$36=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$36:$AH$36)))</f>
         <v/>
       </c>
       <c r="N36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$36:$AH$36))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$36:$AH$36=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$36:$AH$36)))</f>
         <v/>
       </c>
     </row>
@@ -8082,27 +7816,27 @@
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
       <c r="I37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$37:$AH$37))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$37:$AH$37=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$37:$AH$37)))</f>
         <v/>
       </c>
       <c r="J37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$37:$AH$37))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$37:$AH$37=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$37:$AH$37)))</f>
         <v/>
       </c>
       <c r="K37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$37:$AH$37))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$37:$AH$37=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$37:$AH$37)))</f>
         <v/>
       </c>
       <c r="L37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$37:$AH$37))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$37:$AH$37=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$37:$AH$37)))</f>
         <v/>
       </c>
       <c r="M37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$37:$AH$37))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$37:$AH$37=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$37:$AH$37)))</f>
         <v/>
       </c>
       <c r="N37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$37:$AH$37))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$37:$AH$37=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$37:$AH$37)))</f>
         <v/>
       </c>
     </row>
@@ -8117,27 +7851,27 @@
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="5" t="n"/>
       <c r="I38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$38:$AH$38))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$38:$AH$38=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$38:$AH$38)))</f>
         <v/>
       </c>
       <c r="J38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$38:$AH$38))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$38:$AH$38=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$38:$AH$38)))</f>
         <v/>
       </c>
       <c r="K38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$38:$AH$38))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$38:$AH$38=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$38:$AH$38)))</f>
         <v/>
       </c>
       <c r="L38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$38:$AH$38))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$38:$AH$38=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$38:$AH$38)))</f>
         <v/>
       </c>
       <c r="M38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$38:$AH$38))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$38:$AH$38=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$38:$AH$38)))</f>
         <v/>
       </c>
       <c r="N38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$38:$AH$38))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$38:$AH$38=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$38:$AH$38)))</f>
         <v/>
       </c>
     </row>
@@ -8152,27 +7886,27 @@
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
       <c r="I39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$39:$AH$39))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*(Marks!$B$39:$AH$39=1))/SUMPRODUCT((Marks!$B$2:$AH$2=I$3)*ISNUMBER(Marks!$B$39:$AH$39)))</f>
         <v/>
       </c>
       <c r="J39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$39:$AH$39))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*(Marks!$B$39:$AH$39=1))/SUMPRODUCT((Marks!$B$2:$AH$2=J$3)*ISNUMBER(Marks!$B$39:$AH$39)))</f>
         <v/>
       </c>
       <c r="K39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$39:$AH$39))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*(Marks!$B$39:$AH$39=1))/SUMPRODUCT((Marks!$B$2:$AH$2=K$3)*ISNUMBER(Marks!$B$39:$AH$39)))</f>
         <v/>
       </c>
       <c r="L39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$39:$AH$39))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*(Marks!$B$39:$AH$39=1))/SUMPRODUCT((Marks!$B$2:$AH$2=L$3)*ISNUMBER(Marks!$B$39:$AH$39)))</f>
         <v/>
       </c>
       <c r="M39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=M$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$39:$AH$39))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*(Marks!$B$39:$AH$39=1))/SUMPRODUCT((Marks!$B$2:$AH$2=M$3)*ISNUMBER(Marks!$B$39:$AH$39)))</f>
         <v/>
       </c>
       <c r="N39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=N$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$39:$AH$39))=0,"",SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*(Marks!$B$39:$AH$39=1))/SUMPRODUCT((Marks!$B$2:$AH$2=N$3)*ISNUMBER(Marks!$B$39:$AH$39)))</f>
         <v/>
       </c>
     </row>

--- a/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
@@ -5809,7 +5809,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Part 1. Anand's Monday numbers</t>
+          <t>Part 1. Can the warehouse give Anand Monday numbers that his analyst can audit line by line?</t>
         </is>
       </c>
       <c r="C8">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Part 2. Booked against collected</t>
+          <t>Part 2. Can Anand sign what Kalpa collected against what it booked, with nothing lost or counted twice?</t>
         </is>
       </c>
       <c r="C9">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Part 3. The protect list and the plan line</t>
+          <t>Part 3. Which members should Marketing protect and call, and did July to September keep pace with the plan?</t>
         </is>
       </c>
       <c r="C10">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Part 4. One row per customer</t>
+          <t>Part 4. Can the growth team act on Monday's table of 340 customers without checking it first?</t>
         </is>
       </c>
       <c r="C11">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Part 5. The last mile, and spreadsheets in public</t>
+          <t>Part 5. Which spreadsheet numbers can a director trust, in Monday's workbook and in three public cases?</t>
         </is>
       </c>
       <c r="C12">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Part 6. Read the code, read the data: an AI team's tables</t>
+          <t>Part 6. Can a food-delivery company's AI team trust the numbers behind its model and budget decisions?</t>
         </is>
       </c>
       <c r="C13">
@@ -7942,7 +7942,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Part 1. Anand's Monday numbers</t>
+          <t>Part 1. Can the warehouse give Anand Monday numbers that his analyst can audit line by line?</t>
         </is>
       </c>
       <c r="B43" s="7">
@@ -7961,7 +7961,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Part 2. Booked against collected</t>
+          <t>Part 2. Can Anand sign what Kalpa collected against what it booked, with nothing lost or counted twice?</t>
         </is>
       </c>
       <c r="B44" s="7">
@@ -7980,7 +7980,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Part 3. The protect list and the plan line</t>
+          <t>Part 3. Which members should Marketing protect and call, and did July to September keep pace with the plan?</t>
         </is>
       </c>
       <c r="B45" s="7">
@@ -7999,7 +7999,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Part 4. One row per customer</t>
+          <t>Part 4. Can the growth team act on Monday's table of 340 customers without checking it first?</t>
         </is>
       </c>
       <c r="B46" s="7">
@@ -8018,7 +8018,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Part 5. The last mile, and spreadsheets in public</t>
+          <t>Part 5. Which spreadsheet numbers can a director trust, in Monday's workbook and in three public cases?</t>
         </is>
       </c>
       <c r="B47" s="7">
@@ -8037,7 +8037,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Part 6. Read the code, read the data: an AI team's tables</t>
+          <t>Part 6. Can a food-delivery company's AI team trust the numbers behind its model and budget decisions?</t>
         </is>
       </c>
       <c r="B48" s="7">

--- a/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W02/SAT/answer-key/C2_W02_SAT_item_analysis_TRAINER.xlsx
@@ -5863,7 +5863,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Part 4. Can the growth team act on Monday's table of 340 customers without checking it first?</t>
+          <t>Part 4. What must Monday's customer table check before the growth team acts on it?</t>
         </is>
       </c>
       <c r="C11">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Part 5. Which spreadsheet numbers can a director trust, in Monday's workbook and in three public cases?</t>
+          <t>Part 5. Which numbers in Monday's workbook can a director trust, and where did three public cases go wrong?</t>
         </is>
       </c>
       <c r="C12">
@@ -7999,7 +7999,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Part 4. Can the growth team act on Monday's table of 340 customers without checking it first?</t>
+          <t>Part 4. What must Monday's customer table check before the growth team acts on it?</t>
         </is>
       </c>
       <c r="B46" s="7">
@@ -8018,7 +8018,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Part 5. Which spreadsheet numbers can a director trust, in Monday's workbook and in three public cases?</t>
+          <t>Part 5. Which numbers in Monday's workbook can a director trust, and where did three public cases go wrong?</t>
         </is>
       </c>
       <c r="B47" s="7">
